--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CF7FF2-7E97-4E10-9069-3E266E249524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A3F813-E25A-4DF9-917F-CE282F5E726C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>P/5</t>
+  </si>
+  <si>
+    <t>P/2</t>
   </si>
 </sst>
 </file>
@@ -555,8 +558,12 @@
       <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -668,8 +675,12 @@
       <c r="J2" s="1">
         <v>46078</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="K2" s="1">
+        <v>46080</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46085</v>
+      </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -757,6 +768,12 @@
         <v>34</v>
       </c>
       <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -868,6 +885,12 @@
       <c r="J4" t="s">
         <v>34</v>
       </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -977,6 +1000,12 @@
       <c r="J5" t="s">
         <v>34</v>
       </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1086,6 +1115,12 @@
       <c r="J6" t="s">
         <v>34</v>
       </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1195,6 +1230,12 @@
       <c r="J7" t="s">
         <v>34</v>
       </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1304,6 +1345,12 @@
       <c r="J8" t="s">
         <v>34</v>
       </c>
+      <c r="K8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1413,6 +1460,12 @@
       <c r="J9" t="s">
         <v>34</v>
       </c>
+      <c r="K9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1522,6 +1575,12 @@
       <c r="J10" t="s">
         <v>34</v>
       </c>
+      <c r="K10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1631,6 +1690,12 @@
       <c r="J11" t="s">
         <v>34</v>
       </c>
+      <c r="K11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1740,6 +1805,12 @@
       <c r="J12" t="s">
         <v>34</v>
       </c>
+      <c r="K12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1849,6 +1920,12 @@
       <c r="J13" t="s">
         <v>34</v>
       </c>
+      <c r="K13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -1958,6 +2035,12 @@
       <c r="J14" t="s">
         <v>34</v>
       </c>
+      <c r="K14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2067,6 +2150,12 @@
       <c r="J15" t="s">
         <v>34</v>
       </c>
+      <c r="K15" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2176,6 +2265,12 @@
       <c r="J16" t="s">
         <v>34</v>
       </c>
+      <c r="K16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2285,6 +2380,12 @@
       <c r="J17" t="s">
         <v>34</v>
       </c>
+      <c r="K17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2394,6 +2495,12 @@
       <c r="J18" t="s">
         <v>34</v>
       </c>
+      <c r="K18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2503,6 +2610,12 @@
       <c r="J19" t="s">
         <v>34</v>
       </c>
+      <c r="K19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2612,6 +2725,12 @@
       <c r="J20" t="s">
         <v>34</v>
       </c>
+      <c r="K20" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2721,6 +2840,12 @@
       <c r="J21" t="s">
         <v>34</v>
       </c>
+      <c r="K21" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" t="s">
+        <v>41</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2830,6 +2955,12 @@
       <c r="J22" t="s">
         <v>34</v>
       </c>
+      <c r="K22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -2939,6 +3070,12 @@
       <c r="J23" t="s">
         <v>34</v>
       </c>
+      <c r="K23" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3048,6 +3185,12 @@
       <c r="J24" t="s">
         <v>34</v>
       </c>
+      <c r="K24" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3157,6 +3300,12 @@
       <c r="J25" t="s">
         <v>40</v>
       </c>
+      <c r="K25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3266,6 +3415,12 @@
       <c r="J26" t="s">
         <v>35</v>
       </c>
+      <c r="K26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3375,6 +3530,12 @@
       <c r="J27" t="s">
         <v>34</v>
       </c>
+      <c r="K27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3484,6 +3645,12 @@
       <c r="J28" t="s">
         <v>34</v>
       </c>
+      <c r="K28" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3593,6 +3760,12 @@
       <c r="J29" t="s">
         <v>35</v>
       </c>
+      <c r="K29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3702,6 +3875,12 @@
       <c r="J30" t="s">
         <v>34</v>
       </c>
+      <c r="K30" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" t="s">
+        <v>41</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3811,6 +3990,12 @@
       <c r="J31" t="s">
         <v>34</v>
       </c>
+      <c r="K31" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -3892,7 +4077,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 D3:AZ10 BB3:BB22 BE4:BJ10 BK4:DG31 D11:BA22 BC11:BJ22 D23:BJ31">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 BE4:BJ10 BK4:DG31 BC11:BJ22 M23:BJ31 M11:BA22 D3:AZ5 M6:AZ10 D6:J31 K3:L31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A3F813-E25A-4DF9-917F-CE282F5E726C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336B6E54-FDE7-4DD3-88AE-E26CA616D4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -564,8 +564,12 @@
       <c r="L1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -681,8 +685,12 @@
       <c r="L2" s="1">
         <v>46085</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="M2" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N2" s="1">
+        <v>46092</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -774,6 +782,12 @@
         <v>34</v>
       </c>
       <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -891,6 +905,12 @@
       <c r="L4" t="s">
         <v>34</v>
       </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1006,6 +1026,12 @@
       <c r="L5" t="s">
         <v>34</v>
       </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1121,6 +1147,12 @@
       <c r="L6" t="s">
         <v>34</v>
       </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1236,6 +1268,12 @@
       <c r="L7" t="s">
         <v>34</v>
       </c>
+      <c r="M7" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1351,6 +1389,12 @@
       <c r="L8" t="s">
         <v>34</v>
       </c>
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1466,6 +1510,12 @@
       <c r="L9" t="s">
         <v>34</v>
       </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1581,6 +1631,12 @@
       <c r="L10" t="s">
         <v>34</v>
       </c>
+      <c r="M10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1696,6 +1752,12 @@
       <c r="L11" t="s">
         <v>34</v>
       </c>
+      <c r="M11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1811,6 +1873,12 @@
       <c r="L12" t="s">
         <v>34</v>
       </c>
+      <c r="M12" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1926,6 +1994,12 @@
       <c r="L13" t="s">
         <v>34</v>
       </c>
+      <c r="M13" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2041,6 +2115,12 @@
       <c r="L14" t="s">
         <v>34</v>
       </c>
+      <c r="M14" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2156,6 +2236,12 @@
       <c r="L15" t="s">
         <v>34</v>
       </c>
+      <c r="M15" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2271,6 +2357,12 @@
       <c r="L16" t="s">
         <v>34</v>
       </c>
+      <c r="M16" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2386,6 +2478,12 @@
       <c r="L17" t="s">
         <v>34</v>
       </c>
+      <c r="M17" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2501,6 +2599,12 @@
       <c r="L18" t="s">
         <v>34</v>
       </c>
+      <c r="M18" t="s">
+        <v>34</v>
+      </c>
+      <c r="N18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2616,6 +2720,12 @@
       <c r="L19" t="s">
         <v>34</v>
       </c>
+      <c r="M19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2731,6 +2841,12 @@
       <c r="L20" t="s">
         <v>34</v>
       </c>
+      <c r="M20" t="s">
+        <v>34</v>
+      </c>
+      <c r="N20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2846,6 +2962,12 @@
       <c r="L21" t="s">
         <v>41</v>
       </c>
+      <c r="M21" t="s">
+        <v>34</v>
+      </c>
+      <c r="N21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2961,6 +3083,12 @@
       <c r="L22" t="s">
         <v>34</v>
       </c>
+      <c r="M22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3076,6 +3204,12 @@
       <c r="L23" t="s">
         <v>34</v>
       </c>
+      <c r="M23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3191,6 +3325,12 @@
       <c r="L24" t="s">
         <v>34</v>
       </c>
+      <c r="M24" t="s">
+        <v>34</v>
+      </c>
+      <c r="N24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3306,6 +3446,12 @@
       <c r="L25" t="s">
         <v>34</v>
       </c>
+      <c r="M25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" t="s">
+        <v>35</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3421,6 +3567,12 @@
       <c r="L26" t="s">
         <v>34</v>
       </c>
+      <c r="M26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3536,6 +3688,12 @@
       <c r="L27" t="s">
         <v>34</v>
       </c>
+      <c r="M27" t="s">
+        <v>34</v>
+      </c>
+      <c r="N27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3651,6 +3809,12 @@
       <c r="L28" t="s">
         <v>34</v>
       </c>
+      <c r="M28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3766,6 +3930,12 @@
       <c r="L29" t="s">
         <v>34</v>
       </c>
+      <c r="M29" t="s">
+        <v>34</v>
+      </c>
+      <c r="N29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3881,6 +4051,12 @@
       <c r="L30" t="s">
         <v>41</v>
       </c>
+      <c r="M30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N30" t="s">
+        <v>35</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3996,6 +4172,12 @@
       <c r="L31" t="s">
         <v>34</v>
       </c>
+      <c r="M31" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4077,7 +4259,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 BE4:BJ10 BK4:DG31 BC11:BJ22 M23:BJ31 M11:BA22 D3:AZ5 M6:AZ10 D6:J31 K3:L31">
+  <conditionalFormatting sqref="BE3:DG3 D3:AZ5 BB3:BB22 K3:L31 BE4:BJ10 BK4:DG31 M6:AZ10 D6:J31 M11:BA22 BC11:BJ22 M23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336B6E54-FDE7-4DD3-88AE-E26CA616D4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD67E8F-DD13-4EBF-91F3-3EA32B1A3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -570,8 +570,12 @@
       <c r="N1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -691,8 +695,12 @@
       <c r="N2" s="1">
         <v>46092</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
+      <c r="O2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="P2" s="1">
+        <v>46099</v>
+      </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -788,6 +796,12 @@
         <v>34</v>
       </c>
       <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -911,6 +925,12 @@
       <c r="N4" t="s">
         <v>34</v>
       </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1032,6 +1052,12 @@
       <c r="N5" t="s">
         <v>34</v>
       </c>
+      <c r="O5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1153,6 +1179,12 @@
       <c r="N6" t="s">
         <v>34</v>
       </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1274,6 +1306,12 @@
       <c r="N7" t="s">
         <v>34</v>
       </c>
+      <c r="O7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1395,6 +1433,12 @@
       <c r="N8" t="s">
         <v>34</v>
       </c>
+      <c r="O8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1516,6 +1560,12 @@
       <c r="N9" t="s">
         <v>34</v>
       </c>
+      <c r="O9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1637,6 +1687,12 @@
       <c r="N10" t="s">
         <v>34</v>
       </c>
+      <c r="O10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1758,6 +1814,12 @@
       <c r="N11" t="s">
         <v>34</v>
       </c>
+      <c r="O11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1879,6 +1941,12 @@
       <c r="N12" t="s">
         <v>34</v>
       </c>
+      <c r="O12" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2000,6 +2068,12 @@
       <c r="N13" t="s">
         <v>34</v>
       </c>
+      <c r="O13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2121,6 +2195,12 @@
       <c r="N14" t="s">
         <v>34</v>
       </c>
+      <c r="O14" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2242,6 +2322,12 @@
       <c r="N15" t="s">
         <v>34</v>
       </c>
+      <c r="O15" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2363,6 +2449,12 @@
       <c r="N16" t="s">
         <v>34</v>
       </c>
+      <c r="O16" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2484,6 +2576,12 @@
       <c r="N17" t="s">
         <v>34</v>
       </c>
+      <c r="O17" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2605,6 +2703,12 @@
       <c r="N18" t="s">
         <v>34</v>
       </c>
+      <c r="O18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2726,6 +2830,12 @@
       <c r="N19" t="s">
         <v>34</v>
       </c>
+      <c r="O19" t="s">
+        <v>34</v>
+      </c>
+      <c r="P19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2847,6 +2957,12 @@
       <c r="N20" t="s">
         <v>34</v>
       </c>
+      <c r="O20" t="s">
+        <v>34</v>
+      </c>
+      <c r="P20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2968,6 +3084,12 @@
       <c r="N21" t="s">
         <v>34</v>
       </c>
+      <c r="O21" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3089,6 +3211,12 @@
       <c r="N22" t="s">
         <v>34</v>
       </c>
+      <c r="O22" t="s">
+        <v>35</v>
+      </c>
+      <c r="P22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3210,6 +3338,12 @@
       <c r="N23" t="s">
         <v>34</v>
       </c>
+      <c r="O23" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3331,6 +3465,12 @@
       <c r="N24" t="s">
         <v>34</v>
       </c>
+      <c r="O24" t="s">
+        <v>34</v>
+      </c>
+      <c r="P24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3452,6 +3592,12 @@
       <c r="N25" t="s">
         <v>35</v>
       </c>
+      <c r="O25" t="s">
+        <v>34</v>
+      </c>
+      <c r="P25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3573,6 +3719,12 @@
       <c r="N26" t="s">
         <v>34</v>
       </c>
+      <c r="O26" t="s">
+        <v>34</v>
+      </c>
+      <c r="P26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3694,6 +3846,12 @@
       <c r="N27" t="s">
         <v>34</v>
       </c>
+      <c r="O27" t="s">
+        <v>34</v>
+      </c>
+      <c r="P27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3815,6 +3973,12 @@
       <c r="N28" t="s">
         <v>34</v>
       </c>
+      <c r="O28" t="s">
+        <v>34</v>
+      </c>
+      <c r="P28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3936,6 +4100,12 @@
       <c r="N29" t="s">
         <v>34</v>
       </c>
+      <c r="O29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4057,6 +4227,12 @@
       <c r="N30" t="s">
         <v>35</v>
       </c>
+      <c r="O30" t="s">
+        <v>34</v>
+      </c>
+      <c r="P30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4178,6 +4354,12 @@
       <c r="N31" t="s">
         <v>34</v>
       </c>
+      <c r="O31" t="s">
+        <v>34</v>
+      </c>
+      <c r="P31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4259,7 +4441,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 D3:AZ5 BB3:BB22 K3:L31 BE4:BJ10 BK4:DG31 M6:AZ10 D6:J31 M11:BA22 BC11:BJ22 M23:BJ31">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 K3:L31 BE4:BJ10 BK4:DG31 D6:J31 BC11:BJ22 M6:N31 D3:AZ3 D4:N5 P23:BJ31 P11:BA22 P4:AZ10 O4:O31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD67E8F-DD13-4EBF-91F3-3EA32B1A3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5B5CEC-9E9B-4472-81BD-A0C9A0F7D7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -576,7 +576,9 @@
       <c r="P1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
@@ -701,7 +703,9 @@
       <c r="P2" s="1">
         <v>46099</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="1">
+        <v>46101</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -802,6 +806,9 @@
         <v>34</v>
       </c>
       <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -931,6 +938,9 @@
       <c r="P4" t="s">
         <v>34</v>
       </c>
+      <c r="Q4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1058,6 +1068,9 @@
       <c r="P5" t="s">
         <v>34</v>
       </c>
+      <c r="Q5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1185,6 +1198,9 @@
       <c r="P6" t="s">
         <v>34</v>
       </c>
+      <c r="Q6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1312,6 +1328,9 @@
       <c r="P7" t="s">
         <v>34</v>
       </c>
+      <c r="Q7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1439,6 +1458,9 @@
       <c r="P8" t="s">
         <v>34</v>
       </c>
+      <c r="Q8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1566,6 +1588,9 @@
       <c r="P9" t="s">
         <v>34</v>
       </c>
+      <c r="Q9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1693,6 +1718,9 @@
       <c r="P10" t="s">
         <v>34</v>
       </c>
+      <c r="Q10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1820,6 +1848,9 @@
       <c r="P11" t="s">
         <v>34</v>
       </c>
+      <c r="Q11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1947,6 +1978,9 @@
       <c r="P12" t="s">
         <v>34</v>
       </c>
+      <c r="Q12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2074,6 +2108,9 @@
       <c r="P13" t="s">
         <v>34</v>
       </c>
+      <c r="Q13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2201,6 +2238,9 @@
       <c r="P14" t="s">
         <v>34</v>
       </c>
+      <c r="Q14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2328,6 +2368,9 @@
       <c r="P15" t="s">
         <v>34</v>
       </c>
+      <c r="Q15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2455,6 +2498,9 @@
       <c r="P16" t="s">
         <v>34</v>
       </c>
+      <c r="Q16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2582,6 +2628,9 @@
       <c r="P17" t="s">
         <v>34</v>
       </c>
+      <c r="Q17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2709,6 +2758,9 @@
       <c r="P18" t="s">
         <v>34</v>
       </c>
+      <c r="Q18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2836,6 +2888,9 @@
       <c r="P19" t="s">
         <v>34</v>
       </c>
+      <c r="Q19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2963,6 +3018,9 @@
       <c r="P20" t="s">
         <v>34</v>
       </c>
+      <c r="Q20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3090,6 +3148,9 @@
       <c r="P21" t="s">
         <v>34</v>
       </c>
+      <c r="Q21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3217,6 +3278,9 @@
       <c r="P22" t="s">
         <v>34</v>
       </c>
+      <c r="Q22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3344,6 +3408,9 @@
       <c r="P23" t="s">
         <v>34</v>
       </c>
+      <c r="Q23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3471,6 +3538,9 @@
       <c r="P24" t="s">
         <v>34</v>
       </c>
+      <c r="Q24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3598,6 +3668,9 @@
       <c r="P25" t="s">
         <v>34</v>
       </c>
+      <c r="Q25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3725,6 +3798,9 @@
       <c r="P26" t="s">
         <v>34</v>
       </c>
+      <c r="Q26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3852,6 +3928,9 @@
       <c r="P27" t="s">
         <v>34</v>
       </c>
+      <c r="Q27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3979,6 +4058,9 @@
       <c r="P28" t="s">
         <v>34</v>
       </c>
+      <c r="Q28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4106,6 +4188,9 @@
       <c r="P29" t="s">
         <v>34</v>
       </c>
+      <c r="Q29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4233,6 +4318,9 @@
       <c r="P30" t="s">
         <v>34</v>
       </c>
+      <c r="Q30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4360,6 +4448,9 @@
       <c r="P31" t="s">
         <v>34</v>
       </c>
+      <c r="Q31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4441,7 +4532,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 K3:L31 BE4:BJ10 BK4:DG31 D6:J31 BC11:BJ22 M6:N31 D3:AZ3 D4:N5 P23:BJ31 P11:BA22 P4:AZ10 O4:O31">
+  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 P4:AZ10 BE4:BJ10 O4:O31 BK4:DG31 D6:J31 M6:N31 P11:BA22 BC11:BJ22 P23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5B5CEC-9E9B-4472-81BD-A0C9A0F7D7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6995E1-38DB-4BDC-B64F-057A03BFE915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>P/2</t>
+  </si>
+  <si>
+    <t>4P</t>
   </si>
 </sst>
 </file>
@@ -526,17 +529,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -579,7 +582,9 @@
       <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -654,7 +659,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -706,7 +711,9 @@
       <c r="Q2" s="1">
         <v>46101</v>
       </c>
-      <c r="R2" s="1"/>
+      <c r="R2" s="1">
+        <v>46106</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -757,7 +764,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -809,6 +816,9 @@
         <v>34</v>
       </c>
       <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -887,7 +897,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -939,6 +949,9 @@
         <v>34</v>
       </c>
       <c r="Q4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1017,7 +1030,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1069,6 +1082,9 @@
         <v>34</v>
       </c>
       <c r="Q5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1147,7 +1163,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1199,6 +1215,9 @@
         <v>34</v>
       </c>
       <c r="Q6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1277,7 +1296,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1329,6 +1348,9 @@
         <v>34</v>
       </c>
       <c r="Q7" t="s">
+        <v>34</v>
+      </c>
+      <c r="R7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1407,7 +1429,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1459,6 +1481,9 @@
         <v>34</v>
       </c>
       <c r="Q8" t="s">
+        <v>34</v>
+      </c>
+      <c r="R8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1537,7 +1562,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1589,6 +1614,9 @@
         <v>34</v>
       </c>
       <c r="Q9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R9" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1667,7 +1695,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1719,6 +1747,9 @@
         <v>34</v>
       </c>
       <c r="Q10" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1797,7 +1828,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1849,6 +1880,9 @@
         <v>34</v>
       </c>
       <c r="Q11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -1927,7 +1961,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -1979,6 +2013,9 @@
         <v>34</v>
       </c>
       <c r="Q12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2057,7 +2094,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2109,6 +2146,9 @@
         <v>34</v>
       </c>
       <c r="Q13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2187,7 +2227,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2240,6 +2280,9 @@
       </c>
       <c r="Q14" t="s">
         <v>34</v>
+      </c>
+      <c r="R14" t="s">
+        <v>42</v>
       </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
@@ -2317,7 +2360,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2369,6 +2412,9 @@
         <v>34</v>
       </c>
       <c r="Q15" t="s">
+        <v>34</v>
+      </c>
+      <c r="R15" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2447,7 +2493,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2499,6 +2545,9 @@
         <v>34</v>
       </c>
       <c r="Q16" t="s">
+        <v>34</v>
+      </c>
+      <c r="R16" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2577,7 +2626,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2629,6 +2678,9 @@
         <v>34</v>
       </c>
       <c r="Q17" t="s">
+        <v>34</v>
+      </c>
+      <c r="R17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2707,7 +2759,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2759,6 +2811,9 @@
         <v>34</v>
       </c>
       <c r="Q18" t="s">
+        <v>34</v>
+      </c>
+      <c r="R18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2837,7 +2892,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2889,6 +2944,9 @@
         <v>34</v>
       </c>
       <c r="Q19" t="s">
+        <v>34</v>
+      </c>
+      <c r="R19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -2967,7 +3025,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3019,6 +3077,9 @@
         <v>34</v>
       </c>
       <c r="Q20" t="s">
+        <v>34</v>
+      </c>
+      <c r="R20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3097,7 +3158,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3150,6 +3211,9 @@
       </c>
       <c r="Q21" t="s">
         <v>34</v>
+      </c>
+      <c r="R21" t="s">
+        <v>42</v>
       </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
@@ -3227,7 +3291,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3279,6 +3343,9 @@
         <v>34</v>
       </c>
       <c r="Q22" t="s">
+        <v>34</v>
+      </c>
+      <c r="R22" t="s">
         <v>34</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3357,7 +3424,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3409,6 +3476,9 @@
         <v>34</v>
       </c>
       <c r="Q23" t="s">
+        <v>34</v>
+      </c>
+      <c r="R23" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3487,7 +3557,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3539,6 +3609,9 @@
         <v>34</v>
       </c>
       <c r="Q24" t="s">
+        <v>34</v>
+      </c>
+      <c r="R24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3617,7 +3690,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3669,6 +3742,9 @@
         <v>34</v>
       </c>
       <c r="Q25" t="s">
+        <v>34</v>
+      </c>
+      <c r="R25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3747,7 +3823,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3799,6 +3875,9 @@
         <v>34</v>
       </c>
       <c r="Q26" t="s">
+        <v>34</v>
+      </c>
+      <c r="R26" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3877,7 +3956,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3929,6 +4008,9 @@
         <v>34</v>
       </c>
       <c r="Q27" t="s">
+        <v>34</v>
+      </c>
+      <c r="R27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4007,7 +4089,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4059,6 +4141,9 @@
         <v>34</v>
       </c>
       <c r="Q28" t="s">
+        <v>34</v>
+      </c>
+      <c r="R28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4137,7 +4222,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4189,6 +4274,9 @@
         <v>34</v>
       </c>
       <c r="Q29" t="s">
+        <v>34</v>
+      </c>
+      <c r="R29" t="s">
         <v>34</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4267,7 +4355,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4320,6 +4408,9 @@
       </c>
       <c r="Q30" t="s">
         <v>34</v>
+      </c>
+      <c r="R30" t="s">
+        <v>35</v>
       </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
@@ -4397,7 +4488,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4450,6 +4541,9 @@
       </c>
       <c r="Q31" t="s">
         <v>34</v>
+      </c>
+      <c r="R31" t="s">
+        <v>35</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -4532,7 +4626,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 P4:AZ10 BE4:BJ10 O4:O31 BK4:DG31 D6:J31 M6:N31 P11:BA22 BC11:BJ22 P23:BJ31">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 S23:BJ31 S11:BA22 S4:AZ10 O4:R31 D3:AZ3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4545,14 +4639,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4560,147 +4654,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>31</v>
       </c>
@@ -4714,18 +4808,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -4733,7 +4827,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -4742,7 +4836,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -4751,7 +4845,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -4760,7 +4854,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -4769,13 +4863,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -4784,7 +4878,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -4793,7 +4887,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -4809,13 +4903,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -4824,7 +4918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -4833,7 +4927,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -4842,7 +4936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -4851,7 +4945,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -4860,7 +4954,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -4869,7 +4963,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -4878,7 +4972,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -4887,7 +4981,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -4896,7 +4990,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -4905,7 +4999,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -4914,7 +5008,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -4923,7 +5017,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -4932,25 +5026,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -4959,7 +5053,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -4968,7 +5062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -4977,7 +5071,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6995E1-38DB-4BDC-B64F-057A03BFE915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9ABDCE-EF42-413F-B5BF-20F86BE1FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -529,17 +529,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -585,7 +588,9 @@
       <c r="R1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -659,7 +664,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -714,7 +719,9 @@
       <c r="R2" s="1">
         <v>46106</v>
       </c>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1">
+        <v>46108</v>
+      </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -764,7 +771,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -819,6 +826,9 @@
         <v>34</v>
       </c>
       <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -897,7 +907,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -952,6 +962,9 @@
         <v>34</v>
       </c>
       <c r="R4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1030,7 +1043,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1085,6 +1098,9 @@
         <v>34</v>
       </c>
       <c r="R5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1163,7 +1179,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1218,6 +1234,9 @@
         <v>34</v>
       </c>
       <c r="R6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1296,7 +1315,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1351,6 +1370,9 @@
         <v>34</v>
       </c>
       <c r="R7" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1429,7 +1451,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1484,6 +1506,9 @@
         <v>34</v>
       </c>
       <c r="R8" t="s">
+        <v>34</v>
+      </c>
+      <c r="S8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1562,7 +1587,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1618,6 +1643,9 @@
       </c>
       <c r="R9" t="s">
         <v>34</v>
+      </c>
+      <c r="S9" t="s">
+        <v>35</v>
       </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
@@ -1695,7 +1723,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1750,6 +1778,9 @@
         <v>34</v>
       </c>
       <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1828,7 +1859,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1883,6 +1914,9 @@
         <v>34</v>
       </c>
       <c r="R11" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -1961,7 +1995,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2016,6 +2050,9 @@
         <v>34</v>
       </c>
       <c r="R12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2094,7 +2131,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2149,6 +2186,9 @@
         <v>34</v>
       </c>
       <c r="R13" t="s">
+        <v>34</v>
+      </c>
+      <c r="S13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2227,7 +2267,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2283,6 +2323,9 @@
       </c>
       <c r="R14" t="s">
         <v>42</v>
+      </c>
+      <c r="S14" t="s">
+        <v>35</v>
       </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
@@ -2360,7 +2403,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2415,6 +2458,9 @@
         <v>34</v>
       </c>
       <c r="R15" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2493,7 +2539,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2548,6 +2594,9 @@
         <v>34</v>
       </c>
       <c r="R16" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2626,7 +2675,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2681,6 +2730,9 @@
         <v>34</v>
       </c>
       <c r="R17" t="s">
+        <v>34</v>
+      </c>
+      <c r="S17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2759,7 +2811,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2814,6 +2866,9 @@
         <v>34</v>
       </c>
       <c r="R18" t="s">
+        <v>34</v>
+      </c>
+      <c r="S18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2892,7 +2947,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2947,6 +3002,9 @@
         <v>34</v>
       </c>
       <c r="R19" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3025,7 +3083,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3080,6 +3138,9 @@
         <v>34</v>
       </c>
       <c r="R20" t="s">
+        <v>34</v>
+      </c>
+      <c r="S20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3158,7 +3219,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3214,6 +3275,9 @@
       </c>
       <c r="R21" t="s">
         <v>42</v>
+      </c>
+      <c r="S21" t="s">
+        <v>34</v>
       </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
@@ -3291,7 +3355,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3346,6 +3410,9 @@
         <v>34</v>
       </c>
       <c r="R22" t="s">
+        <v>34</v>
+      </c>
+      <c r="S22" t="s">
         <v>34</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3424,7 +3491,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3480,6 +3547,9 @@
       </c>
       <c r="R23" t="s">
         <v>34</v>
+      </c>
+      <c r="S23" t="s">
+        <v>35</v>
       </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
@@ -3557,7 +3627,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3612,6 +3682,9 @@
         <v>34</v>
       </c>
       <c r="R24" t="s">
+        <v>34</v>
+      </c>
+      <c r="S24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3690,7 +3763,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3745,6 +3818,9 @@
         <v>34</v>
       </c>
       <c r="R25" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3823,7 +3899,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3878,6 +3954,9 @@
         <v>34</v>
       </c>
       <c r="R26" t="s">
+        <v>34</v>
+      </c>
+      <c r="S26" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3956,7 +4035,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4011,6 +4090,9 @@
         <v>34</v>
       </c>
       <c r="R27" t="s">
+        <v>34</v>
+      </c>
+      <c r="S27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4089,7 +4171,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4144,6 +4226,9 @@
         <v>34</v>
       </c>
       <c r="R28" t="s">
+        <v>34</v>
+      </c>
+      <c r="S28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4222,7 +4307,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4277,6 +4362,9 @@
         <v>34</v>
       </c>
       <c r="R29" t="s">
+        <v>34</v>
+      </c>
+      <c r="S29" t="s">
         <v>34</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4355,7 +4443,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4411,6 +4499,9 @@
       </c>
       <c r="R30" t="s">
         <v>35</v>
+      </c>
+      <c r="S30" t="s">
+        <v>34</v>
       </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
@@ -4488,7 +4579,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4544,6 +4635,9 @@
       </c>
       <c r="R31" t="s">
         <v>35</v>
+      </c>
+      <c r="S31" t="s">
+        <v>34</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -4626,7 +4720,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 S23:BJ31 S11:BA22 S4:AZ10 O4:R31 D3:AZ3">
+  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 S4:AZ10 BE4:BJ10 O4:R31 BK4:DG31 D6:J31 M6:N31 S11:BA22 BC11:BJ22 S23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4639,14 +4733,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4654,147 +4748,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>31</v>
       </c>
@@ -4808,18 +4902,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -4827,7 +4921,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -4836,7 +4930,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -4845,7 +4939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -4854,7 +4948,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -4863,13 +4957,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -4878,7 +4972,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -4887,7 +4981,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -4903,13 +4997,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -4918,7 +5012,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -4927,7 +5021,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -4936,7 +5030,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -4945,7 +5039,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -4954,7 +5048,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -4963,7 +5057,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -4972,7 +5066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -4981,7 +5075,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -4990,7 +5084,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -4999,7 +5093,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -5008,7 +5102,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -5017,7 +5111,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -5026,25 +5120,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -5053,7 +5147,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -5062,7 +5156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -5071,7 +5165,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9ABDCE-EF42-413F-B5BF-20F86BE1FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF36FA7-1449-451D-9443-140D0BA72A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -591,7 +591,9 @@
       <c r="S1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -722,7 +724,9 @@
       <c r="S2" s="1">
         <v>46108</v>
       </c>
-      <c r="T2" s="1"/>
+      <c r="T2" s="1">
+        <v>46113</v>
+      </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -829,6 +833,9 @@
         <v>34</v>
       </c>
       <c r="S3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -967,6 +974,9 @@
       <c r="S4" t="s">
         <v>34</v>
       </c>
+      <c r="T4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1103,6 +1113,9 @@
       <c r="S5" t="s">
         <v>34</v>
       </c>
+      <c r="T5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1239,6 +1252,9 @@
       <c r="S6" t="s">
         <v>34</v>
       </c>
+      <c r="T6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1375,6 +1391,9 @@
       <c r="S7" t="s">
         <v>34</v>
       </c>
+      <c r="T7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1511,6 +1530,9 @@
       <c r="S8" t="s">
         <v>34</v>
       </c>
+      <c r="T8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1647,6 +1669,9 @@
       <c r="S9" t="s">
         <v>35</v>
       </c>
+      <c r="T9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1783,6 +1808,9 @@
       <c r="S10" t="s">
         <v>34</v>
       </c>
+      <c r="T10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1919,6 +1947,9 @@
       <c r="S11" t="s">
         <v>34</v>
       </c>
+      <c r="T11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2055,6 +2086,9 @@
       <c r="S12" t="s">
         <v>34</v>
       </c>
+      <c r="T12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2191,6 +2225,9 @@
       <c r="S13" t="s">
         <v>34</v>
       </c>
+      <c r="T13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2327,6 +2364,9 @@
       <c r="S14" t="s">
         <v>35</v>
       </c>
+      <c r="T14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2463,6 +2503,9 @@
       <c r="S15" t="s">
         <v>34</v>
       </c>
+      <c r="T15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2599,6 +2642,9 @@
       <c r="S16" t="s">
         <v>34</v>
       </c>
+      <c r="T16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2735,6 +2781,9 @@
       <c r="S17" t="s">
         <v>34</v>
       </c>
+      <c r="T17" t="s">
+        <v>35</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2871,6 +2920,9 @@
       <c r="S18" t="s">
         <v>34</v>
       </c>
+      <c r="T18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3007,6 +3059,9 @@
       <c r="S19" t="s">
         <v>34</v>
       </c>
+      <c r="T19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3143,6 +3198,9 @@
       <c r="S20" t="s">
         <v>34</v>
       </c>
+      <c r="T20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3279,6 +3337,9 @@
       <c r="S21" t="s">
         <v>34</v>
       </c>
+      <c r="T21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3415,6 +3476,9 @@
       <c r="S22" t="s">
         <v>34</v>
       </c>
+      <c r="T22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3551,6 +3615,9 @@
       <c r="S23" t="s">
         <v>35</v>
       </c>
+      <c r="T23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3687,6 +3754,9 @@
       <c r="S24" t="s">
         <v>34</v>
       </c>
+      <c r="T24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3823,6 +3893,9 @@
       <c r="S25" t="s">
         <v>34</v>
       </c>
+      <c r="T25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3959,6 +4032,9 @@
       <c r="S26" t="s">
         <v>34</v>
       </c>
+      <c r="T26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4095,6 +4171,9 @@
       <c r="S27" t="s">
         <v>34</v>
       </c>
+      <c r="T27" t="s">
+        <v>35</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4231,6 +4310,9 @@
       <c r="S28" t="s">
         <v>34</v>
       </c>
+      <c r="T28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4367,6 +4449,9 @@
       <c r="S29" t="s">
         <v>34</v>
       </c>
+      <c r="T29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4503,6 +4588,9 @@
       <c r="S30" t="s">
         <v>34</v>
       </c>
+      <c r="T30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4639,6 +4727,9 @@
       <c r="S31" t="s">
         <v>34</v>
       </c>
+      <c r="T31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF36FA7-1449-451D-9443-140D0BA72A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64574C9-8B71-4E8C-A49C-0D818975AA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>4P</t>
+  </si>
+  <si>
+    <t>aniver</t>
+  </si>
+  <si>
+    <t>feriado</t>
   </si>
 </sst>
 </file>
@@ -594,9 +600,15 @@
       <c r="T1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
@@ -727,9 +739,15 @@
       <c r="T2" s="1">
         <v>46113</v>
       </c>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
+      <c r="U2" s="1">
+        <v>46084</v>
+      </c>
+      <c r="V2" s="1">
+        <v>46120</v>
+      </c>
+      <c r="W2" s="1">
+        <v>46122</v>
+      </c>
       <c r="X2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -836,6 +854,15 @@
         <v>34</v>
       </c>
       <c r="T3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -977,6 +1004,15 @@
       <c r="T4" t="s">
         <v>34</v>
       </c>
+      <c r="U4" t="s">
+        <v>44</v>
+      </c>
+      <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1116,6 +1152,15 @@
       <c r="T5" t="s">
         <v>34</v>
       </c>
+      <c r="U5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1255,6 +1300,15 @@
       <c r="T6" t="s">
         <v>34</v>
       </c>
+      <c r="U6" t="s">
+        <v>44</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1394,6 +1448,15 @@
       <c r="T7" t="s">
         <v>34</v>
       </c>
+      <c r="U7" t="s">
+        <v>44</v>
+      </c>
+      <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1533,6 +1596,15 @@
       <c r="T8" t="s">
         <v>34</v>
       </c>
+      <c r="U8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
+        <v>35</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1672,6 +1744,15 @@
       <c r="T9" t="s">
         <v>34</v>
       </c>
+      <c r="U9" t="s">
+        <v>44</v>
+      </c>
+      <c r="V9" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1811,6 +1892,15 @@
       <c r="T10" t="s">
         <v>34</v>
       </c>
+      <c r="U10" t="s">
+        <v>44</v>
+      </c>
+      <c r="V10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1950,6 +2040,15 @@
       <c r="T11" t="s">
         <v>34</v>
       </c>
+      <c r="U11" t="s">
+        <v>44</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2089,6 +2188,15 @@
       <c r="T12" t="s">
         <v>34</v>
       </c>
+      <c r="U12" t="s">
+        <v>44</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2228,6 +2336,15 @@
       <c r="T13" t="s">
         <v>34</v>
       </c>
+      <c r="U13" t="s">
+        <v>44</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2367,6 +2484,15 @@
       <c r="T14" t="s">
         <v>34</v>
       </c>
+      <c r="U14" t="s">
+        <v>44</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2506,6 +2632,15 @@
       <c r="T15" t="s">
         <v>34</v>
       </c>
+      <c r="U15" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2645,6 +2780,15 @@
       <c r="T16" t="s">
         <v>34</v>
       </c>
+      <c r="U16" t="s">
+        <v>44</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2784,6 +2928,15 @@
       <c r="T17" t="s">
         <v>35</v>
       </c>
+      <c r="U17" t="s">
+        <v>44</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2923,6 +3076,15 @@
       <c r="T18" t="s">
         <v>34</v>
       </c>
+      <c r="U18" t="s">
+        <v>44</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3062,6 +3224,15 @@
       <c r="T19" t="s">
         <v>34</v>
       </c>
+      <c r="U19" t="s">
+        <v>44</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3201,6 +3372,15 @@
       <c r="T20" t="s">
         <v>34</v>
       </c>
+      <c r="U20" t="s">
+        <v>44</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3340,6 +3520,15 @@
       <c r="T21" t="s">
         <v>34</v>
       </c>
+      <c r="U21" t="s">
+        <v>44</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3479,6 +3668,15 @@
       <c r="T22" t="s">
         <v>34</v>
       </c>
+      <c r="U22" t="s">
+        <v>44</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3618,6 +3816,15 @@
       <c r="T23" t="s">
         <v>34</v>
       </c>
+      <c r="U23" t="s">
+        <v>44</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3757,6 +3964,15 @@
       <c r="T24" t="s">
         <v>34</v>
       </c>
+      <c r="U24" t="s">
+        <v>44</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3896,6 +4112,15 @@
       <c r="T25" t="s">
         <v>34</v>
       </c>
+      <c r="U25" t="s">
+        <v>44</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>35</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4035,6 +4260,15 @@
       <c r="T26" t="s">
         <v>34</v>
       </c>
+      <c r="U26" t="s">
+        <v>44</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4174,6 +4408,15 @@
       <c r="T27" t="s">
         <v>35</v>
       </c>
+      <c r="U27" t="s">
+        <v>44</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4313,6 +4556,15 @@
       <c r="T28" t="s">
         <v>34</v>
       </c>
+      <c r="U28" t="s">
+        <v>44</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4452,6 +4704,15 @@
       <c r="T29" t="s">
         <v>34</v>
       </c>
+      <c r="U29" t="s">
+        <v>44</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4591,6 +4852,15 @@
       <c r="T30" t="s">
         <v>34</v>
       </c>
+      <c r="U30" t="s">
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4730,6 +5000,15 @@
       <c r="T31" t="s">
         <v>34</v>
       </c>
+      <c r="U31" t="s">
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4811,7 +5090,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 S4:AZ10 BE4:BJ10 O4:R31 BK4:DG31 D6:J31 M6:N31 S11:BA22 BC11:BJ22 S23:BJ31">
+  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 W23:BJ31 W11:BA22 W4:AZ10 O4:V31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64574C9-8B71-4E8C-A49C-0D818975AA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411A67C9-9C76-4889-AC4F-3838F98741BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -609,8 +609,12 @@
       <c r="W1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
@@ -748,7 +752,12 @@
       <c r="W2" s="1">
         <v>46122</v>
       </c>
-      <c r="X2" s="1"/>
+      <c r="X2" s="1">
+        <v>46127</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>46129</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -863,6 +872,12 @@
         <v>43</v>
       </c>
       <c r="W3" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1013,6 +1028,12 @@
       <c r="W4" t="s">
         <v>34</v>
       </c>
+      <c r="X4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1161,6 +1182,12 @@
       <c r="W5" t="s">
         <v>34</v>
       </c>
+      <c r="X5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1309,6 +1336,12 @@
       <c r="W6" t="s">
         <v>34</v>
       </c>
+      <c r="X6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1457,6 +1490,12 @@
       <c r="W7" t="s">
         <v>34</v>
       </c>
+      <c r="X7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1605,6 +1644,12 @@
       <c r="W8" t="s">
         <v>35</v>
       </c>
+      <c r="X8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1753,6 +1798,12 @@
       <c r="W9" t="s">
         <v>34</v>
       </c>
+      <c r="X9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>35</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1901,6 +1952,12 @@
       <c r="W10" t="s">
         <v>34</v>
       </c>
+      <c r="X10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2049,6 +2106,12 @@
       <c r="W11" t="s">
         <v>34</v>
       </c>
+      <c r="X11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2197,6 +2260,12 @@
       <c r="W12" t="s">
         <v>34</v>
       </c>
+      <c r="X12" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2345,6 +2414,12 @@
       <c r="W13" t="s">
         <v>34</v>
       </c>
+      <c r="X13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2493,6 +2568,12 @@
       <c r="W14" t="s">
         <v>34</v>
       </c>
+      <c r="X14" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2641,6 +2722,12 @@
       <c r="W15" t="s">
         <v>34</v>
       </c>
+      <c r="X15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2789,6 +2876,12 @@
       <c r="W16" t="s">
         <v>34</v>
       </c>
+      <c r="X16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2937,6 +3030,12 @@
       <c r="W17" t="s">
         <v>34</v>
       </c>
+      <c r="X17" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3085,6 +3184,12 @@
       <c r="W18" t="s">
         <v>34</v>
       </c>
+      <c r="X18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>35</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3233,6 +3338,12 @@
       <c r="W19" t="s">
         <v>34</v>
       </c>
+      <c r="X19" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3381,6 +3492,12 @@
       <c r="W20" t="s">
         <v>34</v>
       </c>
+      <c r="X20" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3529,6 +3646,12 @@
       <c r="W21" t="s">
         <v>34</v>
       </c>
+      <c r="X21" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3677,6 +3800,12 @@
       <c r="W22" t="s">
         <v>34</v>
       </c>
+      <c r="X22" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3825,6 +3954,12 @@
       <c r="W23" t="s">
         <v>34</v>
       </c>
+      <c r="X23" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3973,6 +4108,12 @@
       <c r="W24" t="s">
         <v>34</v>
       </c>
+      <c r="X24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4121,6 +4262,12 @@
       <c r="W25" t="s">
         <v>35</v>
       </c>
+      <c r="X25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4269,6 +4416,12 @@
       <c r="W26" t="s">
         <v>34</v>
       </c>
+      <c r="X26" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4417,6 +4570,12 @@
       <c r="W27" t="s">
         <v>34</v>
       </c>
+      <c r="X27" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4565,6 +4724,12 @@
       <c r="W28" t="s">
         <v>34</v>
       </c>
+      <c r="X28" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4713,6 +4878,12 @@
       <c r="W29" t="s">
         <v>34</v>
       </c>
+      <c r="X29" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4861,6 +5032,12 @@
       <c r="W30" t="s">
         <v>34</v>
       </c>
+      <c r="X30" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5009,6 +5186,12 @@
       <c r="W31" t="s">
         <v>34</v>
       </c>
+      <c r="X31" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5090,7 +5273,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 W23:BJ31 W11:BA22 W4:AZ10 O4:V31">
+  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 W4:AZ10 BE4:BJ10 O4:V31 BK4:DG31 D6:J31 M6:N31 W11:BA22 BC11:BJ22 W23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411A67C9-9C76-4889-AC4F-3838F98741BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E62B98-A16B-48C9-9DB0-4CFE7EE0758D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -543,7 +543,9 @@
     <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="50" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.6640625" customWidth="1"/>
+    <col min="26" max="26" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="50" width="7.6640625" customWidth="1"/>
     <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
@@ -615,7 +617,9 @@
       <c r="Y1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -758,6 +762,9 @@
       <c r="Y2" s="1">
         <v>46129</v>
       </c>
+      <c r="Z2" s="1">
+        <v>46134</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -878,6 +885,9 @@
         <v>34</v>
       </c>
       <c r="Y3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1034,6 +1044,9 @@
       <c r="Y4" t="s">
         <v>34</v>
       </c>
+      <c r="Z4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1188,6 +1201,9 @@
       <c r="Y5" t="s">
         <v>34</v>
       </c>
+      <c r="Z5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1342,6 +1358,9 @@
       <c r="Y6" t="s">
         <v>34</v>
       </c>
+      <c r="Z6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1496,6 +1515,9 @@
       <c r="Y7" t="s">
         <v>34</v>
       </c>
+      <c r="Z7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1650,6 +1672,9 @@
       <c r="Y8" t="s">
         <v>34</v>
       </c>
+      <c r="Z8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1804,6 +1829,9 @@
       <c r="Y9" t="s">
         <v>35</v>
       </c>
+      <c r="Z9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1958,6 +1986,9 @@
       <c r="Y10" t="s">
         <v>34</v>
       </c>
+      <c r="Z10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2112,6 +2143,9 @@
       <c r="Y11" t="s">
         <v>34</v>
       </c>
+      <c r="Z11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2266,6 +2300,9 @@
       <c r="Y12" t="s">
         <v>34</v>
       </c>
+      <c r="Z12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2420,6 +2457,9 @@
       <c r="Y13" t="s">
         <v>34</v>
       </c>
+      <c r="Z13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2574,6 +2614,9 @@
       <c r="Y14" t="s">
         <v>34</v>
       </c>
+      <c r="Z14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2728,6 +2771,9 @@
       <c r="Y15" t="s">
         <v>34</v>
       </c>
+      <c r="Z15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2882,6 +2928,9 @@
       <c r="Y16" t="s">
         <v>34</v>
       </c>
+      <c r="Z16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3036,6 +3085,9 @@
       <c r="Y17" t="s">
         <v>34</v>
       </c>
+      <c r="Z17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3190,6 +3242,9 @@
       <c r="Y18" t="s">
         <v>35</v>
       </c>
+      <c r="Z18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3344,6 +3399,9 @@
       <c r="Y19" t="s">
         <v>34</v>
       </c>
+      <c r="Z19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3498,6 +3556,9 @@
       <c r="Y20" t="s">
         <v>34</v>
       </c>
+      <c r="Z20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3652,6 +3713,9 @@
       <c r="Y21" t="s">
         <v>34</v>
       </c>
+      <c r="Z21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3806,6 +3870,9 @@
       <c r="Y22" t="s">
         <v>34</v>
       </c>
+      <c r="Z22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3960,6 +4027,9 @@
       <c r="Y23" t="s">
         <v>34</v>
       </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4114,6 +4184,9 @@
       <c r="Y24" t="s">
         <v>34</v>
       </c>
+      <c r="Z24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4268,6 +4341,9 @@
       <c r="Y25" t="s">
         <v>34</v>
       </c>
+      <c r="Z25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4422,6 +4498,9 @@
       <c r="Y26" t="s">
         <v>34</v>
       </c>
+      <c r="Z26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4576,6 +4655,9 @@
       <c r="Y27" t="s">
         <v>34</v>
       </c>
+      <c r="Z27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4730,6 +4812,9 @@
       <c r="Y28" t="s">
         <v>34</v>
       </c>
+      <c r="Z28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4884,6 +4969,9 @@
       <c r="Y29" t="s">
         <v>34</v>
       </c>
+      <c r="Z29" t="s">
+        <v>35</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5038,6 +5126,9 @@
       <c r="Y30" t="s">
         <v>34</v>
       </c>
+      <c r="Z30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5192,6 +5283,9 @@
       <c r="Y31" t="s">
         <v>34</v>
       </c>
+      <c r="Z31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E62B98-A16B-48C9-9DB0-4CFE7EE0758D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B863D56-0B3E-41AC-99D1-6E78FFF11FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -544,8 +544,8 @@
     <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="25" width="7.6640625" customWidth="1"/>
-    <col min="26" max="26" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="50" width="7.6640625" customWidth="1"/>
+    <col min="26" max="27" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="50" width="7.6640625" customWidth="1"/>
     <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
@@ -620,7 +620,9 @@
       <c r="Z1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
@@ -765,6 +767,9 @@
       <c r="Z2" s="1">
         <v>46134</v>
       </c>
+      <c r="AA2" s="1">
+        <v>46136</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -888,6 +893,9 @@
         <v>34</v>
       </c>
       <c r="Z3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1047,6 +1055,9 @@
       <c r="Z4" t="s">
         <v>34</v>
       </c>
+      <c r="AA4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1204,6 +1215,9 @@
       <c r="Z5" t="s">
         <v>34</v>
       </c>
+      <c r="AA5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1361,6 +1375,9 @@
       <c r="Z6" t="s">
         <v>34</v>
       </c>
+      <c r="AA6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1518,6 +1535,9 @@
       <c r="Z7" t="s">
         <v>34</v>
       </c>
+      <c r="AA7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1675,6 +1695,9 @@
       <c r="Z8" t="s">
         <v>34</v>
       </c>
+      <c r="AA8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1832,6 +1855,9 @@
       <c r="Z9" t="s">
         <v>34</v>
       </c>
+      <c r="AA9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1989,6 +2015,9 @@
       <c r="Z10" t="s">
         <v>34</v>
       </c>
+      <c r="AA10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2146,6 +2175,9 @@
       <c r="Z11" t="s">
         <v>34</v>
       </c>
+      <c r="AA11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2303,6 +2335,9 @@
       <c r="Z12" t="s">
         <v>34</v>
       </c>
+      <c r="AA12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2460,6 +2495,9 @@
       <c r="Z13" t="s">
         <v>34</v>
       </c>
+      <c r="AA13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2617,6 +2655,9 @@
       <c r="Z14" t="s">
         <v>34</v>
       </c>
+      <c r="AA14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2774,6 +2815,9 @@
       <c r="Z15" t="s">
         <v>34</v>
       </c>
+      <c r="AA15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2931,6 +2975,9 @@
       <c r="Z16" t="s">
         <v>34</v>
       </c>
+      <c r="AA16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3088,6 +3135,9 @@
       <c r="Z17" t="s">
         <v>34</v>
       </c>
+      <c r="AA17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3245,6 +3295,9 @@
       <c r="Z18" t="s">
         <v>34</v>
       </c>
+      <c r="AA18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3402,6 +3455,9 @@
       <c r="Z19" t="s">
         <v>34</v>
       </c>
+      <c r="AA19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3559,6 +3615,9 @@
       <c r="Z20" t="s">
         <v>34</v>
       </c>
+      <c r="AA20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3716,6 +3775,9 @@
       <c r="Z21" t="s">
         <v>34</v>
       </c>
+      <c r="AA21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3873,6 +3935,9 @@
       <c r="Z22" t="s">
         <v>34</v>
       </c>
+      <c r="AA22" t="s">
+        <v>35</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4030,6 +4095,9 @@
       <c r="Z23" t="s">
         <v>34</v>
       </c>
+      <c r="AA23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4187,6 +4255,9 @@
       <c r="Z24" t="s">
         <v>34</v>
       </c>
+      <c r="AA24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4344,6 +4415,9 @@
       <c r="Z25" t="s">
         <v>34</v>
       </c>
+      <c r="AA25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4501,6 +4575,9 @@
       <c r="Z26" t="s">
         <v>34</v>
       </c>
+      <c r="AA26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4658,6 +4735,9 @@
       <c r="Z27" t="s">
         <v>34</v>
       </c>
+      <c r="AA27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4815,6 +4895,9 @@
       <c r="Z28" t="s">
         <v>34</v>
       </c>
+      <c r="AA28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4972,6 +5055,9 @@
       <c r="Z29" t="s">
         <v>35</v>
       </c>
+      <c r="AA29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5129,6 +5215,9 @@
       <c r="Z30" t="s">
         <v>34</v>
       </c>
+      <c r="AA30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5286,6 +5375,9 @@
       <c r="Z31" t="s">
         <v>34</v>
       </c>
+      <c r="AA31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B863D56-0B3E-41AC-99D1-6E78FFF11FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60BE0B3E-535C-4B83-BCD2-EADE68699AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>feriado</t>
+  </si>
+  <si>
+    <t>4P/4F</t>
   </si>
 </sst>
 </file>
@@ -535,22 +538,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.6640625" customWidth="1"/>
-    <col min="26" max="27" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -688,7 +690,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -814,7 +816,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -974,7 +976,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1134,7 +1136,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1294,7 +1296,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1454,7 +1456,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1614,7 +1616,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1774,7 +1776,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1934,7 +1936,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -2094,7 +2096,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -2254,7 +2256,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2414,7 +2416,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2574,7 +2576,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2734,7 +2736,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2894,7 +2896,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2976,7 +2978,7 @@
         <v>34</v>
       </c>
       <c r="AA16" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -3054,7 +3056,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -3214,7 +3216,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -3374,7 +3376,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3534,7 +3536,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3694,7 +3696,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3854,7 +3856,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -4014,7 +4016,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -4174,7 +4176,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -4334,7 +4336,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -4494,7 +4496,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -4654,7 +4656,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4814,7 +4816,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4974,7 +4976,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -5134,7 +5136,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -5294,7 +5296,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -5472,14 +5474,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5487,147 +5489,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>31</v>
       </c>
@@ -5641,18 +5643,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -5660,7 +5662,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -5669,7 +5671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -5678,7 +5680,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -5687,7 +5689,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -5696,13 +5698,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -5711,7 +5713,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -5720,7 +5722,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -5736,13 +5738,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -5751,7 +5753,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -5760,7 +5762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -5769,7 +5771,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -5778,7 +5780,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -5787,7 +5789,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -5796,7 +5798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -5805,7 +5807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -5814,7 +5816,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -5823,7 +5825,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -5832,7 +5834,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -5841,7 +5843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -5850,7 +5852,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -5859,25 +5861,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -5886,7 +5888,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -5895,7 +5897,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -5904,7 +5906,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60BE0B3E-535C-4B83-BCD2-EADE68699AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A1F9C9-A142-4A95-BF85-F51F3B8C4906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -538,21 +538,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.7109375" customWidth="1"/>
+    <col min="20" max="25" width="7.6640625" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="28" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -625,7 +625,9 @@
       <c r="AA1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="1"/>
+      <c r="AB1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -690,7 +692,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -772,6 +774,10 @@
       <c r="AA2" s="1">
         <v>46136</v>
       </c>
+      <c r="AB2" s="1">
+        <v>46141</v>
+      </c>
+      <c r="AC2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -816,7 +822,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -898,6 +904,9 @@
         <v>34</v>
       </c>
       <c r="AA3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -976,7 +985,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1058,6 +1067,9 @@
         <v>34</v>
       </c>
       <c r="AA4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1136,7 +1148,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1218,6 +1230,9 @@
         <v>34</v>
       </c>
       <c r="AA5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1296,7 +1311,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1378,6 +1393,9 @@
         <v>34</v>
       </c>
       <c r="AA6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1456,7 +1474,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1538,6 +1556,9 @@
         <v>34</v>
       </c>
       <c r="AA7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1616,7 +1637,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1698,6 +1719,9 @@
         <v>34</v>
       </c>
       <c r="AA8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1776,7 +1800,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1858,6 +1882,9 @@
         <v>34</v>
       </c>
       <c r="AA9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB9" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1936,7 +1963,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -2018,6 +2045,9 @@
         <v>34</v>
       </c>
       <c r="AA10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2096,7 +2126,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -2178,6 +2208,9 @@
         <v>34</v>
       </c>
       <c r="AA11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2256,7 +2289,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2338,6 +2371,9 @@
         <v>34</v>
       </c>
       <c r="AA12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2416,7 +2452,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2498,6 +2534,9 @@
         <v>34</v>
       </c>
       <c r="AA13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2576,7 +2615,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2658,6 +2697,9 @@
         <v>34</v>
       </c>
       <c r="AA14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB14" t="s">
         <v>34</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2736,7 +2778,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2818,6 +2860,9 @@
         <v>34</v>
       </c>
       <c r="AA15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2896,7 +2941,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2979,6 +3024,9 @@
       </c>
       <c r="AA16" t="s">
         <v>45</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>34</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -3056,7 +3104,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -3138,6 +3186,9 @@
         <v>34</v>
       </c>
       <c r="AA17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3216,7 +3267,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -3298,6 +3349,9 @@
         <v>34</v>
       </c>
       <c r="AA18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3376,7 +3430,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3458,6 +3512,9 @@
         <v>34</v>
       </c>
       <c r="AA19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3536,7 +3593,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3618,6 +3675,9 @@
         <v>34</v>
       </c>
       <c r="AA20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3696,7 +3756,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3778,6 +3838,9 @@
         <v>34</v>
       </c>
       <c r="AA21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21" t="s">
         <v>34</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3856,7 +3919,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3939,6 +4002,9 @@
       </c>
       <c r="AA22" t="s">
         <v>35</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>34</v>
       </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
@@ -4016,7 +4082,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -4098,6 +4164,9 @@
         <v>34</v>
       </c>
       <c r="AA23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4176,7 +4245,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -4258,6 +4327,9 @@
         <v>34</v>
       </c>
       <c r="AA24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4336,7 +4408,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -4418,6 +4490,9 @@
         <v>34</v>
       </c>
       <c r="AA25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4496,7 +4571,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -4578,6 +4653,9 @@
         <v>34</v>
       </c>
       <c r="AA26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB26" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4656,7 +4734,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4738,6 +4816,9 @@
         <v>34</v>
       </c>
       <c r="AA27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4816,7 +4897,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4898,6 +4979,9 @@
         <v>34</v>
       </c>
       <c r="AA28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4976,7 +5060,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -5058,6 +5142,9 @@
         <v>35</v>
       </c>
       <c r="AA29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB29" t="s">
         <v>34</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5136,7 +5223,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -5218,6 +5305,9 @@
         <v>34</v>
       </c>
       <c r="AA30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30" t="s">
         <v>34</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5296,7 +5386,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -5378,6 +5468,9 @@
         <v>34</v>
       </c>
       <c r="AA31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB31" t="s">
         <v>34</v>
       </c>
       <c r="AU31" s="2"/>
@@ -5474,14 +5567,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5489,147 +5582,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>31</v>
       </c>
@@ -5643,18 +5736,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -5662,7 +5755,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -5671,7 +5764,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -5680,7 +5773,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -5689,7 +5782,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -5698,13 +5791,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -5713,7 +5806,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -5722,7 +5815,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -5738,13 +5831,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -5753,7 +5846,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -5762,7 +5855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -5771,7 +5864,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -5780,7 +5873,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -5789,7 +5882,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -5798,7 +5891,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -5807,7 +5900,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -5816,7 +5909,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -5825,7 +5918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -5834,7 +5927,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -5843,7 +5936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -5852,7 +5945,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -5861,25 +5954,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -5888,7 +5981,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -5897,7 +5990,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -5906,7 +5999,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A1F9C9-A142-4A95-BF85-F51F3B8C4906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BC68A0-6D7A-4FA4-AD3E-DE946CB89734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -628,9 +628,15 @@
       <c r="AB1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
+      <c r="AC1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
@@ -777,7 +783,15 @@
       <c r="AB2" s="1">
         <v>46141</v>
       </c>
-      <c r="AC2" s="1"/>
+      <c r="AC2" s="1">
+        <v>46143</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>46148</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>46150</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -907,6 +921,12 @@
         <v>34</v>
       </c>
       <c r="AB3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1072,6 +1092,12 @@
       <c r="AB4" t="s">
         <v>34</v>
       </c>
+      <c r="AC4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1235,6 +1261,12 @@
       <c r="AB5" t="s">
         <v>34</v>
       </c>
+      <c r="AC5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1398,6 +1430,12 @@
       <c r="AB6" t="s">
         <v>34</v>
       </c>
+      <c r="AC6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1561,6 +1599,12 @@
       <c r="AB7" t="s">
         <v>34</v>
       </c>
+      <c r="AC7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1724,6 +1768,12 @@
       <c r="AB8" t="s">
         <v>34</v>
       </c>
+      <c r="AC8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1887,6 +1937,12 @@
       <c r="AB9" t="s">
         <v>34</v>
       </c>
+      <c r="AC9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2050,6 +2106,12 @@
       <c r="AB10" t="s">
         <v>34</v>
       </c>
+      <c r="AC10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2213,6 +2275,12 @@
       <c r="AB11" t="s">
         <v>34</v>
       </c>
+      <c r="AC11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2376,6 +2444,12 @@
       <c r="AB12" t="s">
         <v>34</v>
       </c>
+      <c r="AC12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2539,6 +2613,12 @@
       <c r="AB13" t="s">
         <v>34</v>
       </c>
+      <c r="AC13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2702,6 +2782,12 @@
       <c r="AB14" t="s">
         <v>34</v>
       </c>
+      <c r="AC14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2865,6 +2951,12 @@
       <c r="AB15" t="s">
         <v>34</v>
       </c>
+      <c r="AC15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3028,6 +3120,12 @@
       <c r="AB16" t="s">
         <v>34</v>
       </c>
+      <c r="AC16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3191,6 +3289,12 @@
       <c r="AB17" t="s">
         <v>34</v>
       </c>
+      <c r="AC17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3354,6 +3458,12 @@
       <c r="AB18" t="s">
         <v>34</v>
       </c>
+      <c r="AC18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3517,6 +3627,12 @@
       <c r="AB19" t="s">
         <v>34</v>
       </c>
+      <c r="AC19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3680,6 +3796,12 @@
       <c r="AB20" t="s">
         <v>34</v>
       </c>
+      <c r="AC20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3843,6 +3965,12 @@
       <c r="AB21" t="s">
         <v>34</v>
       </c>
+      <c r="AC21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4006,6 +4134,12 @@
       <c r="AB22" t="s">
         <v>34</v>
       </c>
+      <c r="AC22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4169,6 +4303,12 @@
       <c r="AB23" t="s">
         <v>34</v>
       </c>
+      <c r="AC23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4332,6 +4472,12 @@
       <c r="AB24" t="s">
         <v>34</v>
       </c>
+      <c r="AC24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4495,6 +4641,12 @@
       <c r="AB25" t="s">
         <v>34</v>
       </c>
+      <c r="AC25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4658,6 +4810,12 @@
       <c r="AB26" t="s">
         <v>34</v>
       </c>
+      <c r="AC26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4821,6 +4979,12 @@
       <c r="AB27" t="s">
         <v>34</v>
       </c>
+      <c r="AC27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4984,6 +5148,12 @@
       <c r="AB28" t="s">
         <v>34</v>
       </c>
+      <c r="AC28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5147,6 +5317,12 @@
       <c r="AB29" t="s">
         <v>34</v>
       </c>
+      <c r="AC29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5310,6 +5486,12 @@
       <c r="AB30" t="s">
         <v>34</v>
       </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5473,6 +5655,12 @@
       <c r="AB31" t="s">
         <v>34</v>
       </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5554,7 +5742,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AZ3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 W4:AZ10 BE4:BJ10 O4:V31 BK4:DG31 D6:J31 M6:N31 W11:BA22 BC11:BJ22 W23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 O4:AB31 AD23:BJ31 AD11:BA22 AD3:AZ10 AC3:AC31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BC68A0-6D7A-4FA4-AD3E-DE946CB89734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A363D187-0C59-47A0-B87E-8B9DD2974AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -637,8 +637,12 @@
       <c r="AE1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
+      <c r="AF1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
@@ -792,6 +796,12 @@
       <c r="AE2" s="1">
         <v>46150</v>
       </c>
+      <c r="AF2" s="1">
+        <v>46155</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>46157</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -927,6 +937,9 @@
         <v>44</v>
       </c>
       <c r="AD3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1098,6 +1111,9 @@
       <c r="AD4" t="s">
         <v>34</v>
       </c>
+      <c r="AE4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1267,6 +1283,9 @@
       <c r="AD5" t="s">
         <v>34</v>
       </c>
+      <c r="AE5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1436,6 +1455,9 @@
       <c r="AD6" t="s">
         <v>34</v>
       </c>
+      <c r="AE6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1605,6 +1627,9 @@
       <c r="AD7" t="s">
         <v>34</v>
       </c>
+      <c r="AE7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1774,6 +1799,9 @@
       <c r="AD8" t="s">
         <v>34</v>
       </c>
+      <c r="AE8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1943,6 +1971,9 @@
       <c r="AD9" t="s">
         <v>34</v>
       </c>
+      <c r="AE9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2112,6 +2143,9 @@
       <c r="AD10" t="s">
         <v>34</v>
       </c>
+      <c r="AE10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2281,6 +2315,9 @@
       <c r="AD11" t="s">
         <v>34</v>
       </c>
+      <c r="AE11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2450,6 +2487,9 @@
       <c r="AD12" t="s">
         <v>34</v>
       </c>
+      <c r="AE12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2619,6 +2659,9 @@
       <c r="AD13" t="s">
         <v>34</v>
       </c>
+      <c r="AE13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2788,6 +2831,9 @@
       <c r="AD14" t="s">
         <v>34</v>
       </c>
+      <c r="AE14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2957,6 +3003,9 @@
       <c r="AD15" t="s">
         <v>34</v>
       </c>
+      <c r="AE15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3126,6 +3175,9 @@
       <c r="AD16" t="s">
         <v>34</v>
       </c>
+      <c r="AE16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3295,6 +3347,9 @@
       <c r="AD17" t="s">
         <v>34</v>
       </c>
+      <c r="AE17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3464,6 +3519,9 @@
       <c r="AD18" t="s">
         <v>34</v>
       </c>
+      <c r="AE18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3633,6 +3691,9 @@
       <c r="AD19" t="s">
         <v>34</v>
       </c>
+      <c r="AE19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3802,6 +3863,9 @@
       <c r="AD20" t="s">
         <v>34</v>
       </c>
+      <c r="AE20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3971,6 +4035,9 @@
       <c r="AD21" t="s">
         <v>34</v>
       </c>
+      <c r="AE21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4140,6 +4207,9 @@
       <c r="AD22" t="s">
         <v>34</v>
       </c>
+      <c r="AE22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4309,6 +4379,9 @@
       <c r="AD23" t="s">
         <v>34</v>
       </c>
+      <c r="AE23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4478,6 +4551,9 @@
       <c r="AD24" t="s">
         <v>34</v>
       </c>
+      <c r="AE24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4647,6 +4723,9 @@
       <c r="AD25" t="s">
         <v>34</v>
       </c>
+      <c r="AE25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4816,6 +4895,9 @@
       <c r="AD26" t="s">
         <v>34</v>
       </c>
+      <c r="AE26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4985,6 +5067,9 @@
       <c r="AD27" t="s">
         <v>34</v>
       </c>
+      <c r="AE27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5154,6 +5239,9 @@
       <c r="AD28" t="s">
         <v>34</v>
       </c>
+      <c r="AE28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -5323,6 +5411,9 @@
       <c r="AD29" t="s">
         <v>34</v>
       </c>
+      <c r="AE29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5492,6 +5583,9 @@
       <c r="AD30" t="s">
         <v>34</v>
       </c>
+      <c r="AE30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5661,6 +5755,9 @@
       <c r="AD31" t="s">
         <v>34</v>
       </c>
+      <c r="AE31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -5742,7 +5839,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 O4:AB31 AD23:BJ31 AD11:BA22 AD3:AZ10 AC3:AC31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AF23:BJ31 AF11:BA22 AF3:AZ10 AC3:AE31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A363D187-0C59-47A0-B87E-8B9DD2974AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDB1864-1A8A-4F98-A756-B14DE607312F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -180,7 +180,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,16 +214,309 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -231,12 +524,160 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -245,10 +686,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="43">
+    <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase2" xfId="24" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase3" xfId="28" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase4" xfId="32" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase5" xfId="36" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase1" xfId="21" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase2" xfId="25" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase3" xfId="29" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase4" xfId="33" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase5" xfId="37" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase1" xfId="22" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase2" xfId="26" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase3" xfId="30" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase4" xfId="34" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase5" xfId="38" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase6" xfId="42" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bom" xfId="7" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="12" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Célula de Verificação" xfId="14" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Célula Vinculada" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Ênfase1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Ênfase2" xfId="23" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Ênfase3" xfId="27" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Ênfase4" xfId="31" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Ênfase5" xfId="35" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Ênfase6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="10" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Nota" xfId="16" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Ruim" xfId="8" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Saída" xfId="11" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de Aviso" xfId="15" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto Explicativo" xfId="17" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 1" xfId="3" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -540,7 +1023,7 @@
   <dimension ref="A1:DS31"/>
   <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
     <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
@@ -849,7 +1332,7 @@
     <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
-        <v>0</v>
+        <v>25130313</v>
       </c>
       <c r="B3" t="str">
         <f>alunos!B2</f>
@@ -940,6 +1423,12 @@
         <v>34</v>
       </c>
       <c r="AE3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1021,7 +1510,7 @@
     <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
-        <v>0</v>
+        <v>25129077</v>
       </c>
       <c r="B4" t="str">
         <f>alunos!B3</f>
@@ -1112,6 +1601,12 @@
         <v>34</v>
       </c>
       <c r="AE4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG4" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1193,7 +1688,7 @@
     <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
-        <v>0</v>
+        <v>25129045</v>
       </c>
       <c r="B5" t="str">
         <f>alunos!B4</f>
@@ -1284,6 +1779,12 @@
         <v>34</v>
       </c>
       <c r="AE5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG5" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1365,7 +1866,7 @@
     <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
-        <v>0</v>
+        <v>25129967</v>
       </c>
       <c r="B6" t="str">
         <f>alunos!B5</f>
@@ -1456,6 +1957,12 @@
         <v>34</v>
       </c>
       <c r="AE6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG6" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1537,7 +2044,7 @@
     <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
-        <v>0</v>
+        <v>25129049</v>
       </c>
       <c r="B7" t="str">
         <f>alunos!B6</f>
@@ -1628,6 +2135,12 @@
         <v>34</v>
       </c>
       <c r="AE7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG7" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1709,7 +2222,7 @@
     <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
-        <v>0</v>
+        <v>25129051</v>
       </c>
       <c r="B8" t="str">
         <f>alunos!B7</f>
@@ -1800,6 +2313,12 @@
         <v>34</v>
       </c>
       <c r="AE8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG8" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1881,7 +2400,7 @@
     <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
-        <v>0</v>
+        <v>25129087</v>
       </c>
       <c r="B9" t="str">
         <f>alunos!B8</f>
@@ -1972,6 +2491,12 @@
         <v>34</v>
       </c>
       <c r="AE9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2053,7 +2578,7 @@
     <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
-        <v>0</v>
+        <v>25129053</v>
       </c>
       <c r="B10" t="str">
         <f>alunos!B9</f>
@@ -2144,6 +2669,12 @@
         <v>34</v>
       </c>
       <c r="AE10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG10" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2225,7 +2756,7 @@
     <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
-        <v>0</v>
+        <v>25129055</v>
       </c>
       <c r="B11" t="str">
         <f>alunos!B10</f>
@@ -2316,6 +2847,12 @@
         <v>34</v>
       </c>
       <c r="AE11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG11" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2397,7 +2934,7 @@
     <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
-        <v>0</v>
+        <v>25129178</v>
       </c>
       <c r="B12" t="str">
         <f>alunos!B11</f>
@@ -2488,6 +3025,12 @@
         <v>34</v>
       </c>
       <c r="AE12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG12" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2569,7 +3112,7 @@
     <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
-        <v>0</v>
+        <v>25129089</v>
       </c>
       <c r="B13" t="str">
         <f>alunos!B12</f>
@@ -2660,6 +3203,12 @@
         <v>34</v>
       </c>
       <c r="AE13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG13" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2741,7 +3290,7 @@
     <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
-        <v>0</v>
+        <v>25129057</v>
       </c>
       <c r="B14" t="str">
         <f>alunos!B13</f>
@@ -2832,6 +3381,12 @@
         <v>34</v>
       </c>
       <c r="AE14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG14" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2913,7 +3468,7 @@
     <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
-        <v>0</v>
+        <v>25129091</v>
       </c>
       <c r="B15" t="str">
         <f>alunos!B14</f>
@@ -3004,6 +3559,12 @@
         <v>34</v>
       </c>
       <c r="AE15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG15" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3085,7 +3646,7 @@
     <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
-        <v>0</v>
+        <v>25129123</v>
       </c>
       <c r="B16" t="str">
         <f>alunos!B15</f>
@@ -3176,6 +3737,12 @@
         <v>34</v>
       </c>
       <c r="AE16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG16" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3257,7 +3824,7 @@
     <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
-        <v>0</v>
+        <v>25129059</v>
       </c>
       <c r="B17" t="str">
         <f>alunos!B16</f>
@@ -3348,6 +3915,12 @@
         <v>34</v>
       </c>
       <c r="AE17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG17" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3429,7 +4002,7 @@
     <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
-        <v>0</v>
+        <v>25129061</v>
       </c>
       <c r="B18" t="str">
         <f>alunos!B17</f>
@@ -3520,6 +4093,12 @@
         <v>34</v>
       </c>
       <c r="AE18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG18" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3601,7 +4180,7 @@
     <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
-        <v>0</v>
+        <v>25129095</v>
       </c>
       <c r="B19" t="str">
         <f>alunos!B18</f>
@@ -3692,6 +4271,12 @@
         <v>34</v>
       </c>
       <c r="AE19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG19" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3773,7 +4358,7 @@
     <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
-        <v>0</v>
+        <v>25130299</v>
       </c>
       <c r="B20" t="str">
         <f>alunos!B19</f>
@@ -3864,6 +4449,12 @@
         <v>34</v>
       </c>
       <c r="AE20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG20" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3945,7 +4536,7 @@
     <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
-        <v>0</v>
+        <v>25129249</v>
       </c>
       <c r="B21" t="str">
         <f>alunos!B20</f>
@@ -4036,6 +4627,12 @@
         <v>34</v>
       </c>
       <c r="AE21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG21" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4117,7 +4714,7 @@
     <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
-        <v>0</v>
+        <v>25129970</v>
       </c>
       <c r="B22" t="str">
         <f>alunos!B21</f>
@@ -4208,6 +4805,12 @@
         <v>34</v>
       </c>
       <c r="AE22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG22" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4289,7 +4892,7 @@
     <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
-        <v>0</v>
+        <v>25130290</v>
       </c>
       <c r="B23" t="str">
         <f>alunos!B22</f>
@@ -4380,6 +4983,12 @@
         <v>34</v>
       </c>
       <c r="AE23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG23" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4461,7 +5070,7 @@
     <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
-        <v>0</v>
+        <v>25129129</v>
       </c>
       <c r="B24" t="str">
         <f>alunos!B23</f>
@@ -4552,6 +5161,12 @@
         <v>34</v>
       </c>
       <c r="AE24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG24" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4633,7 +5248,7 @@
     <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
-        <v>0</v>
+        <v>25129237</v>
       </c>
       <c r="B25" t="str">
         <f>alunos!B24</f>
@@ -4724,6 +5339,12 @@
         <v>34</v>
       </c>
       <c r="AE25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG25" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4805,7 +5426,7 @@
     <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
-        <v>0</v>
+        <v>25129063</v>
       </c>
       <c r="B26" t="str">
         <f>alunos!B25</f>
@@ -4896,6 +5517,12 @@
         <v>34</v>
       </c>
       <c r="AE26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG26" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4977,7 +5604,7 @@
     <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
-        <v>0</v>
+        <v>25129065</v>
       </c>
       <c r="B27" t="str">
         <f>alunos!B26</f>
@@ -5068,6 +5695,12 @@
         <v>34</v>
       </c>
       <c r="AE27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG27" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5149,7 +5782,7 @@
     <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
-        <v>0</v>
+        <v>25129182</v>
       </c>
       <c r="B28" t="str">
         <f>alunos!B27</f>
@@ -5240,6 +5873,12 @@
         <v>34</v>
       </c>
       <c r="AE28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG28" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5321,7 +5960,7 @@
     <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
-        <v>0</v>
+        <v>25129103</v>
       </c>
       <c r="B29" t="str">
         <f>alunos!B28</f>
@@ -5412,6 +6051,12 @@
         <v>34</v>
       </c>
       <c r="AE29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG29" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5493,7 +6138,7 @@
     <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
-        <v>0</v>
+        <v>25129131</v>
       </c>
       <c r="B30" t="str">
         <f>alunos!B29</f>
@@ -5584,6 +6229,12 @@
         <v>34</v>
       </c>
       <c r="AE30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG30" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5665,7 +6316,7 @@
     <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
-        <v>0</v>
+        <v>25129099</v>
       </c>
       <c r="B31" t="str">
         <f>alunos!B30</f>
@@ -5756,6 +6407,12 @@
         <v>34</v>
       </c>
       <c r="AE31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG31" s="8" t="s">
         <v>34</v>
       </c>
       <c r="AU31" s="2"/>
@@ -5839,7 +6496,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AF23:BJ31 AF11:BA22 AF3:AZ10 AC3:AE31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AH3:AZ10 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AH11:BA22 BC11:BJ22 AH23:BJ31 AC3:AG31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5868,146 +6525,233 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>25130313</v>
+      </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>25129077</v>
+      </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>25129045</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>25129967</v>
+      </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>25129049</v>
+      </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>25129051</v>
+      </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>25129087</v>
+      </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>25129053</v>
+      </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>25129055</v>
+      </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>25129178</v>
+      </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>25129089</v>
+      </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>25129057</v>
+      </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>25129091</v>
+      </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>25129123</v>
+      </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>25129059</v>
+      </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>25129061</v>
+      </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>25129095</v>
+      </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>25130299</v>
+      </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>25129249</v>
+      </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>25129970</v>
+      </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>25130290</v>
+      </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>25129129</v>
+      </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>25129237</v>
+      </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>25129063</v>
+      </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25129065</v>
+      </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>25129182</v>
+      </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>25129103</v>
+      </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>25129131</v>
+      </c>
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>25129099</v>
+      </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDB1864-1A8A-4F98-A756-B14DE607312F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A1A15A-AF25-4301-9AB7-915278D3C677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -677,7 +677,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -686,7 +686,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1021,21 +1020,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.7109375" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="28" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1185,7 +1184,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1329,7 +1328,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1425,10 +1424,10 @@
       <c r="AE3" t="s">
         <v>34</v>
       </c>
-      <c r="AF3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG3" s="8" t="s">
+      <c r="AF3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1507,7 +1506,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1603,10 +1602,10 @@
       <c r="AE4" t="s">
         <v>34</v>
       </c>
-      <c r="AF4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG4" s="8" t="s">
+      <c r="AF4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1685,7 +1684,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1781,10 +1780,10 @@
       <c r="AE5" t="s">
         <v>34</v>
       </c>
-      <c r="AF5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG5" s="8" t="s">
+      <c r="AF5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1863,7 +1862,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -1959,10 +1958,10 @@
       <c r="AE6" t="s">
         <v>34</v>
       </c>
-      <c r="AF6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG6" s="8" t="s">
+      <c r="AF6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -2041,7 +2040,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2137,10 +2136,10 @@
       <c r="AE7" t="s">
         <v>34</v>
       </c>
-      <c r="AF7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG7" s="8" t="s">
+      <c r="AF7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -2219,7 +2218,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2315,10 +2314,10 @@
       <c r="AE8" t="s">
         <v>34</v>
       </c>
-      <c r="AF8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG8" s="8" t="s">
+      <c r="AF8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -2397,7 +2396,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2493,10 +2492,10 @@
       <c r="AE9" t="s">
         <v>34</v>
       </c>
-      <c r="AF9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG9" s="8" t="s">
+      <c r="AF9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG9" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2575,7 +2574,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -2671,10 +2670,10 @@
       <c r="AE10" t="s">
         <v>34</v>
       </c>
-      <c r="AF10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG10" s="8" t="s">
+      <c r="AF10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2753,7 +2752,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -2849,10 +2848,10 @@
       <c r="AE11" t="s">
         <v>34</v>
       </c>
-      <c r="AF11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG11" s="8" t="s">
+      <c r="AF11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2931,7 +2930,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3027,10 +3026,10 @@
       <c r="AE12" t="s">
         <v>34</v>
       </c>
-      <c r="AF12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG12" s="8" t="s">
+      <c r="AF12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -3109,7 +3108,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3205,10 +3204,10 @@
       <c r="AE13" t="s">
         <v>34</v>
       </c>
-      <c r="AF13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG13" s="8" t="s">
+      <c r="AF13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -3287,7 +3286,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3383,10 +3382,10 @@
       <c r="AE14" t="s">
         <v>34</v>
       </c>
-      <c r="AF14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG14" s="8" t="s">
+      <c r="AF14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG14" t="s">
         <v>34</v>
       </c>
       <c r="AU14" s="2"/>
@@ -3465,7 +3464,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -3561,10 +3560,10 @@
       <c r="AE15" t="s">
         <v>34</v>
       </c>
-      <c r="AF15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG15" s="8" t="s">
+      <c r="AF15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG15" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3643,7 +3642,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -3739,10 +3738,10 @@
       <c r="AE16" t="s">
         <v>34</v>
       </c>
-      <c r="AF16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG16" s="8" t="s">
+      <c r="AF16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG16" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3821,7 +3820,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -3917,10 +3916,10 @@
       <c r="AE17" t="s">
         <v>34</v>
       </c>
-      <c r="AF17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG17" s="8" t="s">
+      <c r="AF17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3999,7 +3998,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4095,10 +4094,10 @@
       <c r="AE18" t="s">
         <v>34</v>
       </c>
-      <c r="AF18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG18" s="8" t="s">
+      <c r="AF18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -4177,7 +4176,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4273,10 +4272,10 @@
       <c r="AE19" t="s">
         <v>34</v>
       </c>
-      <c r="AF19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG19" s="8" t="s">
+      <c r="AF19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -4355,7 +4354,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -4451,10 +4450,10 @@
       <c r="AE20" t="s">
         <v>34</v>
       </c>
-      <c r="AF20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG20" s="8" t="s">
+      <c r="AF20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -4533,7 +4532,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -4629,10 +4628,10 @@
       <c r="AE21" t="s">
         <v>34</v>
       </c>
-      <c r="AF21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG21" s="8" t="s">
+      <c r="AF21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG21" t="s">
         <v>34</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4711,7 +4710,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -4807,10 +4806,10 @@
       <c r="AE22" t="s">
         <v>34</v>
       </c>
-      <c r="AF22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG22" s="8" t="s">
+      <c r="AF22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG22" t="s">
         <v>34</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4889,7 +4888,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -4985,10 +4984,10 @@
       <c r="AE23" t="s">
         <v>34</v>
       </c>
-      <c r="AF23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG23" s="8" t="s">
+      <c r="AF23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG23" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -5067,7 +5066,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -5163,10 +5162,10 @@
       <c r="AE24" t="s">
         <v>34</v>
       </c>
-      <c r="AF24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG24" s="8" t="s">
+      <c r="AF24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -5245,7 +5244,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -5341,10 +5340,10 @@
       <c r="AE25" t="s">
         <v>34</v>
       </c>
-      <c r="AF25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG25" s="8" t="s">
+      <c r="AF25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -5423,7 +5422,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -5519,10 +5518,10 @@
       <c r="AE26" t="s">
         <v>34</v>
       </c>
-      <c r="AF26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG26" s="8" t="s">
+      <c r="AF26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG26" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -5601,7 +5600,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -5697,10 +5696,10 @@
       <c r="AE27" t="s">
         <v>34</v>
       </c>
-      <c r="AF27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG27" s="8" t="s">
+      <c r="AF27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5779,7 +5778,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -5875,10 +5874,10 @@
       <c r="AE28" t="s">
         <v>34</v>
       </c>
-      <c r="AF28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG28" s="8" t="s">
+      <c r="AF28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5957,7 +5956,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -6053,11 +6052,11 @@
       <c r="AE29" t="s">
         <v>34</v>
       </c>
-      <c r="AF29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG29" s="8" t="s">
-        <v>34</v>
+      <c r="AF29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>35</v>
       </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
@@ -6135,7 +6134,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -6231,10 +6230,10 @@
       <c r="AE30" t="s">
         <v>34</v>
       </c>
-      <c r="AF30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG30" s="8" t="s">
+      <c r="AF30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG30" t="s">
         <v>34</v>
       </c>
       <c r="AU30" s="2"/>
@@ -6313,7 +6312,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -6409,10 +6408,10 @@
       <c r="AE31" t="s">
         <v>34</v>
       </c>
-      <c r="AF31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG31" s="8" t="s">
+      <c r="AF31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG31" t="s">
         <v>34</v>
       </c>
       <c r="AU31" s="2"/>
@@ -6496,7 +6495,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AH3:AZ10 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AH11:BA22 BC11:BJ22 AH23:BJ31 AC3:AG31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AH3:AZ10 BB3:BB22 K3:L31 AC3:AG31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AH11:BA22 BC11:BJ22 AH23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6509,14 +6508,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6524,7 +6523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -6532,7 +6531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -6540,7 +6539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -6548,7 +6547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -6556,7 +6555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -6564,7 +6563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -6572,7 +6571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -6580,7 +6579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -6588,7 +6587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -6596,7 +6595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -6604,7 +6603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -6612,7 +6611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -6620,7 +6619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -6628,7 +6627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -6636,7 +6635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -6644,7 +6643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -6652,7 +6651,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -6660,7 +6659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -6668,7 +6667,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -6676,7 +6675,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -6684,7 +6683,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -6692,7 +6691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -6700,7 +6699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -6708,7 +6707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -6716,7 +6715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -6724,7 +6723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -6732,7 +6731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -6740,7 +6739,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -6748,7 +6747,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -6765,18 +6764,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -6784,7 +6783,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -6793,7 +6792,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -6802,7 +6801,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -6811,7 +6810,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -6820,13 +6819,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -6835,7 +6834,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -6844,7 +6843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -6860,13 +6859,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -6875,7 +6874,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -6884,7 +6883,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -6893,7 +6892,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -6902,7 +6901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -6911,7 +6910,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -6920,7 +6919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -6929,7 +6928,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -6938,7 +6937,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -6947,7 +6946,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -6956,7 +6955,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -6965,7 +6964,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -6974,7 +6973,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -6983,25 +6982,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -7010,7 +7009,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -7019,7 +7018,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -7028,7 +7027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A1A15A-AF25-4301-9AB7-915278D3C677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2CFF51-7C9B-43AC-A365-D40AACF4623E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -1020,21 +1020,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.7109375" customWidth="1"/>
+    <col min="20" max="25" width="7.6640625" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="28" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1125,7 +1125,9 @@
       <c r="AG1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" s="1"/>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
@@ -1184,7 +1186,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1283,6 +1285,9 @@
       </c>
       <c r="AG2" s="1">
         <v>46157</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>46162</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -1328,7 +1333,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1428,6 +1433,9 @@
         <v>34</v>
       </c>
       <c r="AG3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1506,7 +1514,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1606,6 +1614,9 @@
         <v>34</v>
       </c>
       <c r="AG4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1684,7 +1695,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1784,6 +1795,9 @@
         <v>34</v>
       </c>
       <c r="AG5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1862,7 +1876,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -1962,6 +1976,9 @@
         <v>34</v>
       </c>
       <c r="AG6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -2040,7 +2057,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2140,6 +2157,9 @@
         <v>34</v>
       </c>
       <c r="AG7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -2218,7 +2238,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2318,6 +2338,9 @@
         <v>34</v>
       </c>
       <c r="AG8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -2396,7 +2419,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2496,6 +2519,9 @@
         <v>34</v>
       </c>
       <c r="AG9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH9" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2574,7 +2600,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -2674,6 +2700,9 @@
         <v>34</v>
       </c>
       <c r="AG10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2752,7 +2781,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -2852,6 +2881,9 @@
         <v>34</v>
       </c>
       <c r="AG11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2930,7 +2962,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3030,6 +3062,9 @@
         <v>34</v>
       </c>
       <c r="AG12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -3108,7 +3143,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3208,6 +3243,9 @@
         <v>34</v>
       </c>
       <c r="AG13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -3286,7 +3324,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3386,6 +3424,9 @@
         <v>34</v>
       </c>
       <c r="AG14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH14" t="s">
         <v>34</v>
       </c>
       <c r="AU14" s="2"/>
@@ -3464,7 +3505,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -3564,6 +3605,9 @@
         <v>34</v>
       </c>
       <c r="AG15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH15" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3642,7 +3686,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -3742,6 +3786,9 @@
         <v>34</v>
       </c>
       <c r="AG16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH16" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3820,7 +3867,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -3920,6 +3967,9 @@
         <v>34</v>
       </c>
       <c r="AG17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3998,7 +4048,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4098,6 +4148,9 @@
         <v>34</v>
       </c>
       <c r="AG18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -4176,7 +4229,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4276,6 +4329,9 @@
         <v>34</v>
       </c>
       <c r="AG19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -4354,7 +4410,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -4454,6 +4510,9 @@
         <v>34</v>
       </c>
       <c r="AG20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -4532,7 +4591,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -4632,6 +4691,9 @@
         <v>34</v>
       </c>
       <c r="AG21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH21" t="s">
         <v>34</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4710,7 +4772,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -4810,6 +4872,9 @@
         <v>34</v>
       </c>
       <c r="AG22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH22" t="s">
         <v>34</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4888,7 +4953,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -4988,6 +5053,9 @@
         <v>34</v>
       </c>
       <c r="AG23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH23" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -5066,7 +5134,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -5166,6 +5234,9 @@
         <v>34</v>
       </c>
       <c r="AG24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -5244,7 +5315,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -5344,6 +5415,9 @@
         <v>34</v>
       </c>
       <c r="AG25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -5422,7 +5496,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -5522,6 +5596,9 @@
         <v>34</v>
       </c>
       <c r="AG26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH26" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -5600,7 +5677,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -5700,6 +5777,9 @@
         <v>34</v>
       </c>
       <c r="AG27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5778,7 +5858,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -5878,6 +5958,9 @@
         <v>34</v>
       </c>
       <c r="AG28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5956,7 +6039,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -6057,6 +6140,9 @@
       </c>
       <c r="AG29" t="s">
         <v>35</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>34</v>
       </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
@@ -6134,7 +6220,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -6234,6 +6320,9 @@
         <v>34</v>
       </c>
       <c r="AG30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH30" t="s">
         <v>34</v>
       </c>
       <c r="AU30" s="2"/>
@@ -6312,7 +6401,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -6412,6 +6501,9 @@
         <v>34</v>
       </c>
       <c r="AG31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH31" t="s">
         <v>34</v>
       </c>
       <c r="AU31" s="2"/>
@@ -6495,7 +6587,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AH3:AZ10 BB3:BB22 K3:L31 AC3:AG31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AH11:BA22 BC11:BJ22 AH23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AH3:AZ3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AI11:BA22 BC11:BJ22 AI23:BJ31 AI4:AZ10 AH4:AH31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6508,14 +6600,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6523,7 +6615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -6531,7 +6623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -6539,7 +6631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -6547,7 +6639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -6555,7 +6647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -6563,7 +6655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -6571,7 +6663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -6579,7 +6671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -6587,7 +6679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -6595,7 +6687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -6603,7 +6695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -6611,7 +6703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -6619,7 +6711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -6627,7 +6719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -6635,7 +6727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -6643,7 +6735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -6651,7 +6743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -6659,7 +6751,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -6667,7 +6759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -6675,7 +6767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -6683,7 +6775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -6691,7 +6783,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -6699,7 +6791,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -6707,7 +6799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -6715,7 +6807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -6723,7 +6815,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -6731,7 +6823,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -6739,7 +6831,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -6747,7 +6839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -6764,18 +6856,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -6783,7 +6875,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -6792,7 +6884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -6801,7 +6893,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -6810,7 +6902,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -6819,13 +6911,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -6834,7 +6926,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -6843,7 +6935,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -6859,13 +6951,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -6874,7 +6966,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -6883,7 +6975,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -6892,7 +6984,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -6901,7 +6993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -6910,7 +7002,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -6919,7 +7011,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -6928,7 +7020,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -6937,7 +7029,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -6946,7 +7038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -6955,7 +7047,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -6964,7 +7056,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -6973,7 +7065,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -6982,25 +7074,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -7009,7 +7101,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -7018,7 +7110,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -7027,7 +7119,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2CFF51-7C9B-43AC-A365-D40AACF4623E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E3DD2A-A27C-4F08-8A1B-51DE0C4CA975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3885" yWindow="3885" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -1020,21 +1020,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.7109375" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="28" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1128,7 +1128,9 @@
       <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1"/>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -1186,7 +1188,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1288,6 +1290,9 @@
       </c>
       <c r="AH2" s="1">
         <v>46162</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>46164</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -1333,7 +1338,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1436,6 +1441,9 @@
         <v>34</v>
       </c>
       <c r="AH3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1514,7 +1522,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1617,6 +1625,9 @@
         <v>34</v>
       </c>
       <c r="AH4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1695,7 +1706,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1798,6 +1809,9 @@
         <v>34</v>
       </c>
       <c r="AH5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1876,7 +1890,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -1979,6 +1993,9 @@
         <v>34</v>
       </c>
       <c r="AH6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -2057,7 +2074,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2160,6 +2177,9 @@
         <v>34</v>
       </c>
       <c r="AH7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -2238,7 +2258,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2341,6 +2361,9 @@
         <v>34</v>
       </c>
       <c r="AH8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -2419,7 +2442,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2522,6 +2545,9 @@
         <v>34</v>
       </c>
       <c r="AH9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI9" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2600,7 +2626,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -2703,6 +2729,9 @@
         <v>34</v>
       </c>
       <c r="AH10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2781,7 +2810,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -2884,6 +2913,9 @@
         <v>34</v>
       </c>
       <c r="AH11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2962,7 +2994,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3065,6 +3097,9 @@
         <v>34</v>
       </c>
       <c r="AH12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -3143,7 +3178,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3246,6 +3281,9 @@
         <v>34</v>
       </c>
       <c r="AH13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -3324,7 +3362,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3427,6 +3465,9 @@
         <v>34</v>
       </c>
       <c r="AH14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI14" t="s">
         <v>34</v>
       </c>
       <c r="AU14" s="2"/>
@@ -3505,7 +3546,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -3608,6 +3649,9 @@
         <v>34</v>
       </c>
       <c r="AH15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI15" t="s">
         <v>34</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3686,7 +3730,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -3789,6 +3833,9 @@
         <v>34</v>
       </c>
       <c r="AH16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI16" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3867,7 +3914,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -3970,6 +4017,9 @@
         <v>34</v>
       </c>
       <c r="AH17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -4048,7 +4098,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4151,6 +4201,9 @@
         <v>34</v>
       </c>
       <c r="AH18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -4229,7 +4282,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4332,6 +4385,9 @@
         <v>34</v>
       </c>
       <c r="AH19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -4410,7 +4466,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -4513,6 +4569,9 @@
         <v>34</v>
       </c>
       <c r="AH20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -4591,7 +4650,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -4694,6 +4753,9 @@
         <v>34</v>
       </c>
       <c r="AH21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI21" t="s">
         <v>34</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4772,7 +4834,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -4875,6 +4937,9 @@
         <v>34</v>
       </c>
       <c r="AH22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI22" t="s">
         <v>34</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4953,7 +5018,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5056,6 +5121,9 @@
         <v>34</v>
       </c>
       <c r="AH23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI23" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -5134,7 +5202,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -5237,6 +5305,9 @@
         <v>34</v>
       </c>
       <c r="AH24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -5315,7 +5386,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -5418,6 +5489,9 @@
         <v>34</v>
       </c>
       <c r="AH25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -5496,7 +5570,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -5599,6 +5673,9 @@
         <v>34</v>
       </c>
       <c r="AH26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI26" t="s">
         <v>34</v>
       </c>
       <c r="AU26" s="2"/>
@@ -5677,7 +5754,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -5780,6 +5857,9 @@
         <v>34</v>
       </c>
       <c r="AH27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5858,7 +5938,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -5961,6 +6041,9 @@
         <v>34</v>
       </c>
       <c r="AH28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -6039,7 +6122,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -6142,6 +6225,9 @@
         <v>35</v>
       </c>
       <c r="AH29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI29" t="s">
         <v>34</v>
       </c>
       <c r="AU29" s="2"/>
@@ -6220,7 +6306,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -6323,6 +6409,9 @@
         <v>34</v>
       </c>
       <c r="AH30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI30" t="s">
         <v>34</v>
       </c>
       <c r="AU30" s="2"/>
@@ -6401,7 +6490,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -6504,6 +6593,9 @@
         <v>34</v>
       </c>
       <c r="AH31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI31" t="s">
         <v>34</v>
       </c>
       <c r="AU31" s="2"/>
@@ -6587,7 +6679,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AH3:AZ3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AI11:BA22 BC11:BJ22 AI23:BJ31 AI4:AZ10 AH4:AH31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 AJ4:AZ10 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AJ11:BA22 BC11:BJ22 AJ23:BJ31 AH3:AZ3 AH4:AI31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6600,14 +6692,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6615,7 +6707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -6623,7 +6715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -6631,7 +6723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -6639,7 +6731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -6647,7 +6739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -6655,7 +6747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -6663,7 +6755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -6671,7 +6763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -6679,7 +6771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -6687,7 +6779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -6695,7 +6787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -6703,7 +6795,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -6711,7 +6803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -6719,7 +6811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -6727,7 +6819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -6735,7 +6827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -6743,7 +6835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -6751,7 +6843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -6759,7 +6851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -6767,7 +6859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -6775,7 +6867,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -6783,7 +6875,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -6791,7 +6883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -6799,7 +6891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -6807,7 +6899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -6815,7 +6907,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -6823,7 +6915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -6831,7 +6923,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -6839,7 +6931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -6856,18 +6948,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -6875,7 +6967,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -6884,7 +6976,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -6893,7 +6985,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -6902,7 +6994,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -6911,13 +7003,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -6926,7 +7018,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -6935,7 +7027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -6951,13 +7043,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -6966,7 +7058,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -6975,7 +7067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -6984,7 +7076,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -6993,7 +7085,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -7002,7 +7094,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -7011,7 +7103,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -7020,7 +7112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -7029,7 +7121,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -7038,7 +7130,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -7047,7 +7139,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -7056,7 +7148,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -7065,7 +7157,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -7074,25 +7166,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -7101,7 +7193,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -7110,7 +7202,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -7119,7 +7211,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E3DD2A-A27C-4F08-8A1B-51DE0C4CA975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422D309C-AE00-4AFA-AA95-67A1BC10012C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="3885" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -1020,21 +1020,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.7109375" customWidth="1"/>
+    <col min="20" max="25" width="7.6640625" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="28" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1188,7 +1188,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1338,7 +1338,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1522,7 +1522,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1706,7 +1706,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1890,7 +1890,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2074,7 +2074,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2258,7 +2258,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2442,7 +2442,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2626,7 +2626,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -2810,7 +2810,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -2994,7 +2994,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3178,7 +3178,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3362,7 +3362,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3546,7 +3546,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -3730,7 +3730,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -3914,7 +3914,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4098,7 +4098,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4282,7 +4282,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4466,7 +4466,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -4650,7 +4650,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -4756,7 +4756,7 @@
         <v>34</v>
       </c>
       <c r="AI21" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
@@ -4834,7 +4834,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5018,7 +5018,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5202,7 +5202,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -5386,7 +5386,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -5570,7 +5570,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -5754,7 +5754,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -5938,7 +5938,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -6122,7 +6122,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -6306,7 +6306,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -6490,7 +6490,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -6596,7 +6596,7 @@
         <v>34</v>
       </c>
       <c r="AI31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -6679,7 +6679,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 AJ4:AZ10 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AJ11:BA22 BC11:BJ22 AJ23:BJ31 AH3:AZ3 AH4:AI31">
+  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 AJ4:AZ10 BE4:BJ10 O4:AB31 AH4:AI31 BK4:DG31 D6:J31 M6:N31 AJ11:BA22 BC11:BJ22 AJ23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6692,14 +6692,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -6948,18 +6948,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -6976,7 +6976,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -6985,7 +6985,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -6994,7 +6994,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -7003,13 +7003,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -7018,7 +7018,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -7027,7 +7027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -7043,13 +7043,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -7058,7 +7058,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -7067,7 +7067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -7076,7 +7076,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -7085,7 +7085,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -7094,7 +7094,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -7103,7 +7103,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -7112,7 +7112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -7121,7 +7121,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -7130,7 +7130,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -7139,7 +7139,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -7148,7 +7148,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -7157,7 +7157,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -7166,25 +7166,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -7193,7 +7193,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -7202,7 +7202,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -7211,7 +7211,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422D309C-AE00-4AFA-AA95-67A1BC10012C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85741EAA-7265-4B5E-ACA1-FC4187405D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -1131,8 +1131,12 @@
       <c r="AI1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
@@ -1294,6 +1298,12 @@
       <c r="AI2" s="1">
         <v>46164</v>
       </c>
+      <c r="AJ2" s="1">
+        <v>46169</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>46171</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -1444,6 +1454,9 @@
         <v>34</v>
       </c>
       <c r="AI3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1630,6 +1643,9 @@
       <c r="AI4" t="s">
         <v>34</v>
       </c>
+      <c r="AJ4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1814,6 +1830,9 @@
       <c r="AI5" t="s">
         <v>34</v>
       </c>
+      <c r="AJ5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1998,6 +2017,9 @@
       <c r="AI6" t="s">
         <v>34</v>
       </c>
+      <c r="AJ6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -2182,6 +2204,9 @@
       <c r="AI7" t="s">
         <v>34</v>
       </c>
+      <c r="AJ7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2366,6 +2391,9 @@
       <c r="AI8" t="s">
         <v>34</v>
       </c>
+      <c r="AJ8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2550,6 +2578,9 @@
       <c r="AI9" t="s">
         <v>34</v>
       </c>
+      <c r="AJ9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2734,6 +2765,9 @@
       <c r="AI10" t="s">
         <v>34</v>
       </c>
+      <c r="AJ10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2918,6 +2952,9 @@
       <c r="AI11" t="s">
         <v>34</v>
       </c>
+      <c r="AJ11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -3102,6 +3139,9 @@
       <c r="AI12" t="s">
         <v>34</v>
       </c>
+      <c r="AJ12" t="s">
+        <v>35</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3286,6 +3326,9 @@
       <c r="AI13" t="s">
         <v>34</v>
       </c>
+      <c r="AJ13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3470,6 +3513,9 @@
       <c r="AI14" t="s">
         <v>34</v>
       </c>
+      <c r="AJ14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3654,6 +3700,9 @@
       <c r="AI15" t="s">
         <v>34</v>
       </c>
+      <c r="AJ15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3838,6 +3887,9 @@
       <c r="AI16" t="s">
         <v>34</v>
       </c>
+      <c r="AJ16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -4022,6 +4074,9 @@
       <c r="AI17" t="s">
         <v>34</v>
       </c>
+      <c r="AJ17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4206,6 +4261,9 @@
       <c r="AI18" t="s">
         <v>34</v>
       </c>
+      <c r="AJ18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4390,6 +4448,9 @@
       <c r="AI19" t="s">
         <v>34</v>
       </c>
+      <c r="AJ19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4574,6 +4635,9 @@
       <c r="AI20" t="s">
         <v>34</v>
       </c>
+      <c r="AJ20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4758,6 +4822,9 @@
       <c r="AI21" t="s">
         <v>40</v>
       </c>
+      <c r="AJ21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4942,6 +5009,9 @@
       <c r="AI22" t="s">
         <v>34</v>
       </c>
+      <c r="AJ22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5126,6 +5196,9 @@
       <c r="AI23" t="s">
         <v>34</v>
       </c>
+      <c r="AJ23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5310,6 +5383,9 @@
       <c r="AI24" t="s">
         <v>34</v>
       </c>
+      <c r="AJ24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5494,6 +5570,9 @@
       <c r="AI25" t="s">
         <v>34</v>
       </c>
+      <c r="AJ25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5678,6 +5757,9 @@
       <c r="AI26" t="s">
         <v>34</v>
       </c>
+      <c r="AJ26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5862,6 +5944,9 @@
       <c r="AI27" t="s">
         <v>34</v>
       </c>
+      <c r="AJ27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -6046,6 +6131,9 @@
       <c r="AI28" t="s">
         <v>34</v>
       </c>
+      <c r="AJ28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6230,6 +6318,9 @@
       <c r="AI29" t="s">
         <v>34</v>
       </c>
+      <c r="AJ29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6414,6 +6505,9 @@
       <c r="AI30" t="s">
         <v>34</v>
       </c>
+      <c r="AJ30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6598,6 +6692,9 @@
       <c r="AI31" t="s">
         <v>35</v>
       </c>
+      <c r="AJ31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85741EAA-7265-4B5E-ACA1-FC4187405D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F8946F-CCC7-4E02-A665-009217A3A62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>4P/4F</t>
+  </si>
+  <si>
+    <t>Feriado</t>
   </si>
 </sst>
 </file>
@@ -1137,10 +1140,18 @@
       <c r="AK1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
+      <c r="AL1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
@@ -1304,6 +1315,18 @@
       <c r="AK2" s="1">
         <v>46171</v>
       </c>
+      <c r="AL2" s="1">
+        <v>46176</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>46183</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>46185</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -1458,6 +1481,15 @@
       </c>
       <c r="AJ3" t="s">
         <v>34</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>46</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
@@ -1646,6 +1678,15 @@
       <c r="AJ4" t="s">
         <v>34</v>
       </c>
+      <c r="AK4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>46</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1833,6 +1874,15 @@
       <c r="AJ5" t="s">
         <v>34</v>
       </c>
+      <c r="AK5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>46</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -2020,6 +2070,15 @@
       <c r="AJ6" t="s">
         <v>34</v>
       </c>
+      <c r="AK6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>46</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -2207,6 +2266,15 @@
       <c r="AJ7" t="s">
         <v>34</v>
       </c>
+      <c r="AK7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>46</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2394,6 +2462,15 @@
       <c r="AJ8" t="s">
         <v>34</v>
       </c>
+      <c r="AK8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>46</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2581,6 +2658,15 @@
       <c r="AJ9" t="s">
         <v>34</v>
       </c>
+      <c r="AK9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>46</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2768,6 +2854,15 @@
       <c r="AJ10" t="s">
         <v>34</v>
       </c>
+      <c r="AK10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>46</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2955,6 +3050,15 @@
       <c r="AJ11" t="s">
         <v>34</v>
       </c>
+      <c r="AK11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>46</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -3142,6 +3246,15 @@
       <c r="AJ12" t="s">
         <v>35</v>
       </c>
+      <c r="AK12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>46</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3329,6 +3442,15 @@
       <c r="AJ13" t="s">
         <v>34</v>
       </c>
+      <c r="AK13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>46</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3516,6 +3638,15 @@
       <c r="AJ14" t="s">
         <v>34</v>
       </c>
+      <c r="AK14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>46</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3703,6 +3834,15 @@
       <c r="AJ15" t="s">
         <v>34</v>
       </c>
+      <c r="AK15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>46</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3890,6 +4030,15 @@
       <c r="AJ16" t="s">
         <v>34</v>
       </c>
+      <c r="AK16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>46</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -4077,6 +4226,15 @@
       <c r="AJ17" t="s">
         <v>34</v>
       </c>
+      <c r="AK17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>46</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4264,6 +4422,15 @@
       <c r="AJ18" t="s">
         <v>34</v>
       </c>
+      <c r="AK18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>46</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4451,6 +4618,15 @@
       <c r="AJ19" t="s">
         <v>34</v>
       </c>
+      <c r="AK19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>46</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4638,6 +4814,15 @@
       <c r="AJ20" t="s">
         <v>34</v>
       </c>
+      <c r="AK20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>46</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4825,6 +5010,15 @@
       <c r="AJ21" t="s">
         <v>34</v>
       </c>
+      <c r="AK21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>46</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -5012,6 +5206,15 @@
       <c r="AJ22" t="s">
         <v>34</v>
       </c>
+      <c r="AK22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>46</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5199,6 +5402,15 @@
       <c r="AJ23" t="s">
         <v>34</v>
       </c>
+      <c r="AK23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>46</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5386,6 +5598,15 @@
       <c r="AJ24" t="s">
         <v>34</v>
       </c>
+      <c r="AK24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>46</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5573,6 +5794,15 @@
       <c r="AJ25" t="s">
         <v>34</v>
       </c>
+      <c r="AK25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>46</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5760,6 +5990,15 @@
       <c r="AJ26" t="s">
         <v>34</v>
       </c>
+      <c r="AK26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>46</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5947,6 +6186,15 @@
       <c r="AJ27" t="s">
         <v>34</v>
       </c>
+      <c r="AK27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>46</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -6134,6 +6382,15 @@
       <c r="AJ28" t="s">
         <v>34</v>
       </c>
+      <c r="AK28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>46</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6321,6 +6578,15 @@
       <c r="AJ29" t="s">
         <v>34</v>
       </c>
+      <c r="AK29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>46</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6508,6 +6774,15 @@
       <c r="AJ30" t="s">
         <v>34</v>
       </c>
+      <c r="AK30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>46</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6695,6 +6970,15 @@
       <c r="AJ31" t="s">
         <v>34</v>
       </c>
+      <c r="AK31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>46</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -6776,7 +7060,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 AJ4:AZ10 BE4:BJ10 O4:AB31 AH4:AI31 BK4:DG31 D6:J31 M6:N31 AJ11:BA22 BC11:BJ22 AJ23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AN4:AZ10 AN11:BA22 AN23:BJ31 AH4:AM31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F8946F-CCC7-4E02-A665-009217A3A62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C317C5A-76F2-4C4B-B79B-EA827DB80A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1023,21 +1023,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.7109375" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="28" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1203,7 +1203,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1371,7 +1371,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1490,6 +1490,9 @@
       </c>
       <c r="AM3" t="s">
         <v>46</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>34</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
@@ -1567,7 +1570,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1686,6 +1689,9 @@
       </c>
       <c r="AM4" t="s">
         <v>46</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>34</v>
       </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
@@ -1763,7 +1769,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1882,6 +1888,9 @@
       </c>
       <c r="AM5" t="s">
         <v>46</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>34</v>
       </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
@@ -1959,7 +1968,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2078,6 +2087,9 @@
       </c>
       <c r="AM6" t="s">
         <v>46</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>34</v>
       </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
@@ -2155,7 +2167,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2274,6 +2286,9 @@
       </c>
       <c r="AM7" t="s">
         <v>46</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>34</v>
       </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
@@ -2351,7 +2366,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2470,6 +2485,9 @@
       </c>
       <c r="AM8" t="s">
         <v>46</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>34</v>
       </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
@@ -2547,7 +2565,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2666,6 +2684,9 @@
       </c>
       <c r="AM9" t="s">
         <v>46</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>34</v>
       </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
@@ -2743,7 +2764,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -2862,6 +2883,9 @@
       </c>
       <c r="AM10" t="s">
         <v>46</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>34</v>
       </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
@@ -2939,7 +2963,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3058,6 +3082,9 @@
       </c>
       <c r="AM11" t="s">
         <v>46</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>34</v>
       </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
@@ -3135,7 +3162,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3254,6 +3281,9 @@
       </c>
       <c r="AM12" t="s">
         <v>46</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>34</v>
       </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
@@ -3331,7 +3361,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3450,6 +3480,9 @@
       </c>
       <c r="AM13" t="s">
         <v>46</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>34</v>
       </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
@@ -3527,7 +3560,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3646,6 +3679,9 @@
       </c>
       <c r="AM14" t="s">
         <v>46</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>34</v>
       </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
@@ -3723,7 +3759,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -3842,6 +3878,9 @@
       </c>
       <c r="AM15" t="s">
         <v>46</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>35</v>
       </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
@@ -3919,7 +3958,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4038,6 +4077,9 @@
       </c>
       <c r="AM16" t="s">
         <v>46</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>34</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -4115,7 +4157,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4234,6 +4276,9 @@
       </c>
       <c r="AM17" t="s">
         <v>46</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>34</v>
       </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
@@ -4311,7 +4356,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4430,6 +4475,9 @@
       </c>
       <c r="AM18" t="s">
         <v>46</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>34</v>
       </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
@@ -4507,7 +4555,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4626,6 +4674,9 @@
       </c>
       <c r="AM19" t="s">
         <v>46</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>34</v>
       </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
@@ -4703,7 +4754,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -4822,6 +4873,9 @@
       </c>
       <c r="AM20" t="s">
         <v>46</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>34</v>
       </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
@@ -4899,7 +4953,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5018,6 +5072,9 @@
       </c>
       <c r="AM21" t="s">
         <v>46</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>34</v>
       </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
@@ -5095,7 +5152,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5214,6 +5271,9 @@
       </c>
       <c r="AM22" t="s">
         <v>46</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>34</v>
       </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
@@ -5291,7 +5351,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5410,6 +5470,9 @@
       </c>
       <c r="AM23" t="s">
         <v>46</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>34</v>
       </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
@@ -5487,7 +5550,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -5606,6 +5669,9 @@
       </c>
       <c r="AM24" t="s">
         <v>46</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>34</v>
       </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
@@ -5683,7 +5749,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -5802,6 +5868,9 @@
       </c>
       <c r="AM25" t="s">
         <v>46</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>34</v>
       </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
@@ -5879,7 +5948,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -5998,6 +6067,9 @@
       </c>
       <c r="AM26" t="s">
         <v>46</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>35</v>
       </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
@@ -6075,7 +6147,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -6194,6 +6266,9 @@
       </c>
       <c r="AM27" t="s">
         <v>46</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>34</v>
       </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
@@ -6271,7 +6346,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -6390,6 +6465,9 @@
       </c>
       <c r="AM28" t="s">
         <v>46</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>34</v>
       </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
@@ -6467,7 +6545,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -6586,6 +6664,9 @@
       </c>
       <c r="AM29" t="s">
         <v>46</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>34</v>
       </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
@@ -6663,7 +6744,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -6782,6 +6863,9 @@
       </c>
       <c r="AM30" t="s">
         <v>46</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>34</v>
       </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
@@ -6859,7 +6943,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -6978,6 +7062,9 @@
       </c>
       <c r="AM31" t="s">
         <v>46</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>34</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -7060,7 +7147,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AN4:AZ10 AN11:BA22 AN23:BJ31 AH4:AM31">
+  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 AN4:AZ4 BE4:BJ10 O4:AB31 AH4:AM31 BK4:DG31 D6:J31 M6:N31 AO11:BA22 BC11:BJ22 AO23:BJ31 AO5:AZ10 AN5:AN31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7073,14 +7160,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7088,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -7096,7 +7183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -7104,7 +7191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -7112,7 +7199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -7120,7 +7207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -7128,7 +7215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -7136,7 +7223,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -7144,7 +7231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -7152,7 +7239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -7160,7 +7247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -7168,7 +7255,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -7176,7 +7263,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -7184,7 +7271,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -7192,7 +7279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -7200,7 +7287,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -7208,7 +7295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -7216,7 +7303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -7224,7 +7311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -7232,7 +7319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -7240,7 +7327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -7248,7 +7335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -7256,7 +7343,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -7264,7 +7351,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -7272,7 +7359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -7280,7 +7367,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -7288,7 +7375,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -7296,7 +7383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -7304,7 +7391,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -7312,7 +7399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -7329,18 +7416,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -7348,7 +7435,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -7357,7 +7444,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -7366,7 +7453,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -7375,7 +7462,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -7384,13 +7471,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -7399,7 +7486,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -7408,7 +7495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -7424,13 +7511,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -7439,7 +7526,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -7448,7 +7535,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -7457,7 +7544,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -7466,7 +7553,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -7475,7 +7562,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -7484,7 +7571,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -7493,7 +7580,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -7502,7 +7589,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -7511,7 +7598,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -7520,7 +7607,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -7529,7 +7616,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -7538,7 +7625,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -7547,25 +7634,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -7574,7 +7661,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -7583,7 +7670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -7592,7 +7679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C317C5A-76F2-4C4B-B79B-EA827DB80A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5553BAEC-B1AD-4373-BBD1-995EB9BB11D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1494,6 +1494,9 @@
       <c r="AN3" t="s">
         <v>34</v>
       </c>
+      <c r="AO3" t="s">
+        <v>34</v>
+      </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -1693,6 +1696,9 @@
       <c r="AN4" t="s">
         <v>34</v>
       </c>
+      <c r="AO4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1892,6 +1898,9 @@
       <c r="AN5" t="s">
         <v>34</v>
       </c>
+      <c r="AO5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -2091,6 +2100,9 @@
       <c r="AN6" t="s">
         <v>34</v>
       </c>
+      <c r="AO6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -2290,6 +2302,9 @@
       <c r="AN7" t="s">
         <v>34</v>
       </c>
+      <c r="AO7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2489,6 +2504,9 @@
       <c r="AN8" t="s">
         <v>34</v>
       </c>
+      <c r="AO8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2688,6 +2706,9 @@
       <c r="AN9" t="s">
         <v>34</v>
       </c>
+      <c r="AO9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2887,6 +2908,9 @@
       <c r="AN10" t="s">
         <v>34</v>
       </c>
+      <c r="AO10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -3086,6 +3110,9 @@
       <c r="AN11" t="s">
         <v>34</v>
       </c>
+      <c r="AO11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -3285,6 +3312,9 @@
       <c r="AN12" t="s">
         <v>34</v>
       </c>
+      <c r="AO12" t="s">
+        <v>34</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3484,6 +3514,9 @@
       <c r="AN13" t="s">
         <v>34</v>
       </c>
+      <c r="AO13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3683,6 +3716,9 @@
       <c r="AN14" t="s">
         <v>34</v>
       </c>
+      <c r="AO14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3882,6 +3918,9 @@
       <c r="AN15" t="s">
         <v>35</v>
       </c>
+      <c r="AO15" t="s">
+        <v>35</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -4081,6 +4120,9 @@
       <c r="AN16" t="s">
         <v>34</v>
       </c>
+      <c r="AO16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -4280,6 +4322,9 @@
       <c r="AN17" t="s">
         <v>34</v>
       </c>
+      <c r="AO17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4479,6 +4524,9 @@
       <c r="AN18" t="s">
         <v>34</v>
       </c>
+      <c r="AO18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4678,6 +4726,9 @@
       <c r="AN19" t="s">
         <v>34</v>
       </c>
+      <c r="AO19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4877,6 +4928,9 @@
       <c r="AN20" t="s">
         <v>34</v>
       </c>
+      <c r="AO20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -5076,6 +5130,9 @@
       <c r="AN21" t="s">
         <v>34</v>
       </c>
+      <c r="AO21" t="s">
+        <v>34</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -5275,6 +5332,9 @@
       <c r="AN22" t="s">
         <v>34</v>
       </c>
+      <c r="AO22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5474,6 +5534,9 @@
       <c r="AN23" t="s">
         <v>34</v>
       </c>
+      <c r="AO23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5673,6 +5736,9 @@
       <c r="AN24" t="s">
         <v>34</v>
       </c>
+      <c r="AO24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5872,6 +5938,9 @@
       <c r="AN25" t="s">
         <v>34</v>
       </c>
+      <c r="AO25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -6071,6 +6140,9 @@
       <c r="AN26" t="s">
         <v>35</v>
       </c>
+      <c r="AO26" t="s">
+        <v>35</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -6270,6 +6342,9 @@
       <c r="AN27" t="s">
         <v>34</v>
       </c>
+      <c r="AO27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -6469,6 +6544,9 @@
       <c r="AN28" t="s">
         <v>34</v>
       </c>
+      <c r="AO28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6668,6 +6746,9 @@
       <c r="AN29" t="s">
         <v>34</v>
       </c>
+      <c r="AO29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6867,6 +6948,9 @@
       <c r="AN30" t="s">
         <v>34</v>
       </c>
+      <c r="AO30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -7066,6 +7150,9 @@
       <c r="AN31" t="s">
         <v>34</v>
       </c>
+      <c r="AO31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -7147,7 +7234,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 D4:N5 AN4:AZ4 BE4:BJ10 O4:AB31 AH4:AM31 BK4:DG31 D6:J31 M6:N31 AO11:BA22 BC11:BJ22 AO23:BJ31 AO5:AZ10 AN5:AN31">
+  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 AN4:AZ4 D4:N5 BE4:BJ10 O4:AB31 AH4:AM31 BK4:DG31 AO5:AZ10 AN5:AN31 D6:J31 M6:N31 AO11:BA22 BC11:BJ22 AO23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5553BAEC-B1AD-4373-BBD1-995EB9BB11D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAE2D38-3FFE-4133-9E00-FEAE1C31E207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1023,21 +1023,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.7109375" customWidth="1"/>
+    <col min="20" max="25" width="7.6640625" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="28" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1152,8 +1152,12 @@
       <c r="AO1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="AP1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -1203,7 +1207,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1326,6 +1330,12 @@
       </c>
       <c r="AO2" s="1">
         <v>46185</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>46190</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>46192</v>
       </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -1371,7 +1381,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1495,6 +1505,9 @@
         <v>34</v>
       </c>
       <c r="AO3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1573,7 +1586,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1697,6 +1710,9 @@
         <v>34</v>
       </c>
       <c r="AO4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP4" t="s">
         <v>34</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1775,7 +1791,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1899,6 +1915,9 @@
         <v>34</v>
       </c>
       <c r="AO5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP5" t="s">
         <v>34</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1977,7 +1996,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2101,6 +2120,9 @@
         <v>34</v>
       </c>
       <c r="AO6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP6" t="s">
         <v>34</v>
       </c>
       <c r="AU6" s="2"/>
@@ -2179,7 +2201,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2303,6 +2325,9 @@
         <v>34</v>
       </c>
       <c r="AO7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP7" t="s">
         <v>34</v>
       </c>
       <c r="AU7" s="2"/>
@@ -2381,7 +2406,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2505,6 +2530,9 @@
         <v>34</v>
       </c>
       <c r="AO8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP8" t="s">
         <v>34</v>
       </c>
       <c r="AU8" s="2"/>
@@ -2583,7 +2611,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2707,6 +2735,9 @@
         <v>34</v>
       </c>
       <c r="AO9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP9" t="s">
         <v>34</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2785,7 +2816,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -2909,6 +2940,9 @@
         <v>34</v>
       </c>
       <c r="AO10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP10" t="s">
         <v>34</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2987,7 +3021,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3111,6 +3145,9 @@
         <v>34</v>
       </c>
       <c r="AO11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP11" t="s">
         <v>34</v>
       </c>
       <c r="AU11" s="2"/>
@@ -3189,7 +3226,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3313,6 +3350,9 @@
         <v>34</v>
       </c>
       <c r="AO12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP12" t="s">
         <v>34</v>
       </c>
       <c r="AU12" s="2"/>
@@ -3391,7 +3431,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3515,6 +3555,9 @@
         <v>34</v>
       </c>
       <c r="AO13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP13" t="s">
         <v>34</v>
       </c>
       <c r="AU13" s="2"/>
@@ -3593,7 +3636,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3717,6 +3760,9 @@
         <v>34</v>
       </c>
       <c r="AO14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP14" t="s">
         <v>34</v>
       </c>
       <c r="AU14" s="2"/>
@@ -3795,7 +3841,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -3920,6 +3966,9 @@
       </c>
       <c r="AO15" t="s">
         <v>35</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>34</v>
       </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
@@ -3997,7 +4046,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4121,6 +4170,9 @@
         <v>34</v>
       </c>
       <c r="AO16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP16" t="s">
         <v>34</v>
       </c>
       <c r="AU16" s="2"/>
@@ -4199,7 +4251,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4323,6 +4375,9 @@
         <v>34</v>
       </c>
       <c r="AO17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP17" t="s">
         <v>34</v>
       </c>
       <c r="AU17" s="2"/>
@@ -4401,7 +4456,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4525,6 +4580,9 @@
         <v>34</v>
       </c>
       <c r="AO18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP18" t="s">
         <v>34</v>
       </c>
       <c r="AU18" s="2"/>
@@ -4603,7 +4661,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4727,6 +4785,9 @@
         <v>34</v>
       </c>
       <c r="AO19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP19" t="s">
         <v>34</v>
       </c>
       <c r="AU19" s="2"/>
@@ -4805,7 +4866,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -4929,6 +4990,9 @@
         <v>34</v>
       </c>
       <c r="AO20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP20" t="s">
         <v>34</v>
       </c>
       <c r="AU20" s="2"/>
@@ -5007,7 +5071,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5131,6 +5195,9 @@
         <v>34</v>
       </c>
       <c r="AO21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP21" t="s">
         <v>34</v>
       </c>
       <c r="AU21" s="2"/>
@@ -5209,7 +5276,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5334,6 +5401,9 @@
       </c>
       <c r="AO22" t="s">
         <v>34</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>40</v>
       </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
@@ -5411,7 +5481,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5535,6 +5605,9 @@
         <v>34</v>
       </c>
       <c r="AO23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP23" t="s">
         <v>34</v>
       </c>
       <c r="AU23" s="2"/>
@@ -5613,7 +5686,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -5737,6 +5810,9 @@
         <v>34</v>
       </c>
       <c r="AO24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP24" t="s">
         <v>34</v>
       </c>
       <c r="AU24" s="2"/>
@@ -5815,7 +5891,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -5939,6 +6015,9 @@
         <v>34</v>
       </c>
       <c r="AO25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP25" t="s">
         <v>34</v>
       </c>
       <c r="AU25" s="2"/>
@@ -6017,7 +6096,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6142,6 +6221,9 @@
       </c>
       <c r="AO26" t="s">
         <v>35</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>34</v>
       </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
@@ -6219,7 +6301,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -6343,6 +6425,9 @@
         <v>34</v>
       </c>
       <c r="AO27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP27" t="s">
         <v>34</v>
       </c>
       <c r="AU27" s="2"/>
@@ -6421,7 +6506,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -6545,6 +6630,9 @@
         <v>34</v>
       </c>
       <c r="AO28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP28" t="s">
         <v>34</v>
       </c>
       <c r="AU28" s="2"/>
@@ -6623,7 +6711,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -6747,6 +6835,9 @@
         <v>34</v>
       </c>
       <c r="AO29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP29" t="s">
         <v>34</v>
       </c>
       <c r="AU29" s="2"/>
@@ -6825,7 +6916,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -6949,6 +7040,9 @@
         <v>34</v>
       </c>
       <c r="AO30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP30" t="s">
         <v>34</v>
       </c>
       <c r="AU30" s="2"/>
@@ -7027,7 +7121,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -7151,6 +7245,9 @@
         <v>34</v>
       </c>
       <c r="AO31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP31" t="s">
         <v>34</v>
       </c>
       <c r="AU31" s="2"/>
@@ -7247,14 +7344,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7262,7 +7359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -7270,7 +7367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -7278,7 +7375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -7286,7 +7383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -7294,7 +7391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -7302,7 +7399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -7310,7 +7407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -7318,7 +7415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -7326,7 +7423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -7334,7 +7431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -7342,7 +7439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -7350,7 +7447,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -7358,7 +7455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -7366,7 +7463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -7374,7 +7471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -7382,7 +7479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -7390,7 +7487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -7398,7 +7495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -7406,7 +7503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -7414,7 +7511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -7422,7 +7519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -7430,7 +7527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -7438,7 +7535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -7446,7 +7543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -7454,7 +7551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -7462,7 +7559,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -7470,7 +7567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -7478,7 +7575,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -7486,7 +7583,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -7503,18 +7600,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -7522,7 +7619,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -7531,7 +7628,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -7540,7 +7637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -7549,7 +7646,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -7558,13 +7655,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -7573,7 +7670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -7582,7 +7679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -7598,13 +7695,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -7613,7 +7710,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -7622,7 +7719,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -7631,7 +7728,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -7640,7 +7737,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -7649,7 +7746,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -7658,7 +7755,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -7667,7 +7764,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -7676,7 +7773,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -7685,7 +7782,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -7694,7 +7791,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -7703,7 +7800,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -7712,7 +7809,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -7721,25 +7818,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -7748,7 +7845,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -7757,7 +7854,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -7766,7 +7863,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAE2D38-3FFE-4133-9E00-FEAE1C31E207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AD666E-E069-4DC2-A065-180103D9CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Feriado</t>
+  </si>
+  <si>
+    <t>FÉRIAS</t>
   </si>
 </sst>
 </file>
@@ -1158,9 +1161,15 @@
       <c r="AQ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
+      <c r="AR1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AU1" s="3"/>
       <c r="AV1" s="3"/>
       <c r="AW1" s="3"/>
@@ -1337,28 +1346,39 @@
       <c r="AQ2" s="1">
         <v>46192</v>
       </c>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
+      <c r="AR2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>46227</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>46232</v>
+      </c>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
       <c r="BS2" s="5"/>
       <c r="BT2" s="5"/>
       <c r="BU2" s="5"/>
@@ -1508,6 +1528,15 @@
         <v>34</v>
       </c>
       <c r="AP3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT3" t="s">
         <v>34</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1715,6 +1744,15 @@
       <c r="AP4" t="s">
         <v>34</v>
       </c>
+      <c r="AQ4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>34</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1920,6 +1958,15 @@
       <c r="AP5" t="s">
         <v>34</v>
       </c>
+      <c r="AQ5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>34</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -2125,6 +2172,15 @@
       <c r="AP6" t="s">
         <v>34</v>
       </c>
+      <c r="AQ6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>34</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -2330,6 +2386,15 @@
       <c r="AP7" t="s">
         <v>34</v>
       </c>
+      <c r="AQ7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>34</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -2535,6 +2600,15 @@
       <c r="AP8" t="s">
         <v>34</v>
       </c>
+      <c r="AQ8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>34</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2740,6 +2814,15 @@
       <c r="AP9" t="s">
         <v>34</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>34</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2945,6 +3028,15 @@
       <c r="AP10" t="s">
         <v>34</v>
       </c>
+      <c r="AQ10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>34</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -3150,6 +3242,15 @@
       <c r="AP11" t="s">
         <v>34</v>
       </c>
+      <c r="AQ11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>34</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -3355,6 +3456,18 @@
       <c r="AP12" t="s">
         <v>34</v>
       </c>
+      <c r="AQ12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>35</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -3560,6 +3673,15 @@
       <c r="AP13" t="s">
         <v>34</v>
       </c>
+      <c r="AQ13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>34</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3765,6 +3887,15 @@
       <c r="AP14" t="s">
         <v>34</v>
       </c>
+      <c r="AQ14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>34</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3970,6 +4101,15 @@
       <c r="AP15" t="s">
         <v>34</v>
       </c>
+      <c r="AQ15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>34</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -4175,6 +4315,15 @@
       <c r="AP16" t="s">
         <v>34</v>
       </c>
+      <c r="AQ16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>34</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -4380,6 +4529,15 @@
       <c r="AP17" t="s">
         <v>34</v>
       </c>
+      <c r="AQ17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>34</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -4585,6 +4743,15 @@
       <c r="AP18" t="s">
         <v>34</v>
       </c>
+      <c r="AQ18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>34</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4790,6 +4957,15 @@
       <c r="AP19" t="s">
         <v>34</v>
       </c>
+      <c r="AQ19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>34</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4995,6 +5171,15 @@
       <c r="AP20" t="s">
         <v>34</v>
       </c>
+      <c r="AQ20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>34</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -5200,6 +5385,15 @@
       <c r="AP21" t="s">
         <v>34</v>
       </c>
+      <c r="AQ21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>35</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -5405,6 +5599,15 @@
       <c r="AP22" t="s">
         <v>40</v>
       </c>
+      <c r="AQ22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>34</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -5610,6 +5813,15 @@
       <c r="AP23" t="s">
         <v>34</v>
       </c>
+      <c r="AQ23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>34</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5815,6 +6027,15 @@
       <c r="AP24" t="s">
         <v>34</v>
       </c>
+      <c r="AQ24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>34</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -6020,6 +6241,15 @@
       <c r="AP25" t="s">
         <v>34</v>
       </c>
+      <c r="AQ25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>34</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -6225,6 +6455,15 @@
       <c r="AP26" t="s">
         <v>34</v>
       </c>
+      <c r="AQ26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>34</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -6430,6 +6669,15 @@
       <c r="AP27" t="s">
         <v>34</v>
       </c>
+      <c r="AQ27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>34</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -6635,6 +6883,15 @@
       <c r="AP28" t="s">
         <v>34</v>
       </c>
+      <c r="AQ28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>34</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6840,6 +7097,15 @@
       <c r="AP29" t="s">
         <v>34</v>
       </c>
+      <c r="AQ29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>34</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -7045,6 +7311,15 @@
       <c r="AP30" t="s">
         <v>34</v>
       </c>
+      <c r="AQ30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>34</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -7250,6 +7525,15 @@
       <c r="AP31" t="s">
         <v>34</v>
       </c>
+      <c r="AQ31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>34</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -7331,7 +7615,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AH3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AG31 AN4:AZ4 D4:N5 BE4:BJ10 O4:AB31 AH4:AM31 BK4:DG31 AO5:AZ10 AN5:AN31 D6:J31 M6:N31 AO11:BA22 BC11:BJ22 AO23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AS23:BJ31 AS11:BA22 AS3:AZ10 AC3:AQ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AD666E-E069-4DC2-A065-180103D9CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824E6632-B25A-484C-B2D6-F8BF0D76AA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3466,7 +3466,7 @@
         <v>35</v>
       </c>
       <c r="AT12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
@@ -7615,7 +7615,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AS23:BJ31 AS11:BA22 AS3:AZ10 AC3:AQ31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AS3:AZ10 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AS11:BA22 BC11:BJ22 AS23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824E6632-B25A-484C-B2D6-F8BF0D76AA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D469E2-E6DD-4C4E-876A-87B00B61A327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -683,7 +683,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -692,6 +692,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1026,21 +1033,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.7109375" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="28" max="46" width="7.7109375" customWidth="1"/>
+    <col min="47" max="47" width="7.7109375" style="8" customWidth="1"/>
+    <col min="48" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1164,13 +1173,15 @@
       <c r="AR1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="10" t="s">
         <v>33</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="3"/>
+      <c r="AU1" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="AV1" s="3"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="1"/>
@@ -1216,7 +1227,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1355,7 +1366,9 @@
       <c r="AT2" s="1">
         <v>46232</v>
       </c>
-      <c r="AU2" s="1"/>
+      <c r="AU2" s="9">
+        <v>46234</v>
+      </c>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
@@ -1401,7 +1414,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1539,7 +1552,9 @@
       <c r="AT3" t="s">
         <v>34</v>
       </c>
-      <c r="AU3" s="2"/>
+      <c r="AU3" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
       <c r="AZ3" s="5"/>
@@ -1615,7 +1630,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1753,7 +1768,9 @@
       <c r="AT4" t="s">
         <v>34</v>
       </c>
-      <c r="AU4" s="2"/>
+      <c r="AU4" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AZ4" s="5"/>
@@ -1829,7 +1846,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1967,7 +1984,9 @@
       <c r="AT5" t="s">
         <v>34</v>
       </c>
-      <c r="AU5" s="2"/>
+      <c r="AU5" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AZ5" s="5"/>
@@ -2043,7 +2062,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2181,7 +2200,9 @@
       <c r="AT6" t="s">
         <v>34</v>
       </c>
-      <c r="AU6" s="2"/>
+      <c r="AU6" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AZ6" s="5"/>
@@ -2257,7 +2278,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2395,7 +2416,9 @@
       <c r="AT7" t="s">
         <v>34</v>
       </c>
-      <c r="AU7" s="2"/>
+      <c r="AU7" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AZ7" s="5"/>
@@ -2471,7 +2494,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2609,7 +2632,9 @@
       <c r="AT8" t="s">
         <v>34</v>
       </c>
-      <c r="AU8" s="2"/>
+      <c r="AU8" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AZ8" s="5"/>
@@ -2685,7 +2710,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2823,7 +2848,9 @@
       <c r="AT9" t="s">
         <v>34</v>
       </c>
-      <c r="AU9" s="2"/>
+      <c r="AU9" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AZ9" s="5"/>
@@ -2899,7 +2926,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3037,7 +3064,9 @@
       <c r="AT10" t="s">
         <v>34</v>
       </c>
-      <c r="AU10" s="2"/>
+      <c r="AU10" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AZ10" s="5"/>
@@ -3113,7 +3142,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3251,7 +3280,9 @@
       <c r="AT11" t="s">
         <v>34</v>
       </c>
-      <c r="AU11" s="2"/>
+      <c r="AU11" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AZ11" s="5"/>
@@ -3327,7 +3358,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3468,7 +3499,9 @@
       <c r="AT12" t="s">
         <v>34</v>
       </c>
-      <c r="AU12" s="2"/>
+      <c r="AU12" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AZ12" s="5"/>
@@ -3544,7 +3577,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3682,7 +3715,9 @@
       <c r="AT13" t="s">
         <v>34</v>
       </c>
-      <c r="AU13" s="2"/>
+      <c r="AU13" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AZ13" s="5"/>
@@ -3758,7 +3793,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3896,7 +3931,9 @@
       <c r="AT14" t="s">
         <v>34</v>
       </c>
-      <c r="AU14" s="2"/>
+      <c r="AU14" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AZ14" s="5"/>
@@ -3972,7 +4009,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4110,7 +4147,9 @@
       <c r="AT15" t="s">
         <v>34</v>
       </c>
-      <c r="AU15" s="2"/>
+      <c r="AU15" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AZ15" s="5"/>
@@ -4186,7 +4225,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4324,7 +4363,9 @@
       <c r="AT16" t="s">
         <v>34</v>
       </c>
-      <c r="AU16" s="2"/>
+      <c r="AU16" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AZ16" s="5"/>
@@ -4400,7 +4441,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4538,7 +4579,9 @@
       <c r="AT17" t="s">
         <v>34</v>
       </c>
-      <c r="AU17" s="2"/>
+      <c r="AU17" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AZ17" s="5"/>
@@ -4614,7 +4657,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4752,7 +4795,9 @@
       <c r="AT18" t="s">
         <v>34</v>
       </c>
-      <c r="AU18" s="2"/>
+      <c r="AU18" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AZ18" s="5"/>
@@ -4828,7 +4873,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -4966,7 +5011,9 @@
       <c r="AT19" t="s">
         <v>34</v>
       </c>
-      <c r="AU19" s="2"/>
+      <c r="AU19" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AZ19" s="5"/>
@@ -5042,7 +5089,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5180,7 +5227,9 @@
       <c r="AT20" t="s">
         <v>34</v>
       </c>
-      <c r="AU20" s="2"/>
+      <c r="AU20" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AZ20" s="5"/>
@@ -5256,7 +5305,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5394,7 +5443,9 @@
       <c r="AT21" t="s">
         <v>35</v>
       </c>
-      <c r="AU21" s="2"/>
+      <c r="AU21" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AZ21" s="5"/>
@@ -5470,7 +5521,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5608,7 +5659,9 @@
       <c r="AT22" t="s">
         <v>34</v>
       </c>
-      <c r="AU22" s="2"/>
+      <c r="AU22" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AZ22" s="5"/>
@@ -5684,7 +5737,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5822,7 +5875,9 @@
       <c r="AT23" t="s">
         <v>34</v>
       </c>
-      <c r="AU23" s="2"/>
+      <c r="AU23" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AZ23" s="5"/>
@@ -5898,7 +5953,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6036,7 +6091,9 @@
       <c r="AT24" t="s">
         <v>34</v>
       </c>
-      <c r="AU24" s="2"/>
+      <c r="AU24" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AZ24" s="5"/>
@@ -6112,7 +6169,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6250,7 +6307,9 @@
       <c r="AT25" t="s">
         <v>34</v>
       </c>
-      <c r="AU25" s="2"/>
+      <c r="AU25" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AZ25" s="5"/>
@@ -6326,7 +6385,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6464,7 +6523,9 @@
       <c r="AT26" t="s">
         <v>34</v>
       </c>
-      <c r="AU26" s="2"/>
+      <c r="AU26" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AZ26" s="5"/>
@@ -6540,7 +6601,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -6678,7 +6739,9 @@
       <c r="AT27" t="s">
         <v>34</v>
       </c>
-      <c r="AU27" s="2"/>
+      <c r="AU27" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AZ27" s="5"/>
@@ -6754,7 +6817,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -6892,7 +6955,9 @@
       <c r="AT28" t="s">
         <v>34</v>
       </c>
-      <c r="AU28" s="2"/>
+      <c r="AU28" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AZ28" s="5"/>
@@ -6968,7 +7033,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7106,7 +7171,9 @@
       <c r="AT29" t="s">
         <v>34</v>
       </c>
-      <c r="AU29" s="2"/>
+      <c r="AU29" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AZ29" s="5"/>
@@ -7182,7 +7249,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7320,7 +7387,9 @@
       <c r="AT30" t="s">
         <v>34</v>
       </c>
-      <c r="AU30" s="2"/>
+      <c r="AU30" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AZ30" s="5"/>
@@ -7396,7 +7465,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -7534,7 +7603,9 @@
       <c r="AT31" t="s">
         <v>34</v>
       </c>
-      <c r="AU31" s="2"/>
+      <c r="AU31" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
       <c r="AZ31" s="5"/>
@@ -7628,14 +7699,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7643,7 +7714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -7651,7 +7722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -7659,7 +7730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -7667,7 +7738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -7675,7 +7746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -7683,7 +7754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -7691,7 +7762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -7699,7 +7770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -7707,7 +7778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -7715,7 +7786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -7723,7 +7794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -7731,7 +7802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -7739,7 +7810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -7747,7 +7818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -7755,7 +7826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -7763,7 +7834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -7771,7 +7842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -7779,7 +7850,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -7787,7 +7858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -7795,7 +7866,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -7803,7 +7874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -7811,7 +7882,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -7819,7 +7890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -7827,7 +7898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -7835,7 +7906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -7843,7 +7914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -7851,7 +7922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -7859,7 +7930,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -7867,7 +7938,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -7884,18 +7955,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -7903,7 +7974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -7912,7 +7983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -7921,7 +7992,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -7930,7 +8001,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -7939,13 +8010,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -7954,7 +8025,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -7963,7 +8034,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -7979,13 +8050,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -7994,7 +8065,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8003,7 +8074,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8012,7 +8083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8021,7 +8092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8030,7 +8101,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8039,7 +8110,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8048,7 +8119,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8057,7 +8128,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8066,7 +8137,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8075,7 +8146,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8084,7 +8155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8093,7 +8164,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8102,25 +8173,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8129,7 +8200,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8138,7 +8209,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8147,7 +8218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D469E2-E6DD-4C4E-876A-87B00B61A327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB8B95C-1213-41B0-8781-A4C773AA7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -683,7 +683,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -692,10 +692,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1042,9 +1038,7 @@
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="25" width="7.7109375" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="46" width="7.7109375" customWidth="1"/>
-    <col min="47" max="47" width="7.7109375" style="8" customWidth="1"/>
-    <col min="48" max="50" width="7.7109375" customWidth="1"/>
+    <col min="28" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
@@ -1173,16 +1167,18 @@
       <c r="AR1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AS1" s="10" t="s">
+      <c r="AS1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="9" t="s">
+      <c r="AU1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AV1" s="3"/>
+      <c r="AV1" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="AW1" s="3"/>
       <c r="AX1" s="1"/>
       <c r="AY1" s="4"/>
@@ -1366,10 +1362,12 @@
       <c r="AT2" s="1">
         <v>46232</v>
       </c>
-      <c r="AU2" s="9">
+      <c r="AU2" s="8">
         <v>46234</v>
       </c>
-      <c r="AV2" s="1"/>
+      <c r="AV2" s="1">
+        <v>46239</v>
+      </c>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
@@ -1552,10 +1550,12 @@
       <c r="AT3" t="s">
         <v>34</v>
       </c>
-      <c r="AU3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV3" s="2"/>
+      <c r="AU3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>34</v>
+      </c>
       <c r="AW3" s="2"/>
       <c r="AZ3" s="5"/>
       <c r="BA3" s="5"/>
@@ -1768,10 +1768,12 @@
       <c r="AT4" t="s">
         <v>34</v>
       </c>
-      <c r="AU4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV4" s="2"/>
+      <c r="AU4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>34</v>
+      </c>
       <c r="AW4" s="2"/>
       <c r="AZ4" s="5"/>
       <c r="BA4" s="5"/>
@@ -1984,10 +1986,12 @@
       <c r="AT5" t="s">
         <v>34</v>
       </c>
-      <c r="AU5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV5" s="2"/>
+      <c r="AU5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>34</v>
+      </c>
       <c r="AW5" s="2"/>
       <c r="AZ5" s="5"/>
       <c r="BA5" s="5"/>
@@ -2200,10 +2204,12 @@
       <c r="AT6" t="s">
         <v>34</v>
       </c>
-      <c r="AU6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV6" s="2"/>
+      <c r="AU6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>34</v>
+      </c>
       <c r="AW6" s="2"/>
       <c r="AZ6" s="5"/>
       <c r="BA6" s="5"/>
@@ -2416,10 +2422,12 @@
       <c r="AT7" t="s">
         <v>34</v>
       </c>
-      <c r="AU7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV7" s="2"/>
+      <c r="AU7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>34</v>
+      </c>
       <c r="AW7" s="2"/>
       <c r="AZ7" s="5"/>
       <c r="BA7" s="5"/>
@@ -2632,10 +2640,12 @@
       <c r="AT8" t="s">
         <v>34</v>
       </c>
-      <c r="AU8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV8" s="2"/>
+      <c r="AU8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>34</v>
+      </c>
       <c r="AW8" s="2"/>
       <c r="AZ8" s="5"/>
       <c r="BA8" s="5"/>
@@ -2848,10 +2858,12 @@
       <c r="AT9" t="s">
         <v>34</v>
       </c>
-      <c r="AU9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV9" s="2"/>
+      <c r="AU9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>34</v>
+      </c>
       <c r="AW9" s="2"/>
       <c r="AZ9" s="5"/>
       <c r="BA9" s="5"/>
@@ -3064,10 +3076,12 @@
       <c r="AT10" t="s">
         <v>34</v>
       </c>
-      <c r="AU10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV10" s="2"/>
+      <c r="AU10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>34</v>
+      </c>
       <c r="AW10" s="2"/>
       <c r="AZ10" s="5"/>
       <c r="BA10" s="5"/>
@@ -3280,10 +3294,12 @@
       <c r="AT11" t="s">
         <v>34</v>
       </c>
-      <c r="AU11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV11" s="2"/>
+      <c r="AU11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>34</v>
+      </c>
       <c r="AW11" s="2"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="5"/>
@@ -3499,10 +3515,12 @@
       <c r="AT12" t="s">
         <v>34</v>
       </c>
-      <c r="AU12" s="8" t="s">
+      <c r="AU12" t="s">
         <v>35</v>
       </c>
-      <c r="AV12" s="2"/>
+      <c r="AV12" t="s">
+        <v>34</v>
+      </c>
       <c r="AW12" s="2"/>
       <c r="AZ12" s="5"/>
       <c r="BA12" s="5"/>
@@ -3715,10 +3733,12 @@
       <c r="AT13" t="s">
         <v>34</v>
       </c>
-      <c r="AU13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV13" s="2"/>
+      <c r="AU13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>34</v>
+      </c>
       <c r="AW13" s="2"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="5"/>
@@ -3931,10 +3951,12 @@
       <c r="AT14" t="s">
         <v>34</v>
       </c>
-      <c r="AU14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV14" s="2"/>
+      <c r="AU14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>35</v>
+      </c>
       <c r="AW14" s="2"/>
       <c r="AZ14" s="5"/>
       <c r="BA14" s="5"/>
@@ -4147,10 +4169,12 @@
       <c r="AT15" t="s">
         <v>34</v>
       </c>
-      <c r="AU15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV15" s="2"/>
+      <c r="AU15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>34</v>
+      </c>
       <c r="AW15" s="2"/>
       <c r="AZ15" s="5"/>
       <c r="BA15" s="5"/>
@@ -4363,10 +4387,12 @@
       <c r="AT16" t="s">
         <v>34</v>
       </c>
-      <c r="AU16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV16" s="2"/>
+      <c r="AU16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>34</v>
+      </c>
       <c r="AW16" s="2"/>
       <c r="AZ16" s="5"/>
       <c r="BA16" s="5"/>
@@ -4579,10 +4605,12 @@
       <c r="AT17" t="s">
         <v>34</v>
       </c>
-      <c r="AU17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV17" s="2"/>
+      <c r="AU17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>34</v>
+      </c>
       <c r="AW17" s="2"/>
       <c r="AZ17" s="5"/>
       <c r="BA17" s="5"/>
@@ -4795,10 +4823,12 @@
       <c r="AT18" t="s">
         <v>34</v>
       </c>
-      <c r="AU18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV18" s="2"/>
+      <c r="AU18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>34</v>
+      </c>
       <c r="AW18" s="2"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="5"/>
@@ -5011,10 +5041,12 @@
       <c r="AT19" t="s">
         <v>34</v>
       </c>
-      <c r="AU19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV19" s="2"/>
+      <c r="AU19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>34</v>
+      </c>
       <c r="AW19" s="2"/>
       <c r="AZ19" s="5"/>
       <c r="BA19" s="5"/>
@@ -5227,10 +5259,12 @@
       <c r="AT20" t="s">
         <v>34</v>
       </c>
-      <c r="AU20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV20" s="2"/>
+      <c r="AU20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>34</v>
+      </c>
       <c r="AW20" s="2"/>
       <c r="AZ20" s="5"/>
       <c r="BA20" s="5"/>
@@ -5443,10 +5477,12 @@
       <c r="AT21" t="s">
         <v>35</v>
       </c>
-      <c r="AU21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV21" s="2"/>
+      <c r="AU21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>34</v>
+      </c>
       <c r="AW21" s="2"/>
       <c r="AZ21" s="5"/>
       <c r="BA21" s="5"/>
@@ -5659,10 +5695,12 @@
       <c r="AT22" t="s">
         <v>34</v>
       </c>
-      <c r="AU22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV22" s="2"/>
+      <c r="AU22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>34</v>
+      </c>
       <c r="AW22" s="2"/>
       <c r="AZ22" s="5"/>
       <c r="BA22" s="5"/>
@@ -5875,10 +5913,12 @@
       <c r="AT23" t="s">
         <v>34</v>
       </c>
-      <c r="AU23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV23" s="2"/>
+      <c r="AU23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>34</v>
+      </c>
       <c r="AW23" s="2"/>
       <c r="AZ23" s="5"/>
       <c r="BA23" s="5"/>
@@ -6091,10 +6131,12 @@
       <c r="AT24" t="s">
         <v>34</v>
       </c>
-      <c r="AU24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV24" s="2"/>
+      <c r="AU24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>34</v>
+      </c>
       <c r="AW24" s="2"/>
       <c r="AZ24" s="5"/>
       <c r="BA24" s="5"/>
@@ -6307,10 +6349,12 @@
       <c r="AT25" t="s">
         <v>34</v>
       </c>
-      <c r="AU25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV25" s="2"/>
+      <c r="AU25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>34</v>
+      </c>
       <c r="AW25" s="2"/>
       <c r="AZ25" s="5"/>
       <c r="BA25" s="5"/>
@@ -6523,10 +6567,12 @@
       <c r="AT26" t="s">
         <v>34</v>
       </c>
-      <c r="AU26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV26" s="2"/>
+      <c r="AU26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>34</v>
+      </c>
       <c r="AW26" s="2"/>
       <c r="AZ26" s="5"/>
       <c r="BA26" s="5"/>
@@ -6739,10 +6785,12 @@
       <c r="AT27" t="s">
         <v>34</v>
       </c>
-      <c r="AU27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV27" s="2"/>
+      <c r="AU27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>34</v>
+      </c>
       <c r="AW27" s="2"/>
       <c r="AZ27" s="5"/>
       <c r="BA27" s="5"/>
@@ -6955,10 +7003,12 @@
       <c r="AT28" t="s">
         <v>34</v>
       </c>
-      <c r="AU28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV28" s="2"/>
+      <c r="AU28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>34</v>
+      </c>
       <c r="AW28" s="2"/>
       <c r="AZ28" s="5"/>
       <c r="BA28" s="5"/>
@@ -7171,10 +7221,12 @@
       <c r="AT29" t="s">
         <v>34</v>
       </c>
-      <c r="AU29" s="8" t="s">
+      <c r="AU29" t="s">
         <v>35</v>
       </c>
-      <c r="AV29" s="2"/>
+      <c r="AV29" t="s">
+        <v>34</v>
+      </c>
       <c r="AW29" s="2"/>
       <c r="AZ29" s="5"/>
       <c r="BA29" s="5"/>
@@ -7387,10 +7439,12 @@
       <c r="AT30" t="s">
         <v>34</v>
       </c>
-      <c r="AU30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV30" s="2"/>
+      <c r="AU30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>34</v>
+      </c>
       <c r="AW30" s="2"/>
       <c r="AZ30" s="5"/>
       <c r="BA30" s="5"/>
@@ -7603,10 +7657,12 @@
       <c r="AT31" t="s">
         <v>34</v>
       </c>
-      <c r="AU31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV31" s="2"/>
+      <c r="AU31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>34</v>
+      </c>
       <c r="AW31" s="2"/>
       <c r="AZ31" s="5"/>
       <c r="BA31" s="5"/>
@@ -7686,7 +7742,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 AS3:AZ10 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AS11:BA22 BC11:BJ22 AS23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AS3:AZ3 AW4:AZ10 AW23:BJ31 AW11:BA22 AS4:AV31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB8B95C-1213-41B0-8781-A4C773AA7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A11B778-169E-4259-B926-02E637A6C0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -683,11 +683,10 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1029,21 +1028,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.7109375" customWidth="1"/>
+    <col min="20" max="25" width="7.6640625" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="28" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="4" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1167,63 +1166,63 @@
       <c r="AR1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AS1" s="8" t="s">
+      <c r="AS1" s="7" t="s">
         <v>33</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="8" t="s">
+      <c r="AU1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AV1" s="8" t="s">
+      <c r="AV1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
+      <c r="AW1" s="7"/>
+      <c r="AX1" s="7"/>
+      <c r="AY1" s="7"/>
+      <c r="AZ1" s="7"/>
+      <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
+      <c r="BC1" s="7"/>
+      <c r="BD1" s="7"/>
+      <c r="BE1" s="7"/>
+      <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
+      <c r="BH1" s="7"/>
+      <c r="BI1" s="7"/>
+      <c r="BJ1" s="7"/>
+      <c r="BK1" s="7"/>
+      <c r="BL1" s="7"/>
+      <c r="BM1" s="7"/>
+      <c r="BN1" s="7"/>
+      <c r="BO1" s="7"/>
+      <c r="BP1" s="7"/>
+      <c r="BQ1" s="7"/>
+      <c r="BR1" s="7"/>
+      <c r="BS1" s="3"/>
+      <c r="BT1" s="3"/>
+      <c r="BU1" s="3"/>
+      <c r="BV1" s="3"/>
+      <c r="BW1" s="3"/>
+      <c r="BX1" s="3"/>
+      <c r="BY1" s="3"/>
+      <c r="BZ1" s="3"/>
+      <c r="CA1" s="3"/>
+      <c r="CB1" s="3"/>
+      <c r="CC1" s="3"/>
+      <c r="CD1" s="3"/>
+      <c r="CE1" s="3"/>
+      <c r="CF1" s="3"/>
+      <c r="CG1" s="3"/>
       <c r="CH1" s="1"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-    </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="CI1" s="3"/>
+      <c r="CJ1" s="3"/>
+      <c r="CK1" s="3"/>
+      <c r="CL1" s="3"/>
+      <c r="CM1" s="3"/>
+    </row>
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1362,57 +1361,57 @@
       <c r="AT2" s="1">
         <v>46232</v>
       </c>
-      <c r="AU2" s="8">
+      <c r="AU2" s="7">
         <v>46234</v>
       </c>
       <c r="AV2" s="1">
         <v>46239</v>
       </c>
-      <c r="AW2" s="1"/>
+      <c r="AW2" s="7"/>
       <c r="AX2" s="1"/>
-      <c r="AY2" s="1"/>
+      <c r="AY2" s="7"/>
       <c r="AZ2" s="1"/>
-      <c r="BA2" s="1"/>
+      <c r="BA2" s="7"/>
       <c r="BB2" s="1"/>
-      <c r="BC2" s="1"/>
+      <c r="BC2" s="7"/>
       <c r="BD2" s="1"/>
-      <c r="BE2" s="1"/>
+      <c r="BE2" s="7"/>
       <c r="BF2" s="1"/>
-      <c r="BG2" s="1"/>
+      <c r="BG2" s="7"/>
       <c r="BH2" s="1"/>
-      <c r="BI2" s="1"/>
+      <c r="BI2" s="7"/>
       <c r="BJ2" s="1"/>
-      <c r="BK2" s="1"/>
+      <c r="BK2" s="7"/>
       <c r="BL2" s="1"/>
-      <c r="BM2" s="1"/>
+      <c r="BM2" s="7"/>
       <c r="BN2" s="1"/>
-      <c r="BO2" s="1"/>
+      <c r="BO2" s="7"/>
       <c r="BP2" s="1"/>
-      <c r="BQ2" s="1"/>
+      <c r="BQ2" s="7"/>
       <c r="BR2" s="1"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
-      <c r="CL2" s="5"/>
-      <c r="CM2" s="5"/>
-    </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="BS2" s="4"/>
+      <c r="BT2" s="4"/>
+      <c r="BU2" s="4"/>
+      <c r="BV2" s="4"/>
+      <c r="BW2" s="4"/>
+      <c r="BX2" s="4"/>
+      <c r="BY2" s="4"/>
+      <c r="BZ2" s="4"/>
+      <c r="CA2" s="4"/>
+      <c r="CB2" s="4"/>
+      <c r="CC2" s="4"/>
+      <c r="CD2" s="4"/>
+      <c r="CE2" s="4"/>
+      <c r="CF2" s="4"/>
+      <c r="CG2" s="4"/>
+      <c r="CH2" s="4"/>
+      <c r="CI2" s="4"/>
+      <c r="CJ2" s="4"/>
+      <c r="CK2" s="4"/>
+      <c r="CL2" s="4"/>
+      <c r="CM2" s="4"/>
+    </row>
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1557,80 +1556,80 @@
         <v>34</v>
       </c>
       <c r="AW3" s="2"/>
-      <c r="AZ3" s="5"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="5"/>
-      <c r="BM3" s="5"/>
-      <c r="BN3" s="5"/>
-      <c r="BO3" s="5"/>
-      <c r="BP3" s="5"/>
-      <c r="BQ3" s="5"/>
-      <c r="BR3" s="5"/>
-      <c r="BS3" s="5"/>
-      <c r="BT3" s="5"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="5"/>
-      <c r="BZ3" s="5"/>
-      <c r="CA3" s="5"/>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="5"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="5"/>
-      <c r="CG3" s="5"/>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
-      <c r="CK3" s="5"/>
-      <c r="CL3" s="5"/>
-      <c r="CM3" s="5"/>
-      <c r="CN3" s="5"/>
-      <c r="CO3" s="5"/>
-      <c r="CP3" s="5"/>
-      <c r="CQ3" s="5"/>
-      <c r="CR3" s="5"/>
-      <c r="CS3" s="5"/>
-      <c r="CT3" s="5"/>
-      <c r="CU3" s="5"/>
-      <c r="CV3" s="5"/>
-      <c r="CW3" s="5"/>
-      <c r="CX3" s="5"/>
-      <c r="CY3" s="5"/>
-      <c r="CZ3" s="5"/>
-      <c r="DA3" s="5"/>
-      <c r="DB3" s="5"/>
-      <c r="DC3" s="5"/>
-      <c r="DD3" s="5"/>
-      <c r="DE3" s="5"/>
-      <c r="DF3" s="5"/>
-      <c r="DG3" s="5"/>
-      <c r="DH3" s="5"/>
-      <c r="DI3" s="5"/>
-      <c r="DJ3" s="5"/>
-      <c r="DK3" s="5"/>
-      <c r="DL3" s="5"/>
-      <c r="DM3" s="5"/>
-      <c r="DN3" s="5"/>
-      <c r="DO3" s="5"/>
-      <c r="DP3" s="5"/>
-      <c r="DQ3" s="5"/>
-      <c r="DR3" s="5"/>
-      <c r="DS3" s="5"/>
-    </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ3" s="4"/>
+      <c r="BA3" s="4"/>
+      <c r="BB3" s="4"/>
+      <c r="BC3" s="4"/>
+      <c r="BD3" s="4"/>
+      <c r="BE3" s="4"/>
+      <c r="BF3" s="4"/>
+      <c r="BG3" s="4"/>
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
+      <c r="BN3" s="4"/>
+      <c r="BO3" s="4"/>
+      <c r="BP3" s="4"/>
+      <c r="BQ3" s="4"/>
+      <c r="BR3" s="4"/>
+      <c r="BS3" s="4"/>
+      <c r="BT3" s="4"/>
+      <c r="BU3" s="4"/>
+      <c r="BV3" s="4"/>
+      <c r="BW3" s="4"/>
+      <c r="BX3" s="4"/>
+      <c r="BY3" s="4"/>
+      <c r="BZ3" s="4"/>
+      <c r="CA3" s="4"/>
+      <c r="CB3" s="4"/>
+      <c r="CC3" s="4"/>
+      <c r="CD3" s="4"/>
+      <c r="CE3" s="4"/>
+      <c r="CF3" s="4"/>
+      <c r="CG3" s="4"/>
+      <c r="CH3" s="4"/>
+      <c r="CI3" s="4"/>
+      <c r="CJ3" s="4"/>
+      <c r="CK3" s="4"/>
+      <c r="CL3" s="4"/>
+      <c r="CM3" s="4"/>
+      <c r="CN3" s="4"/>
+      <c r="CO3" s="4"/>
+      <c r="CP3" s="4"/>
+      <c r="CQ3" s="4"/>
+      <c r="CR3" s="4"/>
+      <c r="CS3" s="4"/>
+      <c r="CT3" s="4"/>
+      <c r="CU3" s="4"/>
+      <c r="CV3" s="4"/>
+      <c r="CW3" s="4"/>
+      <c r="CX3" s="4"/>
+      <c r="CY3" s="4"/>
+      <c r="CZ3" s="4"/>
+      <c r="DA3" s="4"/>
+      <c r="DB3" s="4"/>
+      <c r="DC3" s="4"/>
+      <c r="DD3" s="4"/>
+      <c r="DE3" s="4"/>
+      <c r="DF3" s="4"/>
+      <c r="DG3" s="4"/>
+      <c r="DH3" s="4"/>
+      <c r="DI3" s="4"/>
+      <c r="DJ3" s="4"/>
+      <c r="DK3" s="4"/>
+      <c r="DL3" s="4"/>
+      <c r="DM3" s="4"/>
+      <c r="DN3" s="4"/>
+      <c r="DO3" s="4"/>
+      <c r="DP3" s="4"/>
+      <c r="DQ3" s="4"/>
+      <c r="DR3" s="4"/>
+      <c r="DS3" s="4"/>
+    </row>
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1775,80 +1774,80 @@
         <v>34</v>
       </c>
       <c r="AW4" s="2"/>
-      <c r="AZ4" s="5"/>
-      <c r="BA4" s="5"/>
-      <c r="BB4" s="5"/>
-      <c r="BC4" s="5"/>
-      <c r="BD4" s="5"/>
-      <c r="BE4" s="5"/>
-      <c r="BF4" s="5"/>
-      <c r="BG4" s="5"/>
-      <c r="BH4" s="5"/>
-      <c r="BI4" s="5"/>
-      <c r="BJ4" s="5"/>
-      <c r="BK4" s="5"/>
-      <c r="BL4" s="5"/>
-      <c r="BM4" s="5"/>
-      <c r="BN4" s="5"/>
-      <c r="BO4" s="5"/>
-      <c r="BP4" s="5"/>
-      <c r="BQ4" s="5"/>
-      <c r="BR4" s="5"/>
-      <c r="BS4" s="5"/>
-      <c r="BT4" s="5"/>
-      <c r="BU4" s="5"/>
-      <c r="BV4" s="5"/>
-      <c r="BW4" s="5"/>
-      <c r="BX4" s="5"/>
-      <c r="BY4" s="5"/>
-      <c r="BZ4" s="5"/>
-      <c r="CA4" s="5"/>
-      <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
-      <c r="CD4" s="5"/>
-      <c r="CE4" s="5"/>
-      <c r="CF4" s="5"/>
-      <c r="CG4" s="5"/>
-      <c r="CH4" s="5"/>
-      <c r="CI4" s="5"/>
-      <c r="CJ4" s="5"/>
-      <c r="CK4" s="5"/>
-      <c r="CL4" s="5"/>
-      <c r="CM4" s="5"/>
-      <c r="CN4" s="5"/>
-      <c r="CO4" s="5"/>
-      <c r="CP4" s="5"/>
-      <c r="CQ4" s="5"/>
-      <c r="CR4" s="5"/>
-      <c r="CS4" s="5"/>
-      <c r="CT4" s="5"/>
-      <c r="CU4" s="5"/>
-      <c r="CV4" s="5"/>
-      <c r="CW4" s="5"/>
-      <c r="CX4" s="5"/>
-      <c r="CY4" s="5"/>
-      <c r="CZ4" s="5"/>
-      <c r="DA4" s="5"/>
-      <c r="DB4" s="5"/>
-      <c r="DC4" s="5"/>
-      <c r="DD4" s="5"/>
-      <c r="DE4" s="5"/>
-      <c r="DF4" s="5"/>
-      <c r="DG4" s="5"/>
-      <c r="DH4" s="5"/>
-      <c r="DI4" s="5"/>
-      <c r="DJ4" s="5"/>
-      <c r="DK4" s="5"/>
-      <c r="DL4" s="5"/>
-      <c r="DM4" s="5"/>
-      <c r="DN4" s="5"/>
-      <c r="DO4" s="5"/>
-      <c r="DP4" s="5"/>
-      <c r="DQ4" s="5"/>
-      <c r="DR4" s="5"/>
-      <c r="DS4" s="5"/>
-    </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ4" s="4"/>
+      <c r="BA4" s="4"/>
+      <c r="BB4" s="4"/>
+      <c r="BC4" s="4"/>
+      <c r="BD4" s="4"/>
+      <c r="BE4" s="4"/>
+      <c r="BF4" s="4"/>
+      <c r="BG4" s="4"/>
+      <c r="BH4" s="4"/>
+      <c r="BI4" s="4"/>
+      <c r="BJ4" s="4"/>
+      <c r="BK4" s="4"/>
+      <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
+      <c r="BN4" s="4"/>
+      <c r="BO4" s="4"/>
+      <c r="BP4" s="4"/>
+      <c r="BQ4" s="4"/>
+      <c r="BR4" s="4"/>
+      <c r="BS4" s="4"/>
+      <c r="BT4" s="4"/>
+      <c r="BU4" s="4"/>
+      <c r="BV4" s="4"/>
+      <c r="BW4" s="4"/>
+      <c r="BX4" s="4"/>
+      <c r="BY4" s="4"/>
+      <c r="BZ4" s="4"/>
+      <c r="CA4" s="4"/>
+      <c r="CB4" s="4"/>
+      <c r="CC4" s="4"/>
+      <c r="CD4" s="4"/>
+      <c r="CE4" s="4"/>
+      <c r="CF4" s="4"/>
+      <c r="CG4" s="4"/>
+      <c r="CH4" s="4"/>
+      <c r="CI4" s="4"/>
+      <c r="CJ4" s="4"/>
+      <c r="CK4" s="4"/>
+      <c r="CL4" s="4"/>
+      <c r="CM4" s="4"/>
+      <c r="CN4" s="4"/>
+      <c r="CO4" s="4"/>
+      <c r="CP4" s="4"/>
+      <c r="CQ4" s="4"/>
+      <c r="CR4" s="4"/>
+      <c r="CS4" s="4"/>
+      <c r="CT4" s="4"/>
+      <c r="CU4" s="4"/>
+      <c r="CV4" s="4"/>
+      <c r="CW4" s="4"/>
+      <c r="CX4" s="4"/>
+      <c r="CY4" s="4"/>
+      <c r="CZ4" s="4"/>
+      <c r="DA4" s="4"/>
+      <c r="DB4" s="4"/>
+      <c r="DC4" s="4"/>
+      <c r="DD4" s="4"/>
+      <c r="DE4" s="4"/>
+      <c r="DF4" s="4"/>
+      <c r="DG4" s="4"/>
+      <c r="DH4" s="4"/>
+      <c r="DI4" s="4"/>
+      <c r="DJ4" s="4"/>
+      <c r="DK4" s="4"/>
+      <c r="DL4" s="4"/>
+      <c r="DM4" s="4"/>
+      <c r="DN4" s="4"/>
+      <c r="DO4" s="4"/>
+      <c r="DP4" s="4"/>
+      <c r="DQ4" s="4"/>
+      <c r="DR4" s="4"/>
+      <c r="DS4" s="4"/>
+    </row>
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1993,80 +1992,80 @@
         <v>34</v>
       </c>
       <c r="AW5" s="2"/>
-      <c r="AZ5" s="5"/>
-      <c r="BA5" s="5"/>
-      <c r="BB5" s="5"/>
-      <c r="BC5" s="5"/>
-      <c r="BD5" s="5"/>
-      <c r="BE5" s="5"/>
-      <c r="BF5" s="5"/>
-      <c r="BG5" s="5"/>
-      <c r="BH5" s="5"/>
-      <c r="BI5" s="5"/>
-      <c r="BJ5" s="5"/>
-      <c r="BK5" s="5"/>
-      <c r="BL5" s="5"/>
-      <c r="BM5" s="5"/>
-      <c r="BN5" s="5"/>
-      <c r="BO5" s="5"/>
-      <c r="BP5" s="5"/>
-      <c r="BQ5" s="5"/>
-      <c r="BR5" s="5"/>
-      <c r="BS5" s="5"/>
-      <c r="BT5" s="5"/>
-      <c r="BU5" s="5"/>
-      <c r="BV5" s="5"/>
-      <c r="BW5" s="5"/>
-      <c r="BX5" s="5"/>
-      <c r="BY5" s="5"/>
-      <c r="BZ5" s="5"/>
-      <c r="CA5" s="5"/>
-      <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
-      <c r="CD5" s="5"/>
-      <c r="CE5" s="5"/>
-      <c r="CF5" s="5"/>
-      <c r="CG5" s="5"/>
-      <c r="CH5" s="5"/>
-      <c r="CI5" s="5"/>
-      <c r="CJ5" s="5"/>
-      <c r="CK5" s="5"/>
-      <c r="CL5" s="5"/>
-      <c r="CM5" s="5"/>
-      <c r="CN5" s="5"/>
-      <c r="CO5" s="5"/>
-      <c r="CP5" s="5"/>
-      <c r="CQ5" s="5"/>
-      <c r="CR5" s="5"/>
-      <c r="CS5" s="5"/>
-      <c r="CT5" s="5"/>
-      <c r="CU5" s="5"/>
-      <c r="CV5" s="5"/>
-      <c r="CW5" s="5"/>
-      <c r="CX5" s="5"/>
-      <c r="CY5" s="5"/>
-      <c r="CZ5" s="5"/>
-      <c r="DA5" s="5"/>
-      <c r="DB5" s="5"/>
-      <c r="DC5" s="5"/>
-      <c r="DD5" s="5"/>
-      <c r="DE5" s="5"/>
-      <c r="DF5" s="5"/>
-      <c r="DG5" s="5"/>
-      <c r="DH5" s="5"/>
-      <c r="DI5" s="5"/>
-      <c r="DJ5" s="5"/>
-      <c r="DK5" s="5"/>
-      <c r="DL5" s="5"/>
-      <c r="DM5" s="5"/>
-      <c r="DN5" s="5"/>
-      <c r="DO5" s="5"/>
-      <c r="DP5" s="5"/>
-      <c r="DQ5" s="5"/>
-      <c r="DR5" s="5"/>
-      <c r="DS5" s="5"/>
-    </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ5" s="4"/>
+      <c r="BA5" s="4"/>
+      <c r="BB5" s="4"/>
+      <c r="BC5" s="4"/>
+      <c r="BD5" s="4"/>
+      <c r="BE5" s="4"/>
+      <c r="BF5" s="4"/>
+      <c r="BG5" s="4"/>
+      <c r="BH5" s="4"/>
+      <c r="BI5" s="4"/>
+      <c r="BJ5" s="4"/>
+      <c r="BK5" s="4"/>
+      <c r="BL5" s="4"/>
+      <c r="BM5" s="4"/>
+      <c r="BN5" s="4"/>
+      <c r="BO5" s="4"/>
+      <c r="BP5" s="4"/>
+      <c r="BQ5" s="4"/>
+      <c r="BR5" s="4"/>
+      <c r="BS5" s="4"/>
+      <c r="BT5" s="4"/>
+      <c r="BU5" s="4"/>
+      <c r="BV5" s="4"/>
+      <c r="BW5" s="4"/>
+      <c r="BX5" s="4"/>
+      <c r="BY5" s="4"/>
+      <c r="BZ5" s="4"/>
+      <c r="CA5" s="4"/>
+      <c r="CB5" s="4"/>
+      <c r="CC5" s="4"/>
+      <c r="CD5" s="4"/>
+      <c r="CE5" s="4"/>
+      <c r="CF5" s="4"/>
+      <c r="CG5" s="4"/>
+      <c r="CH5" s="4"/>
+      <c r="CI5" s="4"/>
+      <c r="CJ5" s="4"/>
+      <c r="CK5" s="4"/>
+      <c r="CL5" s="4"/>
+      <c r="CM5" s="4"/>
+      <c r="CN5" s="4"/>
+      <c r="CO5" s="4"/>
+      <c r="CP5" s="4"/>
+      <c r="CQ5" s="4"/>
+      <c r="CR5" s="4"/>
+      <c r="CS5" s="4"/>
+      <c r="CT5" s="4"/>
+      <c r="CU5" s="4"/>
+      <c r="CV5" s="4"/>
+      <c r="CW5" s="4"/>
+      <c r="CX5" s="4"/>
+      <c r="CY5" s="4"/>
+      <c r="CZ5" s="4"/>
+      <c r="DA5" s="4"/>
+      <c r="DB5" s="4"/>
+      <c r="DC5" s="4"/>
+      <c r="DD5" s="4"/>
+      <c r="DE5" s="4"/>
+      <c r="DF5" s="4"/>
+      <c r="DG5" s="4"/>
+      <c r="DH5" s="4"/>
+      <c r="DI5" s="4"/>
+      <c r="DJ5" s="4"/>
+      <c r="DK5" s="4"/>
+      <c r="DL5" s="4"/>
+      <c r="DM5" s="4"/>
+      <c r="DN5" s="4"/>
+      <c r="DO5" s="4"/>
+      <c r="DP5" s="4"/>
+      <c r="DQ5" s="4"/>
+      <c r="DR5" s="4"/>
+      <c r="DS5" s="4"/>
+    </row>
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2211,80 +2210,80 @@
         <v>34</v>
       </c>
       <c r="AW6" s="2"/>
-      <c r="AZ6" s="5"/>
-      <c r="BA6" s="5"/>
-      <c r="BB6" s="5"/>
-      <c r="BC6" s="5"/>
-      <c r="BD6" s="5"/>
-      <c r="BE6" s="5"/>
-      <c r="BF6" s="5"/>
-      <c r="BG6" s="5"/>
-      <c r="BH6" s="5"/>
-      <c r="BI6" s="5"/>
-      <c r="BJ6" s="5"/>
-      <c r="BK6" s="5"/>
-      <c r="BL6" s="5"/>
-      <c r="BM6" s="5"/>
-      <c r="BN6" s="5"/>
-      <c r="BO6" s="5"/>
-      <c r="BP6" s="5"/>
-      <c r="BQ6" s="5"/>
-      <c r="BR6" s="5"/>
-      <c r="BS6" s="5"/>
-      <c r="BT6" s="5"/>
-      <c r="BU6" s="5"/>
-      <c r="BV6" s="5"/>
-      <c r="BW6" s="5"/>
-      <c r="BX6" s="5"/>
-      <c r="BY6" s="5"/>
-      <c r="BZ6" s="5"/>
-      <c r="CA6" s="5"/>
-      <c r="CB6" s="5"/>
-      <c r="CC6" s="5"/>
-      <c r="CD6" s="5"/>
-      <c r="CE6" s="5"/>
-      <c r="CF6" s="5"/>
-      <c r="CG6" s="5"/>
-      <c r="CH6" s="5"/>
-      <c r="CI6" s="7"/>
-      <c r="CJ6" s="5"/>
-      <c r="CK6" s="5"/>
-      <c r="CL6" s="5"/>
-      <c r="CM6" s="5"/>
-      <c r="CN6" s="5"/>
-      <c r="CO6" s="5"/>
-      <c r="CP6" s="5"/>
-      <c r="CQ6" s="5"/>
-      <c r="CR6" s="5"/>
-      <c r="CS6" s="5"/>
-      <c r="CT6" s="5"/>
-      <c r="CU6" s="5"/>
-      <c r="CV6" s="5"/>
-      <c r="CW6" s="5"/>
-      <c r="CX6" s="5"/>
-      <c r="CY6" s="5"/>
-      <c r="CZ6" s="5"/>
-      <c r="DA6" s="5"/>
-      <c r="DB6" s="5"/>
-      <c r="DC6" s="5"/>
-      <c r="DD6" s="5"/>
-      <c r="DE6" s="5"/>
-      <c r="DF6" s="5"/>
-      <c r="DG6" s="5"/>
-      <c r="DH6" s="5"/>
-      <c r="DI6" s="5"/>
-      <c r="DJ6" s="5"/>
-      <c r="DK6" s="5"/>
-      <c r="DL6" s="5"/>
-      <c r="DM6" s="5"/>
-      <c r="DN6" s="5"/>
-      <c r="DO6" s="5"/>
-      <c r="DP6" s="5"/>
-      <c r="DQ6" s="5"/>
-      <c r="DR6" s="5"/>
-      <c r="DS6" s="5"/>
-    </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ6" s="4"/>
+      <c r="BA6" s="4"/>
+      <c r="BB6" s="4"/>
+      <c r="BC6" s="4"/>
+      <c r="BD6" s="4"/>
+      <c r="BE6" s="4"/>
+      <c r="BF6" s="4"/>
+      <c r="BG6" s="4"/>
+      <c r="BH6" s="4"/>
+      <c r="BI6" s="4"/>
+      <c r="BJ6" s="4"/>
+      <c r="BK6" s="4"/>
+      <c r="BL6" s="4"/>
+      <c r="BM6" s="4"/>
+      <c r="BN6" s="4"/>
+      <c r="BO6" s="4"/>
+      <c r="BP6" s="4"/>
+      <c r="BQ6" s="4"/>
+      <c r="BR6" s="4"/>
+      <c r="BS6" s="4"/>
+      <c r="BT6" s="4"/>
+      <c r="BU6" s="4"/>
+      <c r="BV6" s="4"/>
+      <c r="BW6" s="4"/>
+      <c r="BX6" s="4"/>
+      <c r="BY6" s="4"/>
+      <c r="BZ6" s="4"/>
+      <c r="CA6" s="4"/>
+      <c r="CB6" s="4"/>
+      <c r="CC6" s="4"/>
+      <c r="CD6" s="4"/>
+      <c r="CE6" s="4"/>
+      <c r="CF6" s="4"/>
+      <c r="CG6" s="4"/>
+      <c r="CH6" s="4"/>
+      <c r="CI6" s="6"/>
+      <c r="CJ6" s="4"/>
+      <c r="CK6" s="4"/>
+      <c r="CL6" s="4"/>
+      <c r="CM6" s="4"/>
+      <c r="CN6" s="4"/>
+      <c r="CO6" s="4"/>
+      <c r="CP6" s="4"/>
+      <c r="CQ6" s="4"/>
+      <c r="CR6" s="4"/>
+      <c r="CS6" s="4"/>
+      <c r="CT6" s="4"/>
+      <c r="CU6" s="4"/>
+      <c r="CV6" s="4"/>
+      <c r="CW6" s="4"/>
+      <c r="CX6" s="4"/>
+      <c r="CY6" s="4"/>
+      <c r="CZ6" s="4"/>
+      <c r="DA6" s="4"/>
+      <c r="DB6" s="4"/>
+      <c r="DC6" s="4"/>
+      <c r="DD6" s="4"/>
+      <c r="DE6" s="4"/>
+      <c r="DF6" s="4"/>
+      <c r="DG6" s="4"/>
+      <c r="DH6" s="4"/>
+      <c r="DI6" s="4"/>
+      <c r="DJ6" s="4"/>
+      <c r="DK6" s="4"/>
+      <c r="DL6" s="4"/>
+      <c r="DM6" s="4"/>
+      <c r="DN6" s="4"/>
+      <c r="DO6" s="4"/>
+      <c r="DP6" s="4"/>
+      <c r="DQ6" s="4"/>
+      <c r="DR6" s="4"/>
+      <c r="DS6" s="4"/>
+    </row>
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2429,80 +2428,80 @@
         <v>34</v>
       </c>
       <c r="AW7" s="2"/>
-      <c r="AZ7" s="5"/>
-      <c r="BA7" s="5"/>
-      <c r="BB7" s="5"/>
-      <c r="BC7" s="5"/>
-      <c r="BD7" s="5"/>
-      <c r="BE7" s="5"/>
-      <c r="BF7" s="5"/>
-      <c r="BG7" s="5"/>
-      <c r="BH7" s="5"/>
-      <c r="BI7" s="5"/>
-      <c r="BJ7" s="5"/>
-      <c r="BK7" s="5"/>
-      <c r="BL7" s="5"/>
-      <c r="BM7" s="5"/>
-      <c r="BN7" s="5"/>
-      <c r="BO7" s="5"/>
-      <c r="BP7" s="5"/>
-      <c r="BQ7" s="5"/>
-      <c r="BR7" s="5"/>
-      <c r="BS7" s="5"/>
-      <c r="BT7" s="5"/>
-      <c r="BU7" s="5"/>
-      <c r="BV7" s="5"/>
-      <c r="BW7" s="5"/>
-      <c r="BX7" s="5"/>
-      <c r="BY7" s="5"/>
-      <c r="BZ7" s="5"/>
-      <c r="CA7" s="5"/>
-      <c r="CB7" s="5"/>
-      <c r="CC7" s="5"/>
-      <c r="CD7" s="5"/>
-      <c r="CE7" s="5"/>
-      <c r="CF7" s="5"/>
-      <c r="CG7" s="5"/>
-      <c r="CH7" s="5"/>
-      <c r="CI7" s="6"/>
-      <c r="CJ7" s="5"/>
-      <c r="CK7" s="5"/>
-      <c r="CL7" s="5"/>
-      <c r="CM7" s="5"/>
-      <c r="CN7" s="5"/>
-      <c r="CO7" s="5"/>
-      <c r="CP7" s="5"/>
-      <c r="CQ7" s="5"/>
-      <c r="CR7" s="5"/>
-      <c r="CS7" s="5"/>
-      <c r="CT7" s="5"/>
-      <c r="CU7" s="5"/>
-      <c r="CV7" s="5"/>
-      <c r="CW7" s="5"/>
-      <c r="CX7" s="5"/>
-      <c r="CY7" s="5"/>
-      <c r="CZ7" s="5"/>
-      <c r="DA7" s="5"/>
-      <c r="DB7" s="5"/>
-      <c r="DC7" s="5"/>
-      <c r="DD7" s="5"/>
-      <c r="DE7" s="5"/>
-      <c r="DF7" s="5"/>
-      <c r="DG7" s="5"/>
-      <c r="DH7" s="5"/>
-      <c r="DI7" s="5"/>
-      <c r="DJ7" s="5"/>
-      <c r="DK7" s="5"/>
-      <c r="DL7" s="5"/>
-      <c r="DM7" s="5"/>
-      <c r="DN7" s="5"/>
-      <c r="DO7" s="5"/>
-      <c r="DP7" s="5"/>
-      <c r="DQ7" s="5"/>
-      <c r="DR7" s="5"/>
-      <c r="DS7" s="5"/>
-    </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ7" s="4"/>
+      <c r="BA7" s="4"/>
+      <c r="BB7" s="4"/>
+      <c r="BC7" s="4"/>
+      <c r="BD7" s="4"/>
+      <c r="BE7" s="4"/>
+      <c r="BF7" s="4"/>
+      <c r="BG7" s="4"/>
+      <c r="BH7" s="4"/>
+      <c r="BI7" s="4"/>
+      <c r="BJ7" s="4"/>
+      <c r="BK7" s="4"/>
+      <c r="BL7" s="4"/>
+      <c r="BM7" s="4"/>
+      <c r="BN7" s="4"/>
+      <c r="BO7" s="4"/>
+      <c r="BP7" s="4"/>
+      <c r="BQ7" s="4"/>
+      <c r="BR7" s="4"/>
+      <c r="BS7" s="4"/>
+      <c r="BT7" s="4"/>
+      <c r="BU7" s="4"/>
+      <c r="BV7" s="4"/>
+      <c r="BW7" s="4"/>
+      <c r="BX7" s="4"/>
+      <c r="BY7" s="4"/>
+      <c r="BZ7" s="4"/>
+      <c r="CA7" s="4"/>
+      <c r="CB7" s="4"/>
+      <c r="CC7" s="4"/>
+      <c r="CD7" s="4"/>
+      <c r="CE7" s="4"/>
+      <c r="CF7" s="4"/>
+      <c r="CG7" s="4"/>
+      <c r="CH7" s="4"/>
+      <c r="CI7" s="5"/>
+      <c r="CJ7" s="4"/>
+      <c r="CK7" s="4"/>
+      <c r="CL7" s="4"/>
+      <c r="CM7" s="4"/>
+      <c r="CN7" s="4"/>
+      <c r="CO7" s="4"/>
+      <c r="CP7" s="4"/>
+      <c r="CQ7" s="4"/>
+      <c r="CR7" s="4"/>
+      <c r="CS7" s="4"/>
+      <c r="CT7" s="4"/>
+      <c r="CU7" s="4"/>
+      <c r="CV7" s="4"/>
+      <c r="CW7" s="4"/>
+      <c r="CX7" s="4"/>
+      <c r="CY7" s="4"/>
+      <c r="CZ7" s="4"/>
+      <c r="DA7" s="4"/>
+      <c r="DB7" s="4"/>
+      <c r="DC7" s="4"/>
+      <c r="DD7" s="4"/>
+      <c r="DE7" s="4"/>
+      <c r="DF7" s="4"/>
+      <c r="DG7" s="4"/>
+      <c r="DH7" s="4"/>
+      <c r="DI7" s="4"/>
+      <c r="DJ7" s="4"/>
+      <c r="DK7" s="4"/>
+      <c r="DL7" s="4"/>
+      <c r="DM7" s="4"/>
+      <c r="DN7" s="4"/>
+      <c r="DO7" s="4"/>
+      <c r="DP7" s="4"/>
+      <c r="DQ7" s="4"/>
+      <c r="DR7" s="4"/>
+      <c r="DS7" s="4"/>
+    </row>
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2647,80 +2646,80 @@
         <v>34</v>
       </c>
       <c r="AW8" s="2"/>
-      <c r="AZ8" s="5"/>
-      <c r="BA8" s="5"/>
-      <c r="BB8" s="5"/>
-      <c r="BC8" s="5"/>
-      <c r="BD8" s="5"/>
-      <c r="BE8" s="5"/>
-      <c r="BF8" s="5"/>
-      <c r="BG8" s="5"/>
-      <c r="BH8" s="5"/>
-      <c r="BI8" s="5"/>
-      <c r="BJ8" s="5"/>
-      <c r="BK8" s="5"/>
-      <c r="BL8" s="5"/>
-      <c r="BM8" s="5"/>
-      <c r="BN8" s="5"/>
-      <c r="BO8" s="5"/>
-      <c r="BP8" s="5"/>
-      <c r="BQ8" s="5"/>
-      <c r="BR8" s="5"/>
-      <c r="BS8" s="5"/>
-      <c r="BT8" s="5"/>
-      <c r="BU8" s="5"/>
-      <c r="BV8" s="5"/>
-      <c r="BW8" s="5"/>
-      <c r="BX8" s="5"/>
-      <c r="BY8" s="5"/>
-      <c r="BZ8" s="5"/>
-      <c r="CA8" s="5"/>
-      <c r="CB8" s="5"/>
-      <c r="CC8" s="5"/>
-      <c r="CD8" s="5"/>
-      <c r="CE8" s="5"/>
-      <c r="CF8" s="5"/>
-      <c r="CG8" s="5"/>
-      <c r="CH8" s="5"/>
-      <c r="CI8" s="5"/>
-      <c r="CJ8" s="5"/>
-      <c r="CK8" s="5"/>
-      <c r="CL8" s="5"/>
-      <c r="CM8" s="5"/>
-      <c r="CN8" s="5"/>
-      <c r="CO8" s="5"/>
-      <c r="CP8" s="5"/>
-      <c r="CQ8" s="5"/>
-      <c r="CR8" s="5"/>
-      <c r="CS8" s="5"/>
-      <c r="CT8" s="5"/>
-      <c r="CU8" s="5"/>
-      <c r="CV8" s="5"/>
-      <c r="CW8" s="5"/>
-      <c r="CX8" s="5"/>
-      <c r="CY8" s="5"/>
-      <c r="CZ8" s="5"/>
-      <c r="DA8" s="5"/>
-      <c r="DB8" s="5"/>
-      <c r="DC8" s="5"/>
-      <c r="DD8" s="5"/>
-      <c r="DE8" s="5"/>
-      <c r="DF8" s="5"/>
-      <c r="DG8" s="5"/>
-      <c r="DH8" s="5"/>
-      <c r="DI8" s="5"/>
-      <c r="DJ8" s="5"/>
-      <c r="DK8" s="5"/>
-      <c r="DL8" s="5"/>
-      <c r="DM8" s="5"/>
-      <c r="DN8" s="5"/>
-      <c r="DO8" s="5"/>
-      <c r="DP8" s="5"/>
-      <c r="DQ8" s="5"/>
-      <c r="DR8" s="5"/>
-      <c r="DS8" s="5"/>
-    </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ8" s="4"/>
+      <c r="BA8" s="4"/>
+      <c r="BB8" s="4"/>
+      <c r="BC8" s="4"/>
+      <c r="BD8" s="4"/>
+      <c r="BE8" s="4"/>
+      <c r="BF8" s="4"/>
+      <c r="BG8" s="4"/>
+      <c r="BH8" s="4"/>
+      <c r="BI8" s="4"/>
+      <c r="BJ8" s="4"/>
+      <c r="BK8" s="4"/>
+      <c r="BL8" s="4"/>
+      <c r="BM8" s="4"/>
+      <c r="BN8" s="4"/>
+      <c r="BO8" s="4"/>
+      <c r="BP8" s="4"/>
+      <c r="BQ8" s="4"/>
+      <c r="BR8" s="4"/>
+      <c r="BS8" s="4"/>
+      <c r="BT8" s="4"/>
+      <c r="BU8" s="4"/>
+      <c r="BV8" s="4"/>
+      <c r="BW8" s="4"/>
+      <c r="BX8" s="4"/>
+      <c r="BY8" s="4"/>
+      <c r="BZ8" s="4"/>
+      <c r="CA8" s="4"/>
+      <c r="CB8" s="4"/>
+      <c r="CC8" s="4"/>
+      <c r="CD8" s="4"/>
+      <c r="CE8" s="4"/>
+      <c r="CF8" s="4"/>
+      <c r="CG8" s="4"/>
+      <c r="CH8" s="4"/>
+      <c r="CI8" s="4"/>
+      <c r="CJ8" s="4"/>
+      <c r="CK8" s="4"/>
+      <c r="CL8" s="4"/>
+      <c r="CM8" s="4"/>
+      <c r="CN8" s="4"/>
+      <c r="CO8" s="4"/>
+      <c r="CP8" s="4"/>
+      <c r="CQ8" s="4"/>
+      <c r="CR8" s="4"/>
+      <c r="CS8" s="4"/>
+      <c r="CT8" s="4"/>
+      <c r="CU8" s="4"/>
+      <c r="CV8" s="4"/>
+      <c r="CW8" s="4"/>
+      <c r="CX8" s="4"/>
+      <c r="CY8" s="4"/>
+      <c r="CZ8" s="4"/>
+      <c r="DA8" s="4"/>
+      <c r="DB8" s="4"/>
+      <c r="DC8" s="4"/>
+      <c r="DD8" s="4"/>
+      <c r="DE8" s="4"/>
+      <c r="DF8" s="4"/>
+      <c r="DG8" s="4"/>
+      <c r="DH8" s="4"/>
+      <c r="DI8" s="4"/>
+      <c r="DJ8" s="4"/>
+      <c r="DK8" s="4"/>
+      <c r="DL8" s="4"/>
+      <c r="DM8" s="4"/>
+      <c r="DN8" s="4"/>
+      <c r="DO8" s="4"/>
+      <c r="DP8" s="4"/>
+      <c r="DQ8" s="4"/>
+      <c r="DR8" s="4"/>
+      <c r="DS8" s="4"/>
+    </row>
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2865,80 +2864,80 @@
         <v>34</v>
       </c>
       <c r="AW9" s="2"/>
-      <c r="AZ9" s="5"/>
-      <c r="BA9" s="5"/>
-      <c r="BB9" s="5"/>
-      <c r="BC9" s="5"/>
-      <c r="BD9" s="5"/>
-      <c r="BE9" s="5"/>
-      <c r="BF9" s="5"/>
-      <c r="BG9" s="5"/>
-      <c r="BH9" s="5"/>
-      <c r="BI9" s="5"/>
-      <c r="BJ9" s="5"/>
-      <c r="BK9" s="5"/>
-      <c r="BL9" s="5"/>
-      <c r="BM9" s="5"/>
-      <c r="BN9" s="5"/>
-      <c r="BO9" s="5"/>
-      <c r="BP9" s="5"/>
-      <c r="BQ9" s="5"/>
-      <c r="BR9" s="5"/>
-      <c r="BS9" s="5"/>
-      <c r="BT9" s="5"/>
-      <c r="BU9" s="5"/>
-      <c r="BV9" s="5"/>
-      <c r="BW9" s="5"/>
-      <c r="BX9" s="5"/>
-      <c r="BY9" s="5"/>
-      <c r="BZ9" s="5"/>
-      <c r="CA9" s="5"/>
-      <c r="CB9" s="5"/>
-      <c r="CC9" s="5"/>
-      <c r="CD9" s="5"/>
-      <c r="CE9" s="5"/>
-      <c r="CF9" s="5"/>
-      <c r="CG9" s="5"/>
-      <c r="CH9" s="5"/>
-      <c r="CI9" s="5"/>
-      <c r="CJ9" s="5"/>
-      <c r="CK9" s="5"/>
-      <c r="CL9" s="5"/>
-      <c r="CM9" s="5"/>
-      <c r="CN9" s="5"/>
-      <c r="CO9" s="5"/>
-      <c r="CP9" s="5"/>
-      <c r="CQ9" s="5"/>
-      <c r="CR9" s="5"/>
-      <c r="CS9" s="5"/>
-      <c r="CT9" s="5"/>
-      <c r="CU9" s="5"/>
-      <c r="CV9" s="5"/>
-      <c r="CW9" s="5"/>
-      <c r="CX9" s="5"/>
-      <c r="CY9" s="5"/>
-      <c r="CZ9" s="5"/>
-      <c r="DA9" s="5"/>
-      <c r="DB9" s="5"/>
-      <c r="DC9" s="5"/>
-      <c r="DD9" s="5"/>
-      <c r="DE9" s="5"/>
-      <c r="DF9" s="5"/>
-      <c r="DG9" s="5"/>
-      <c r="DH9" s="5"/>
-      <c r="DI9" s="5"/>
-      <c r="DJ9" s="5"/>
-      <c r="DK9" s="5"/>
-      <c r="DL9" s="5"/>
-      <c r="DM9" s="5"/>
-      <c r="DN9" s="5"/>
-      <c r="DO9" s="5"/>
-      <c r="DP9" s="5"/>
-      <c r="DQ9" s="5"/>
-      <c r="DR9" s="5"/>
-      <c r="DS9" s="5"/>
-    </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
+      <c r="BC9" s="4"/>
+      <c r="BD9" s="4"/>
+      <c r="BE9" s="4"/>
+      <c r="BF9" s="4"/>
+      <c r="BG9" s="4"/>
+      <c r="BH9" s="4"/>
+      <c r="BI9" s="4"/>
+      <c r="BJ9" s="4"/>
+      <c r="BK9" s="4"/>
+      <c r="BL9" s="4"/>
+      <c r="BM9" s="4"/>
+      <c r="BN9" s="4"/>
+      <c r="BO9" s="4"/>
+      <c r="BP9" s="4"/>
+      <c r="BQ9" s="4"/>
+      <c r="BR9" s="4"/>
+      <c r="BS9" s="4"/>
+      <c r="BT9" s="4"/>
+      <c r="BU9" s="4"/>
+      <c r="BV9" s="4"/>
+      <c r="BW9" s="4"/>
+      <c r="BX9" s="4"/>
+      <c r="BY9" s="4"/>
+      <c r="BZ9" s="4"/>
+      <c r="CA9" s="4"/>
+      <c r="CB9" s="4"/>
+      <c r="CC9" s="4"/>
+      <c r="CD9" s="4"/>
+      <c r="CE9" s="4"/>
+      <c r="CF9" s="4"/>
+      <c r="CG9" s="4"/>
+      <c r="CH9" s="4"/>
+      <c r="CI9" s="4"/>
+      <c r="CJ9" s="4"/>
+      <c r="CK9" s="4"/>
+      <c r="CL9" s="4"/>
+      <c r="CM9" s="4"/>
+      <c r="CN9" s="4"/>
+      <c r="CO9" s="4"/>
+      <c r="CP9" s="4"/>
+      <c r="CQ9" s="4"/>
+      <c r="CR9" s="4"/>
+      <c r="CS9" s="4"/>
+      <c r="CT9" s="4"/>
+      <c r="CU9" s="4"/>
+      <c r="CV9" s="4"/>
+      <c r="CW9" s="4"/>
+      <c r="CX9" s="4"/>
+      <c r="CY9" s="4"/>
+      <c r="CZ9" s="4"/>
+      <c r="DA9" s="4"/>
+      <c r="DB9" s="4"/>
+      <c r="DC9" s="4"/>
+      <c r="DD9" s="4"/>
+      <c r="DE9" s="4"/>
+      <c r="DF9" s="4"/>
+      <c r="DG9" s="4"/>
+      <c r="DH9" s="4"/>
+      <c r="DI9" s="4"/>
+      <c r="DJ9" s="4"/>
+      <c r="DK9" s="4"/>
+      <c r="DL9" s="4"/>
+      <c r="DM9" s="4"/>
+      <c r="DN9" s="4"/>
+      <c r="DO9" s="4"/>
+      <c r="DP9" s="4"/>
+      <c r="DQ9" s="4"/>
+      <c r="DR9" s="4"/>
+      <c r="DS9" s="4"/>
+    </row>
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3083,80 +3082,80 @@
         <v>34</v>
       </c>
       <c r="AW10" s="2"/>
-      <c r="AZ10" s="5"/>
-      <c r="BA10" s="5"/>
-      <c r="BB10" s="5"/>
-      <c r="BC10" s="5"/>
-      <c r="BD10" s="5"/>
-      <c r="BE10" s="5"/>
-      <c r="BF10" s="5"/>
-      <c r="BG10" s="5"/>
-      <c r="BH10" s="5"/>
-      <c r="BI10" s="5"/>
-      <c r="BJ10" s="5"/>
-      <c r="BK10" s="5"/>
-      <c r="BL10" s="5"/>
-      <c r="BM10" s="5"/>
-      <c r="BN10" s="5"/>
-      <c r="BO10" s="5"/>
-      <c r="BP10" s="5"/>
-      <c r="BQ10" s="5"/>
-      <c r="BR10" s="5"/>
-      <c r="BS10" s="5"/>
-      <c r="BT10" s="5"/>
-      <c r="BU10" s="5"/>
-      <c r="BV10" s="5"/>
-      <c r="BW10" s="5"/>
-      <c r="BX10" s="5"/>
-      <c r="BY10" s="5"/>
-      <c r="BZ10" s="5"/>
-      <c r="CA10" s="5"/>
-      <c r="CB10" s="5"/>
-      <c r="CC10" s="5"/>
-      <c r="CD10" s="5"/>
-      <c r="CE10" s="5"/>
-      <c r="CF10" s="5"/>
-      <c r="CG10" s="5"/>
-      <c r="CH10" s="5"/>
-      <c r="CI10" s="5"/>
-      <c r="CJ10" s="5"/>
-      <c r="CK10" s="5"/>
-      <c r="CL10" s="5"/>
-      <c r="CM10" s="5"/>
-      <c r="CN10" s="5"/>
-      <c r="CO10" s="5"/>
-      <c r="CP10" s="5"/>
-      <c r="CQ10" s="5"/>
-      <c r="CR10" s="5"/>
-      <c r="CS10" s="5"/>
-      <c r="CT10" s="5"/>
-      <c r="CU10" s="5"/>
-      <c r="CV10" s="5"/>
-      <c r="CW10" s="5"/>
-      <c r="CX10" s="5"/>
-      <c r="CY10" s="5"/>
-      <c r="CZ10" s="5"/>
-      <c r="DA10" s="5"/>
-      <c r="DB10" s="5"/>
-      <c r="DC10" s="5"/>
-      <c r="DD10" s="5"/>
-      <c r="DE10" s="5"/>
-      <c r="DF10" s="5"/>
-      <c r="DG10" s="5"/>
-      <c r="DH10" s="5"/>
-      <c r="DI10" s="5"/>
-      <c r="DJ10" s="5"/>
-      <c r="DK10" s="5"/>
-      <c r="DL10" s="5"/>
-      <c r="DM10" s="5"/>
-      <c r="DN10" s="5"/>
-      <c r="DO10" s="5"/>
-      <c r="DP10" s="5"/>
-      <c r="DQ10" s="5"/>
-      <c r="DR10" s="5"/>
-      <c r="DS10" s="5"/>
-    </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="4"/>
+      <c r="BE10" s="4"/>
+      <c r="BF10" s="4"/>
+      <c r="BG10" s="4"/>
+      <c r="BH10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+      <c r="BM10" s="4"/>
+      <c r="BN10" s="4"/>
+      <c r="BO10" s="4"/>
+      <c r="BP10" s="4"/>
+      <c r="BQ10" s="4"/>
+      <c r="BR10" s="4"/>
+      <c r="BS10" s="4"/>
+      <c r="BT10" s="4"/>
+      <c r="BU10" s="4"/>
+      <c r="BV10" s="4"/>
+      <c r="BW10" s="4"/>
+      <c r="BX10" s="4"/>
+      <c r="BY10" s="4"/>
+      <c r="BZ10" s="4"/>
+      <c r="CA10" s="4"/>
+      <c r="CB10" s="4"/>
+      <c r="CC10" s="4"/>
+      <c r="CD10" s="4"/>
+      <c r="CE10" s="4"/>
+      <c r="CF10" s="4"/>
+      <c r="CG10" s="4"/>
+      <c r="CH10" s="4"/>
+      <c r="CI10" s="4"/>
+      <c r="CJ10" s="4"/>
+      <c r="CK10" s="4"/>
+      <c r="CL10" s="4"/>
+      <c r="CM10" s="4"/>
+      <c r="CN10" s="4"/>
+      <c r="CO10" s="4"/>
+      <c r="CP10" s="4"/>
+      <c r="CQ10" s="4"/>
+      <c r="CR10" s="4"/>
+      <c r="CS10" s="4"/>
+      <c r="CT10" s="4"/>
+      <c r="CU10" s="4"/>
+      <c r="CV10" s="4"/>
+      <c r="CW10" s="4"/>
+      <c r="CX10" s="4"/>
+      <c r="CY10" s="4"/>
+      <c r="CZ10" s="4"/>
+      <c r="DA10" s="4"/>
+      <c r="DB10" s="4"/>
+      <c r="DC10" s="4"/>
+      <c r="DD10" s="4"/>
+      <c r="DE10" s="4"/>
+      <c r="DF10" s="4"/>
+      <c r="DG10" s="4"/>
+      <c r="DH10" s="4"/>
+      <c r="DI10" s="4"/>
+      <c r="DJ10" s="4"/>
+      <c r="DK10" s="4"/>
+      <c r="DL10" s="4"/>
+      <c r="DM10" s="4"/>
+      <c r="DN10" s="4"/>
+      <c r="DO10" s="4"/>
+      <c r="DP10" s="4"/>
+      <c r="DQ10" s="4"/>
+      <c r="DR10" s="4"/>
+      <c r="DS10" s="4"/>
+    </row>
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3301,80 +3300,80 @@
         <v>34</v>
       </c>
       <c r="AW11" s="2"/>
-      <c r="AZ11" s="5"/>
-      <c r="BA11" s="5"/>
-      <c r="BB11" s="5"/>
-      <c r="BC11" s="5"/>
-      <c r="BD11" s="5"/>
-      <c r="BE11" s="5"/>
-      <c r="BF11" s="5"/>
-      <c r="BG11" s="5"/>
-      <c r="BH11" s="5"/>
-      <c r="BI11" s="5"/>
-      <c r="BJ11" s="5"/>
-      <c r="BK11" s="5"/>
-      <c r="BL11" s="5"/>
-      <c r="BM11" s="5"/>
-      <c r="BN11" s="5"/>
-      <c r="BO11" s="5"/>
-      <c r="BP11" s="5"/>
-      <c r="BQ11" s="5"/>
-      <c r="BR11" s="5"/>
-      <c r="BS11" s="5"/>
-      <c r="BT11" s="5"/>
-      <c r="BU11" s="5"/>
-      <c r="BV11" s="5"/>
-      <c r="BW11" s="5"/>
-      <c r="BX11" s="5"/>
-      <c r="BY11" s="5"/>
-      <c r="BZ11" s="5"/>
-      <c r="CA11" s="5"/>
-      <c r="CB11" s="5"/>
-      <c r="CC11" s="5"/>
-      <c r="CD11" s="5"/>
-      <c r="CE11" s="5"/>
-      <c r="CF11" s="5"/>
-      <c r="CG11" s="5"/>
-      <c r="CH11" s="5"/>
-      <c r="CI11" s="5"/>
-      <c r="CJ11" s="5"/>
-      <c r="CK11" s="5"/>
-      <c r="CL11" s="5"/>
-      <c r="CM11" s="5"/>
-      <c r="CN11" s="5"/>
-      <c r="CO11" s="5"/>
-      <c r="CP11" s="5"/>
-      <c r="CQ11" s="5"/>
-      <c r="CR11" s="5"/>
-      <c r="CS11" s="5"/>
-      <c r="CT11" s="5"/>
-      <c r="CU11" s="5"/>
-      <c r="CV11" s="5"/>
-      <c r="CW11" s="5"/>
-      <c r="CX11" s="5"/>
-      <c r="CY11" s="5"/>
-      <c r="CZ11" s="5"/>
-      <c r="DA11" s="5"/>
-      <c r="DB11" s="5"/>
-      <c r="DC11" s="5"/>
-      <c r="DD11" s="5"/>
-      <c r="DE11" s="5"/>
-      <c r="DF11" s="5"/>
-      <c r="DG11" s="5"/>
-      <c r="DH11" s="5"/>
-      <c r="DI11" s="5"/>
-      <c r="DJ11" s="5"/>
-      <c r="DK11" s="5"/>
-      <c r="DL11" s="5"/>
-      <c r="DM11" s="5"/>
-      <c r="DN11" s="5"/>
-      <c r="DO11" s="5"/>
-      <c r="DP11" s="5"/>
-      <c r="DQ11" s="5"/>
-      <c r="DR11" s="5"/>
-      <c r="DS11" s="5"/>
-    </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="4"/>
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="4"/>
+      <c r="BG11" s="4"/>
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+      <c r="BM11" s="4"/>
+      <c r="BN11" s="4"/>
+      <c r="BO11" s="4"/>
+      <c r="BP11" s="4"/>
+      <c r="BQ11" s="4"/>
+      <c r="BR11" s="4"/>
+      <c r="BS11" s="4"/>
+      <c r="BT11" s="4"/>
+      <c r="BU11" s="4"/>
+      <c r="BV11" s="4"/>
+      <c r="BW11" s="4"/>
+      <c r="BX11" s="4"/>
+      <c r="BY11" s="4"/>
+      <c r="BZ11" s="4"/>
+      <c r="CA11" s="4"/>
+      <c r="CB11" s="4"/>
+      <c r="CC11" s="4"/>
+      <c r="CD11" s="4"/>
+      <c r="CE11" s="4"/>
+      <c r="CF11" s="4"/>
+      <c r="CG11" s="4"/>
+      <c r="CH11" s="4"/>
+      <c r="CI11" s="4"/>
+      <c r="CJ11" s="4"/>
+      <c r="CK11" s="4"/>
+      <c r="CL11" s="4"/>
+      <c r="CM11" s="4"/>
+      <c r="CN11" s="4"/>
+      <c r="CO11" s="4"/>
+      <c r="CP11" s="4"/>
+      <c r="CQ11" s="4"/>
+      <c r="CR11" s="4"/>
+      <c r="CS11" s="4"/>
+      <c r="CT11" s="4"/>
+      <c r="CU11" s="4"/>
+      <c r="CV11" s="4"/>
+      <c r="CW11" s="4"/>
+      <c r="CX11" s="4"/>
+      <c r="CY11" s="4"/>
+      <c r="CZ11" s="4"/>
+      <c r="DA11" s="4"/>
+      <c r="DB11" s="4"/>
+      <c r="DC11" s="4"/>
+      <c r="DD11" s="4"/>
+      <c r="DE11" s="4"/>
+      <c r="DF11" s="4"/>
+      <c r="DG11" s="4"/>
+      <c r="DH11" s="4"/>
+      <c r="DI11" s="4"/>
+      <c r="DJ11" s="4"/>
+      <c r="DK11" s="4"/>
+      <c r="DL11" s="4"/>
+      <c r="DM11" s="4"/>
+      <c r="DN11" s="4"/>
+      <c r="DO11" s="4"/>
+      <c r="DP11" s="4"/>
+      <c r="DQ11" s="4"/>
+      <c r="DR11" s="4"/>
+      <c r="DS11" s="4"/>
+    </row>
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3522,80 +3521,80 @@
         <v>34</v>
       </c>
       <c r="AW12" s="2"/>
-      <c r="AZ12" s="5"/>
-      <c r="BA12" s="5"/>
-      <c r="BB12" s="5"/>
-      <c r="BC12" s="5"/>
-      <c r="BD12" s="5"/>
-      <c r="BE12" s="5"/>
-      <c r="BF12" s="5"/>
-      <c r="BG12" s="5"/>
-      <c r="BH12" s="5"/>
-      <c r="BI12" s="5"/>
-      <c r="BJ12" s="5"/>
-      <c r="BK12" s="5"/>
-      <c r="BL12" s="5"/>
-      <c r="BM12" s="5"/>
-      <c r="BN12" s="5"/>
-      <c r="BO12" s="5"/>
-      <c r="BP12" s="5"/>
-      <c r="BQ12" s="5"/>
-      <c r="BR12" s="5"/>
-      <c r="BS12" s="5"/>
-      <c r="BT12" s="5"/>
-      <c r="BU12" s="5"/>
-      <c r="BV12" s="5"/>
-      <c r="BW12" s="5"/>
-      <c r="BX12" s="5"/>
-      <c r="BY12" s="5"/>
-      <c r="BZ12" s="5"/>
-      <c r="CA12" s="5"/>
-      <c r="CB12" s="5"/>
-      <c r="CC12" s="5"/>
-      <c r="CD12" s="5"/>
-      <c r="CE12" s="5"/>
-      <c r="CF12" s="5"/>
-      <c r="CG12" s="5"/>
-      <c r="CH12" s="5"/>
-      <c r="CI12" s="5"/>
-      <c r="CJ12" s="5"/>
-      <c r="CK12" s="5"/>
-      <c r="CL12" s="5"/>
-      <c r="CM12" s="5"/>
-      <c r="CN12" s="5"/>
-      <c r="CO12" s="5"/>
-      <c r="CP12" s="5"/>
-      <c r="CQ12" s="5"/>
-      <c r="CR12" s="5"/>
-      <c r="CS12" s="5"/>
-      <c r="CT12" s="5"/>
-      <c r="CU12" s="5"/>
-      <c r="CV12" s="5"/>
-      <c r="CW12" s="5"/>
-      <c r="CX12" s="5"/>
-      <c r="CY12" s="5"/>
-      <c r="CZ12" s="5"/>
-      <c r="DA12" s="5"/>
-      <c r="DB12" s="5"/>
-      <c r="DC12" s="5"/>
-      <c r="DD12" s="5"/>
-      <c r="DE12" s="5"/>
-      <c r="DF12" s="5"/>
-      <c r="DG12" s="5"/>
-      <c r="DH12" s="5"/>
-      <c r="DI12" s="5"/>
-      <c r="DJ12" s="5"/>
-      <c r="DK12" s="5"/>
-      <c r="DL12" s="5"/>
-      <c r="DM12" s="5"/>
-      <c r="DN12" s="5"/>
-      <c r="DO12" s="5"/>
-      <c r="DP12" s="5"/>
-      <c r="DQ12" s="5"/>
-      <c r="DR12" s="5"/>
-      <c r="DS12" s="5"/>
-    </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="4"/>
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+      <c r="BD12" s="4"/>
+      <c r="BE12" s="4"/>
+      <c r="BF12" s="4"/>
+      <c r="BG12" s="4"/>
+      <c r="BH12" s="4"/>
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+      <c r="BM12" s="4"/>
+      <c r="BN12" s="4"/>
+      <c r="BO12" s="4"/>
+      <c r="BP12" s="4"/>
+      <c r="BQ12" s="4"/>
+      <c r="BR12" s="4"/>
+      <c r="BS12" s="4"/>
+      <c r="BT12" s="4"/>
+      <c r="BU12" s="4"/>
+      <c r="BV12" s="4"/>
+      <c r="BW12" s="4"/>
+      <c r="BX12" s="4"/>
+      <c r="BY12" s="4"/>
+      <c r="BZ12" s="4"/>
+      <c r="CA12" s="4"/>
+      <c r="CB12" s="4"/>
+      <c r="CC12" s="4"/>
+      <c r="CD12" s="4"/>
+      <c r="CE12" s="4"/>
+      <c r="CF12" s="4"/>
+      <c r="CG12" s="4"/>
+      <c r="CH12" s="4"/>
+      <c r="CI12" s="4"/>
+      <c r="CJ12" s="4"/>
+      <c r="CK12" s="4"/>
+      <c r="CL12" s="4"/>
+      <c r="CM12" s="4"/>
+      <c r="CN12" s="4"/>
+      <c r="CO12" s="4"/>
+      <c r="CP12" s="4"/>
+      <c r="CQ12" s="4"/>
+      <c r="CR12" s="4"/>
+      <c r="CS12" s="4"/>
+      <c r="CT12" s="4"/>
+      <c r="CU12" s="4"/>
+      <c r="CV12" s="4"/>
+      <c r="CW12" s="4"/>
+      <c r="CX12" s="4"/>
+      <c r="CY12" s="4"/>
+      <c r="CZ12" s="4"/>
+      <c r="DA12" s="4"/>
+      <c r="DB12" s="4"/>
+      <c r="DC12" s="4"/>
+      <c r="DD12" s="4"/>
+      <c r="DE12" s="4"/>
+      <c r="DF12" s="4"/>
+      <c r="DG12" s="4"/>
+      <c r="DH12" s="4"/>
+      <c r="DI12" s="4"/>
+      <c r="DJ12" s="4"/>
+      <c r="DK12" s="4"/>
+      <c r="DL12" s="4"/>
+      <c r="DM12" s="4"/>
+      <c r="DN12" s="4"/>
+      <c r="DO12" s="4"/>
+      <c r="DP12" s="4"/>
+      <c r="DQ12" s="4"/>
+      <c r="DR12" s="4"/>
+      <c r="DS12" s="4"/>
+    </row>
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3740,80 +3739,80 @@
         <v>34</v>
       </c>
       <c r="AW13" s="2"/>
-      <c r="AZ13" s="5"/>
-      <c r="BA13" s="5"/>
-      <c r="BB13" s="5"/>
-      <c r="BC13" s="5"/>
-      <c r="BD13" s="5"/>
-      <c r="BE13" s="5"/>
-      <c r="BF13" s="5"/>
-      <c r="BG13" s="5"/>
-      <c r="BH13" s="5"/>
-      <c r="BI13" s="5"/>
-      <c r="BJ13" s="5"/>
-      <c r="BK13" s="5"/>
-      <c r="BL13" s="5"/>
-      <c r="BM13" s="5"/>
-      <c r="BN13" s="5"/>
-      <c r="BO13" s="5"/>
-      <c r="BP13" s="5"/>
-      <c r="BQ13" s="5"/>
-      <c r="BR13" s="5"/>
-      <c r="BS13" s="5"/>
-      <c r="BT13" s="5"/>
-      <c r="BU13" s="5"/>
-      <c r="BV13" s="5"/>
-      <c r="BW13" s="5"/>
-      <c r="BX13" s="5"/>
-      <c r="BY13" s="5"/>
-      <c r="BZ13" s="5"/>
-      <c r="CA13" s="5"/>
-      <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
-      <c r="CD13" s="5"/>
-      <c r="CE13" s="5"/>
-      <c r="CF13" s="5"/>
-      <c r="CG13" s="5"/>
-      <c r="CH13" s="5"/>
-      <c r="CI13" s="5"/>
-      <c r="CJ13" s="5"/>
-      <c r="CK13" s="5"/>
-      <c r="CL13" s="5"/>
-      <c r="CM13" s="5"/>
-      <c r="CN13" s="5"/>
-      <c r="CO13" s="5"/>
-      <c r="CP13" s="5"/>
-      <c r="CQ13" s="5"/>
-      <c r="CR13" s="5"/>
-      <c r="CS13" s="5"/>
-      <c r="CT13" s="5"/>
-      <c r="CU13" s="5"/>
-      <c r="CV13" s="5"/>
-      <c r="CW13" s="5"/>
-      <c r="CX13" s="5"/>
-      <c r="CY13" s="5"/>
-      <c r="CZ13" s="5"/>
-      <c r="DA13" s="5"/>
-      <c r="DB13" s="5"/>
-      <c r="DC13" s="5"/>
-      <c r="DD13" s="5"/>
-      <c r="DE13" s="5"/>
-      <c r="DF13" s="5"/>
-      <c r="DG13" s="5"/>
-      <c r="DH13" s="5"/>
-      <c r="DI13" s="5"/>
-      <c r="DJ13" s="5"/>
-      <c r="DK13" s="5"/>
-      <c r="DL13" s="5"/>
-      <c r="DM13" s="5"/>
-      <c r="DN13" s="5"/>
-      <c r="DO13" s="5"/>
-      <c r="DP13" s="5"/>
-      <c r="DQ13" s="5"/>
-      <c r="DR13" s="5"/>
-      <c r="DS13" s="5"/>
-    </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="4"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="4"/>
+      <c r="BD13" s="4"/>
+      <c r="BE13" s="4"/>
+      <c r="BF13" s="4"/>
+      <c r="BG13" s="4"/>
+      <c r="BH13" s="4"/>
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+      <c r="BM13" s="4"/>
+      <c r="BN13" s="4"/>
+      <c r="BO13" s="4"/>
+      <c r="BP13" s="4"/>
+      <c r="BQ13" s="4"/>
+      <c r="BR13" s="4"/>
+      <c r="BS13" s="4"/>
+      <c r="BT13" s="4"/>
+      <c r="BU13" s="4"/>
+      <c r="BV13" s="4"/>
+      <c r="BW13" s="4"/>
+      <c r="BX13" s="4"/>
+      <c r="BY13" s="4"/>
+      <c r="BZ13" s="4"/>
+      <c r="CA13" s="4"/>
+      <c r="CB13" s="4"/>
+      <c r="CC13" s="4"/>
+      <c r="CD13" s="4"/>
+      <c r="CE13" s="4"/>
+      <c r="CF13" s="4"/>
+      <c r="CG13" s="4"/>
+      <c r="CH13" s="4"/>
+      <c r="CI13" s="4"/>
+      <c r="CJ13" s="4"/>
+      <c r="CK13" s="4"/>
+      <c r="CL13" s="4"/>
+      <c r="CM13" s="4"/>
+      <c r="CN13" s="4"/>
+      <c r="CO13" s="4"/>
+      <c r="CP13" s="4"/>
+      <c r="CQ13" s="4"/>
+      <c r="CR13" s="4"/>
+      <c r="CS13" s="4"/>
+      <c r="CT13" s="4"/>
+      <c r="CU13" s="4"/>
+      <c r="CV13" s="4"/>
+      <c r="CW13" s="4"/>
+      <c r="CX13" s="4"/>
+      <c r="CY13" s="4"/>
+      <c r="CZ13" s="4"/>
+      <c r="DA13" s="4"/>
+      <c r="DB13" s="4"/>
+      <c r="DC13" s="4"/>
+      <c r="DD13" s="4"/>
+      <c r="DE13" s="4"/>
+      <c r="DF13" s="4"/>
+      <c r="DG13" s="4"/>
+      <c r="DH13" s="4"/>
+      <c r="DI13" s="4"/>
+      <c r="DJ13" s="4"/>
+      <c r="DK13" s="4"/>
+      <c r="DL13" s="4"/>
+      <c r="DM13" s="4"/>
+      <c r="DN13" s="4"/>
+      <c r="DO13" s="4"/>
+      <c r="DP13" s="4"/>
+      <c r="DQ13" s="4"/>
+      <c r="DR13" s="4"/>
+      <c r="DS13" s="4"/>
+    </row>
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3958,80 +3957,80 @@
         <v>35</v>
       </c>
       <c r="AW14" s="2"/>
-      <c r="AZ14" s="5"/>
-      <c r="BA14" s="5"/>
-      <c r="BB14" s="5"/>
-      <c r="BC14" s="5"/>
-      <c r="BD14" s="5"/>
-      <c r="BE14" s="5"/>
-      <c r="BF14" s="5"/>
-      <c r="BG14" s="5"/>
-      <c r="BH14" s="5"/>
-      <c r="BI14" s="5"/>
-      <c r="BJ14" s="5"/>
-      <c r="BK14" s="5"/>
-      <c r="BL14" s="5"/>
-      <c r="BM14" s="5"/>
-      <c r="BN14" s="5"/>
-      <c r="BO14" s="5"/>
-      <c r="BP14" s="5"/>
-      <c r="BQ14" s="5"/>
-      <c r="BR14" s="5"/>
-      <c r="BS14" s="5"/>
-      <c r="BT14" s="5"/>
-      <c r="BU14" s="5"/>
-      <c r="BV14" s="5"/>
-      <c r="BW14" s="5"/>
-      <c r="BX14" s="5"/>
-      <c r="BY14" s="5"/>
-      <c r="BZ14" s="5"/>
-      <c r="CA14" s="5"/>
-      <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
-      <c r="CD14" s="5"/>
-      <c r="CE14" s="5"/>
-      <c r="CF14" s="5"/>
-      <c r="CG14" s="5"/>
-      <c r="CH14" s="5"/>
-      <c r="CI14" s="5"/>
-      <c r="CJ14" s="5"/>
-      <c r="CK14" s="5"/>
-      <c r="CL14" s="5"/>
-      <c r="CM14" s="5"/>
-      <c r="CN14" s="5"/>
-      <c r="CO14" s="5"/>
-      <c r="CP14" s="5"/>
-      <c r="CQ14" s="5"/>
-      <c r="CR14" s="5"/>
-      <c r="CS14" s="5"/>
-      <c r="CT14" s="5"/>
-      <c r="CU14" s="5"/>
-      <c r="CV14" s="5"/>
-      <c r="CW14" s="5"/>
-      <c r="CX14" s="5"/>
-      <c r="CY14" s="5"/>
-      <c r="CZ14" s="5"/>
-      <c r="DA14" s="5"/>
-      <c r="DB14" s="5"/>
-      <c r="DC14" s="5"/>
-      <c r="DD14" s="5"/>
-      <c r="DE14" s="5"/>
-      <c r="DF14" s="5"/>
-      <c r="DG14" s="5"/>
-      <c r="DH14" s="5"/>
-      <c r="DI14" s="5"/>
-      <c r="DJ14" s="5"/>
-      <c r="DK14" s="5"/>
-      <c r="DL14" s="5"/>
-      <c r="DM14" s="5"/>
-      <c r="DN14" s="5"/>
-      <c r="DO14" s="5"/>
-      <c r="DP14" s="5"/>
-      <c r="DQ14" s="5"/>
-      <c r="DR14" s="5"/>
-      <c r="DS14" s="5"/>
-    </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="4"/>
+      <c r="BB14" s="4"/>
+      <c r="BC14" s="4"/>
+      <c r="BD14" s="4"/>
+      <c r="BE14" s="4"/>
+      <c r="BF14" s="4"/>
+      <c r="BG14" s="4"/>
+      <c r="BH14" s="4"/>
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+      <c r="BM14" s="4"/>
+      <c r="BN14" s="4"/>
+      <c r="BO14" s="4"/>
+      <c r="BP14" s="4"/>
+      <c r="BQ14" s="4"/>
+      <c r="BR14" s="4"/>
+      <c r="BS14" s="4"/>
+      <c r="BT14" s="4"/>
+      <c r="BU14" s="4"/>
+      <c r="BV14" s="4"/>
+      <c r="BW14" s="4"/>
+      <c r="BX14" s="4"/>
+      <c r="BY14" s="4"/>
+      <c r="BZ14" s="4"/>
+      <c r="CA14" s="4"/>
+      <c r="CB14" s="4"/>
+      <c r="CC14" s="4"/>
+      <c r="CD14" s="4"/>
+      <c r="CE14" s="4"/>
+      <c r="CF14" s="4"/>
+      <c r="CG14" s="4"/>
+      <c r="CH14" s="4"/>
+      <c r="CI14" s="4"/>
+      <c r="CJ14" s="4"/>
+      <c r="CK14" s="4"/>
+      <c r="CL14" s="4"/>
+      <c r="CM14" s="4"/>
+      <c r="CN14" s="4"/>
+      <c r="CO14" s="4"/>
+      <c r="CP14" s="4"/>
+      <c r="CQ14" s="4"/>
+      <c r="CR14" s="4"/>
+      <c r="CS14" s="4"/>
+      <c r="CT14" s="4"/>
+      <c r="CU14" s="4"/>
+      <c r="CV14" s="4"/>
+      <c r="CW14" s="4"/>
+      <c r="CX14" s="4"/>
+      <c r="CY14" s="4"/>
+      <c r="CZ14" s="4"/>
+      <c r="DA14" s="4"/>
+      <c r="DB14" s="4"/>
+      <c r="DC14" s="4"/>
+      <c r="DD14" s="4"/>
+      <c r="DE14" s="4"/>
+      <c r="DF14" s="4"/>
+      <c r="DG14" s="4"/>
+      <c r="DH14" s="4"/>
+      <c r="DI14" s="4"/>
+      <c r="DJ14" s="4"/>
+      <c r="DK14" s="4"/>
+      <c r="DL14" s="4"/>
+      <c r="DM14" s="4"/>
+      <c r="DN14" s="4"/>
+      <c r="DO14" s="4"/>
+      <c r="DP14" s="4"/>
+      <c r="DQ14" s="4"/>
+      <c r="DR14" s="4"/>
+      <c r="DS14" s="4"/>
+    </row>
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4176,80 +4175,80 @@
         <v>34</v>
       </c>
       <c r="AW15" s="2"/>
-      <c r="AZ15" s="5"/>
-      <c r="BA15" s="5"/>
-      <c r="BB15" s="5"/>
-      <c r="BC15" s="5"/>
-      <c r="BD15" s="5"/>
-      <c r="BE15" s="5"/>
-      <c r="BF15" s="5"/>
-      <c r="BG15" s="5"/>
-      <c r="BH15" s="5"/>
-      <c r="BI15" s="5"/>
-      <c r="BJ15" s="5"/>
-      <c r="BK15" s="5"/>
-      <c r="BL15" s="5"/>
-      <c r="BM15" s="5"/>
-      <c r="BN15" s="5"/>
-      <c r="BO15" s="5"/>
-      <c r="BP15" s="5"/>
-      <c r="BQ15" s="5"/>
-      <c r="BR15" s="5"/>
-      <c r="BS15" s="5"/>
-      <c r="BT15" s="5"/>
-      <c r="BU15" s="5"/>
-      <c r="BV15" s="5"/>
-      <c r="BW15" s="5"/>
-      <c r="BX15" s="5"/>
-      <c r="BY15" s="5"/>
-      <c r="BZ15" s="5"/>
-      <c r="CA15" s="5"/>
-      <c r="CB15" s="5"/>
-      <c r="CC15" s="5"/>
-      <c r="CD15" s="5"/>
-      <c r="CE15" s="5"/>
-      <c r="CF15" s="5"/>
-      <c r="CG15" s="5"/>
-      <c r="CH15" s="5"/>
-      <c r="CI15" s="5"/>
-      <c r="CJ15" s="5"/>
-      <c r="CK15" s="5"/>
-      <c r="CL15" s="5"/>
-      <c r="CM15" s="5"/>
-      <c r="CN15" s="5"/>
-      <c r="CO15" s="5"/>
-      <c r="CP15" s="5"/>
-      <c r="CQ15" s="5"/>
-      <c r="CR15" s="5"/>
-      <c r="CS15" s="5"/>
-      <c r="CT15" s="5"/>
-      <c r="CU15" s="5"/>
-      <c r="CV15" s="5"/>
-      <c r="CW15" s="5"/>
-      <c r="CX15" s="5"/>
-      <c r="CY15" s="5"/>
-      <c r="CZ15" s="5"/>
-      <c r="DA15" s="5"/>
-      <c r="DB15" s="5"/>
-      <c r="DC15" s="5"/>
-      <c r="DD15" s="5"/>
-      <c r="DE15" s="5"/>
-      <c r="DF15" s="5"/>
-      <c r="DG15" s="5"/>
-      <c r="DH15" s="5"/>
-      <c r="DI15" s="5"/>
-      <c r="DJ15" s="5"/>
-      <c r="DK15" s="5"/>
-      <c r="DL15" s="5"/>
-      <c r="DM15" s="5"/>
-      <c r="DN15" s="5"/>
-      <c r="DO15" s="5"/>
-      <c r="DP15" s="5"/>
-      <c r="DQ15" s="5"/>
-      <c r="DR15" s="5"/>
-      <c r="DS15" s="5"/>
-    </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="4"/>
+      <c r="BB15" s="4"/>
+      <c r="BC15" s="4"/>
+      <c r="BD15" s="4"/>
+      <c r="BE15" s="4"/>
+      <c r="BF15" s="4"/>
+      <c r="BG15" s="4"/>
+      <c r="BH15" s="4"/>
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="4"/>
+      <c r="BK15" s="4"/>
+      <c r="BL15" s="4"/>
+      <c r="BM15" s="4"/>
+      <c r="BN15" s="4"/>
+      <c r="BO15" s="4"/>
+      <c r="BP15" s="4"/>
+      <c r="BQ15" s="4"/>
+      <c r="BR15" s="4"/>
+      <c r="BS15" s="4"/>
+      <c r="BT15" s="4"/>
+      <c r="BU15" s="4"/>
+      <c r="BV15" s="4"/>
+      <c r="BW15" s="4"/>
+      <c r="BX15" s="4"/>
+      <c r="BY15" s="4"/>
+      <c r="BZ15" s="4"/>
+      <c r="CA15" s="4"/>
+      <c r="CB15" s="4"/>
+      <c r="CC15" s="4"/>
+      <c r="CD15" s="4"/>
+      <c r="CE15" s="4"/>
+      <c r="CF15" s="4"/>
+      <c r="CG15" s="4"/>
+      <c r="CH15" s="4"/>
+      <c r="CI15" s="4"/>
+      <c r="CJ15" s="4"/>
+      <c r="CK15" s="4"/>
+      <c r="CL15" s="4"/>
+      <c r="CM15" s="4"/>
+      <c r="CN15" s="4"/>
+      <c r="CO15" s="4"/>
+      <c r="CP15" s="4"/>
+      <c r="CQ15" s="4"/>
+      <c r="CR15" s="4"/>
+      <c r="CS15" s="4"/>
+      <c r="CT15" s="4"/>
+      <c r="CU15" s="4"/>
+      <c r="CV15" s="4"/>
+      <c r="CW15" s="4"/>
+      <c r="CX15" s="4"/>
+      <c r="CY15" s="4"/>
+      <c r="CZ15" s="4"/>
+      <c r="DA15" s="4"/>
+      <c r="DB15" s="4"/>
+      <c r="DC15" s="4"/>
+      <c r="DD15" s="4"/>
+      <c r="DE15" s="4"/>
+      <c r="DF15" s="4"/>
+      <c r="DG15" s="4"/>
+      <c r="DH15" s="4"/>
+      <c r="DI15" s="4"/>
+      <c r="DJ15" s="4"/>
+      <c r="DK15" s="4"/>
+      <c r="DL15" s="4"/>
+      <c r="DM15" s="4"/>
+      <c r="DN15" s="4"/>
+      <c r="DO15" s="4"/>
+      <c r="DP15" s="4"/>
+      <c r="DQ15" s="4"/>
+      <c r="DR15" s="4"/>
+      <c r="DS15" s="4"/>
+    </row>
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4394,80 +4393,80 @@
         <v>34</v>
       </c>
       <c r="AW16" s="2"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="5"/>
-      <c r="BB16" s="5"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="5"/>
-      <c r="BE16" s="5"/>
-      <c r="BF16" s="5"/>
-      <c r="BG16" s="5"/>
-      <c r="BH16" s="5"/>
-      <c r="BI16" s="5"/>
-      <c r="BJ16" s="5"/>
-      <c r="BK16" s="5"/>
-      <c r="BL16" s="5"/>
-      <c r="BM16" s="5"/>
-      <c r="BN16" s="5"/>
-      <c r="BO16" s="5"/>
-      <c r="BP16" s="5"/>
-      <c r="BQ16" s="5"/>
-      <c r="BR16" s="5"/>
-      <c r="BS16" s="5"/>
-      <c r="BT16" s="5"/>
-      <c r="BU16" s="5"/>
-      <c r="BV16" s="5"/>
-      <c r="BW16" s="5"/>
-      <c r="BX16" s="5"/>
-      <c r="BY16" s="5"/>
-      <c r="BZ16" s="5"/>
-      <c r="CA16" s="5"/>
-      <c r="CB16" s="5"/>
-      <c r="CC16" s="5"/>
-      <c r="CD16" s="5"/>
-      <c r="CE16" s="5"/>
-      <c r="CF16" s="5"/>
-      <c r="CG16" s="5"/>
-      <c r="CH16" s="5"/>
-      <c r="CI16" s="5"/>
-      <c r="CJ16" s="5"/>
-      <c r="CK16" s="5"/>
-      <c r="CL16" s="5"/>
-      <c r="CM16" s="5"/>
-      <c r="CN16" s="5"/>
-      <c r="CO16" s="5"/>
-      <c r="CP16" s="5"/>
-      <c r="CQ16" s="5"/>
-      <c r="CR16" s="5"/>
-      <c r="CS16" s="5"/>
-      <c r="CT16" s="5"/>
-      <c r="CU16" s="5"/>
-      <c r="CV16" s="5"/>
-      <c r="CW16" s="5"/>
-      <c r="CX16" s="5"/>
-      <c r="CY16" s="5"/>
-      <c r="CZ16" s="5"/>
-      <c r="DA16" s="5"/>
-      <c r="DB16" s="5"/>
-      <c r="DC16" s="5"/>
-      <c r="DD16" s="5"/>
-      <c r="DE16" s="5"/>
-      <c r="DF16" s="5"/>
-      <c r="DG16" s="5"/>
-      <c r="DH16" s="5"/>
-      <c r="DI16" s="5"/>
-      <c r="DJ16" s="5"/>
-      <c r="DK16" s="5"/>
-      <c r="DL16" s="5"/>
-      <c r="DM16" s="5"/>
-      <c r="DN16" s="5"/>
-      <c r="DO16" s="5"/>
-      <c r="DP16" s="5"/>
-      <c r="DQ16" s="5"/>
-      <c r="DR16" s="5"/>
-      <c r="DS16" s="5"/>
-    </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="4"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="4"/>
+      <c r="BD16" s="4"/>
+      <c r="BE16" s="4"/>
+      <c r="BF16" s="4"/>
+      <c r="BG16" s="4"/>
+      <c r="BH16" s="4"/>
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="4"/>
+      <c r="BK16" s="4"/>
+      <c r="BL16" s="4"/>
+      <c r="BM16" s="4"/>
+      <c r="BN16" s="4"/>
+      <c r="BO16" s="4"/>
+      <c r="BP16" s="4"/>
+      <c r="BQ16" s="4"/>
+      <c r="BR16" s="4"/>
+      <c r="BS16" s="4"/>
+      <c r="BT16" s="4"/>
+      <c r="BU16" s="4"/>
+      <c r="BV16" s="4"/>
+      <c r="BW16" s="4"/>
+      <c r="BX16" s="4"/>
+      <c r="BY16" s="4"/>
+      <c r="BZ16" s="4"/>
+      <c r="CA16" s="4"/>
+      <c r="CB16" s="4"/>
+      <c r="CC16" s="4"/>
+      <c r="CD16" s="4"/>
+      <c r="CE16" s="4"/>
+      <c r="CF16" s="4"/>
+      <c r="CG16" s="4"/>
+      <c r="CH16" s="4"/>
+      <c r="CI16" s="4"/>
+      <c r="CJ16" s="4"/>
+      <c r="CK16" s="4"/>
+      <c r="CL16" s="4"/>
+      <c r="CM16" s="4"/>
+      <c r="CN16" s="4"/>
+      <c r="CO16" s="4"/>
+      <c r="CP16" s="4"/>
+      <c r="CQ16" s="4"/>
+      <c r="CR16" s="4"/>
+      <c r="CS16" s="4"/>
+      <c r="CT16" s="4"/>
+      <c r="CU16" s="4"/>
+      <c r="CV16" s="4"/>
+      <c r="CW16" s="4"/>
+      <c r="CX16" s="4"/>
+      <c r="CY16" s="4"/>
+      <c r="CZ16" s="4"/>
+      <c r="DA16" s="4"/>
+      <c r="DB16" s="4"/>
+      <c r="DC16" s="4"/>
+      <c r="DD16" s="4"/>
+      <c r="DE16" s="4"/>
+      <c r="DF16" s="4"/>
+      <c r="DG16" s="4"/>
+      <c r="DH16" s="4"/>
+      <c r="DI16" s="4"/>
+      <c r="DJ16" s="4"/>
+      <c r="DK16" s="4"/>
+      <c r="DL16" s="4"/>
+      <c r="DM16" s="4"/>
+      <c r="DN16" s="4"/>
+      <c r="DO16" s="4"/>
+      <c r="DP16" s="4"/>
+      <c r="DQ16" s="4"/>
+      <c r="DR16" s="4"/>
+      <c r="DS16" s="4"/>
+    </row>
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4612,80 +4611,80 @@
         <v>34</v>
       </c>
       <c r="AW17" s="2"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="5"/>
-      <c r="BB17" s="5"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="5"/>
-      <c r="BE17" s="5"/>
-      <c r="BF17" s="5"/>
-      <c r="BG17" s="5"/>
-      <c r="BH17" s="5"/>
-      <c r="BI17" s="5"/>
-      <c r="BJ17" s="5"/>
-      <c r="BK17" s="5"/>
-      <c r="BL17" s="5"/>
-      <c r="BM17" s="5"/>
-      <c r="BN17" s="5"/>
-      <c r="BO17" s="5"/>
-      <c r="BP17" s="5"/>
-      <c r="BQ17" s="5"/>
-      <c r="BR17" s="5"/>
-      <c r="BS17" s="5"/>
-      <c r="BT17" s="5"/>
-      <c r="BU17" s="5"/>
-      <c r="BV17" s="5"/>
-      <c r="BW17" s="5"/>
-      <c r="BX17" s="5"/>
-      <c r="BY17" s="5"/>
-      <c r="BZ17" s="5"/>
-      <c r="CA17" s="5"/>
-      <c r="CB17" s="5"/>
-      <c r="CC17" s="5"/>
-      <c r="CD17" s="5"/>
-      <c r="CE17" s="5"/>
-      <c r="CF17" s="5"/>
-      <c r="CG17" s="5"/>
-      <c r="CH17" s="5"/>
-      <c r="CI17" s="5"/>
-      <c r="CJ17" s="5"/>
-      <c r="CK17" s="5"/>
-      <c r="CL17" s="5"/>
-      <c r="CM17" s="5"/>
-      <c r="CN17" s="5"/>
-      <c r="CO17" s="5"/>
-      <c r="CP17" s="5"/>
-      <c r="CQ17" s="5"/>
-      <c r="CR17" s="5"/>
-      <c r="CS17" s="5"/>
-      <c r="CT17" s="5"/>
-      <c r="CU17" s="5"/>
-      <c r="CV17" s="5"/>
-      <c r="CW17" s="5"/>
-      <c r="CX17" s="5"/>
-      <c r="CY17" s="5"/>
-      <c r="CZ17" s="5"/>
-      <c r="DA17" s="5"/>
-      <c r="DB17" s="5"/>
-      <c r="DC17" s="5"/>
-      <c r="DD17" s="5"/>
-      <c r="DE17" s="5"/>
-      <c r="DF17" s="5"/>
-      <c r="DG17" s="5"/>
-      <c r="DH17" s="5"/>
-      <c r="DI17" s="5"/>
-      <c r="DJ17" s="5"/>
-      <c r="DK17" s="5"/>
-      <c r="DL17" s="5"/>
-      <c r="DM17" s="5"/>
-      <c r="DN17" s="5"/>
-      <c r="DO17" s="5"/>
-      <c r="DP17" s="5"/>
-      <c r="DQ17" s="5"/>
-      <c r="DR17" s="5"/>
-      <c r="DS17" s="5"/>
-    </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="4"/>
+      <c r="BE17" s="4"/>
+      <c r="BF17" s="4"/>
+      <c r="BG17" s="4"/>
+      <c r="BH17" s="4"/>
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="4"/>
+      <c r="BK17" s="4"/>
+      <c r="BL17" s="4"/>
+      <c r="BM17" s="4"/>
+      <c r="BN17" s="4"/>
+      <c r="BO17" s="4"/>
+      <c r="BP17" s="4"/>
+      <c r="BQ17" s="4"/>
+      <c r="BR17" s="4"/>
+      <c r="BS17" s="4"/>
+      <c r="BT17" s="4"/>
+      <c r="BU17" s="4"/>
+      <c r="BV17" s="4"/>
+      <c r="BW17" s="4"/>
+      <c r="BX17" s="4"/>
+      <c r="BY17" s="4"/>
+      <c r="BZ17" s="4"/>
+      <c r="CA17" s="4"/>
+      <c r="CB17" s="4"/>
+      <c r="CC17" s="4"/>
+      <c r="CD17" s="4"/>
+      <c r="CE17" s="4"/>
+      <c r="CF17" s="4"/>
+      <c r="CG17" s="4"/>
+      <c r="CH17" s="4"/>
+      <c r="CI17" s="4"/>
+      <c r="CJ17" s="4"/>
+      <c r="CK17" s="4"/>
+      <c r="CL17" s="4"/>
+      <c r="CM17" s="4"/>
+      <c r="CN17" s="4"/>
+      <c r="CO17" s="4"/>
+      <c r="CP17" s="4"/>
+      <c r="CQ17" s="4"/>
+      <c r="CR17" s="4"/>
+      <c r="CS17" s="4"/>
+      <c r="CT17" s="4"/>
+      <c r="CU17" s="4"/>
+      <c r="CV17" s="4"/>
+      <c r="CW17" s="4"/>
+      <c r="CX17" s="4"/>
+      <c r="CY17" s="4"/>
+      <c r="CZ17" s="4"/>
+      <c r="DA17" s="4"/>
+      <c r="DB17" s="4"/>
+      <c r="DC17" s="4"/>
+      <c r="DD17" s="4"/>
+      <c r="DE17" s="4"/>
+      <c r="DF17" s="4"/>
+      <c r="DG17" s="4"/>
+      <c r="DH17" s="4"/>
+      <c r="DI17" s="4"/>
+      <c r="DJ17" s="4"/>
+      <c r="DK17" s="4"/>
+      <c r="DL17" s="4"/>
+      <c r="DM17" s="4"/>
+      <c r="DN17" s="4"/>
+      <c r="DO17" s="4"/>
+      <c r="DP17" s="4"/>
+      <c r="DQ17" s="4"/>
+      <c r="DR17" s="4"/>
+      <c r="DS17" s="4"/>
+    </row>
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4830,80 +4829,80 @@
         <v>34</v>
       </c>
       <c r="AW18" s="2"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="5"/>
-      <c r="BB18" s="5"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="5"/>
-      <c r="BE18" s="5"/>
-      <c r="BF18" s="5"/>
-      <c r="BG18" s="5"/>
-      <c r="BH18" s="5"/>
-      <c r="BI18" s="5"/>
-      <c r="BJ18" s="5"/>
-      <c r="BK18" s="5"/>
-      <c r="BL18" s="5"/>
-      <c r="BM18" s="5"/>
-      <c r="BN18" s="5"/>
-      <c r="BO18" s="5"/>
-      <c r="BP18" s="5"/>
-      <c r="BQ18" s="5"/>
-      <c r="BR18" s="5"/>
-      <c r="BS18" s="5"/>
-      <c r="BT18" s="5"/>
-      <c r="BU18" s="5"/>
-      <c r="BV18" s="5"/>
-      <c r="BW18" s="5"/>
-      <c r="BX18" s="5"/>
-      <c r="BY18" s="5"/>
-      <c r="BZ18" s="5"/>
-      <c r="CA18" s="5"/>
-      <c r="CB18" s="5"/>
-      <c r="CC18" s="5"/>
-      <c r="CD18" s="5"/>
-      <c r="CE18" s="5"/>
-      <c r="CF18" s="5"/>
-      <c r="CG18" s="5"/>
-      <c r="CH18" s="5"/>
-      <c r="CI18" s="5"/>
-      <c r="CJ18" s="5"/>
-      <c r="CK18" s="5"/>
-      <c r="CL18" s="5"/>
-      <c r="CM18" s="5"/>
-      <c r="CN18" s="5"/>
-      <c r="CO18" s="5"/>
-      <c r="CP18" s="5"/>
-      <c r="CQ18" s="5"/>
-      <c r="CR18" s="5"/>
-      <c r="CS18" s="5"/>
-      <c r="CT18" s="5"/>
-      <c r="CU18" s="5"/>
-      <c r="CV18" s="5"/>
-      <c r="CW18" s="5"/>
-      <c r="CX18" s="5"/>
-      <c r="CY18" s="5"/>
-      <c r="CZ18" s="5"/>
-      <c r="DA18" s="5"/>
-      <c r="DB18" s="5"/>
-      <c r="DC18" s="5"/>
-      <c r="DD18" s="5"/>
-      <c r="DE18" s="5"/>
-      <c r="DF18" s="5"/>
-      <c r="DG18" s="5"/>
-      <c r="DH18" s="5"/>
-      <c r="DI18" s="5"/>
-      <c r="DJ18" s="5"/>
-      <c r="DK18" s="5"/>
-      <c r="DL18" s="5"/>
-      <c r="DM18" s="5"/>
-      <c r="DN18" s="5"/>
-      <c r="DO18" s="5"/>
-      <c r="DP18" s="5"/>
-      <c r="DQ18" s="5"/>
-      <c r="DR18" s="5"/>
-      <c r="DS18" s="5"/>
-    </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="4"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="4"/>
+      <c r="BD18" s="4"/>
+      <c r="BE18" s="4"/>
+      <c r="BF18" s="4"/>
+      <c r="BG18" s="4"/>
+      <c r="BH18" s="4"/>
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="4"/>
+      <c r="BL18" s="4"/>
+      <c r="BM18" s="4"/>
+      <c r="BN18" s="4"/>
+      <c r="BO18" s="4"/>
+      <c r="BP18" s="4"/>
+      <c r="BQ18" s="4"/>
+      <c r="BR18" s="4"/>
+      <c r="BS18" s="4"/>
+      <c r="BT18" s="4"/>
+      <c r="BU18" s="4"/>
+      <c r="BV18" s="4"/>
+      <c r="BW18" s="4"/>
+      <c r="BX18" s="4"/>
+      <c r="BY18" s="4"/>
+      <c r="BZ18" s="4"/>
+      <c r="CA18" s="4"/>
+      <c r="CB18" s="4"/>
+      <c r="CC18" s="4"/>
+      <c r="CD18" s="4"/>
+      <c r="CE18" s="4"/>
+      <c r="CF18" s="4"/>
+      <c r="CG18" s="4"/>
+      <c r="CH18" s="4"/>
+      <c r="CI18" s="4"/>
+      <c r="CJ18" s="4"/>
+      <c r="CK18" s="4"/>
+      <c r="CL18" s="4"/>
+      <c r="CM18" s="4"/>
+      <c r="CN18" s="4"/>
+      <c r="CO18" s="4"/>
+      <c r="CP18" s="4"/>
+      <c r="CQ18" s="4"/>
+      <c r="CR18" s="4"/>
+      <c r="CS18" s="4"/>
+      <c r="CT18" s="4"/>
+      <c r="CU18" s="4"/>
+      <c r="CV18" s="4"/>
+      <c r="CW18" s="4"/>
+      <c r="CX18" s="4"/>
+      <c r="CY18" s="4"/>
+      <c r="CZ18" s="4"/>
+      <c r="DA18" s="4"/>
+      <c r="DB18" s="4"/>
+      <c r="DC18" s="4"/>
+      <c r="DD18" s="4"/>
+      <c r="DE18" s="4"/>
+      <c r="DF18" s="4"/>
+      <c r="DG18" s="4"/>
+      <c r="DH18" s="4"/>
+      <c r="DI18" s="4"/>
+      <c r="DJ18" s="4"/>
+      <c r="DK18" s="4"/>
+      <c r="DL18" s="4"/>
+      <c r="DM18" s="4"/>
+      <c r="DN18" s="4"/>
+      <c r="DO18" s="4"/>
+      <c r="DP18" s="4"/>
+      <c r="DQ18" s="4"/>
+      <c r="DR18" s="4"/>
+      <c r="DS18" s="4"/>
+    </row>
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5048,80 +5047,80 @@
         <v>34</v>
       </c>
       <c r="AW19" s="2"/>
-      <c r="AZ19" s="5"/>
-      <c r="BA19" s="5"/>
-      <c r="BB19" s="5"/>
-      <c r="BC19" s="5"/>
-      <c r="BD19" s="5"/>
-      <c r="BE19" s="5"/>
-      <c r="BF19" s="5"/>
-      <c r="BG19" s="5"/>
-      <c r="BH19" s="5"/>
-      <c r="BI19" s="5"/>
-      <c r="BJ19" s="5"/>
-      <c r="BK19" s="5"/>
-      <c r="BL19" s="5"/>
-      <c r="BM19" s="5"/>
-      <c r="BN19" s="5"/>
-      <c r="BO19" s="5"/>
-      <c r="BP19" s="5"/>
-      <c r="BQ19" s="5"/>
-      <c r="BR19" s="5"/>
-      <c r="BS19" s="5"/>
-      <c r="BT19" s="5"/>
-      <c r="BU19" s="5"/>
-      <c r="BV19" s="5"/>
-      <c r="BW19" s="5"/>
-      <c r="BX19" s="5"/>
-      <c r="BY19" s="5"/>
-      <c r="BZ19" s="5"/>
-      <c r="CA19" s="5"/>
-      <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
-      <c r="CD19" s="5"/>
-      <c r="CE19" s="5"/>
-      <c r="CF19" s="5"/>
-      <c r="CG19" s="5"/>
-      <c r="CH19" s="5"/>
-      <c r="CI19" s="5"/>
-      <c r="CJ19" s="5"/>
-      <c r="CK19" s="5"/>
-      <c r="CL19" s="5"/>
-      <c r="CM19" s="5"/>
-      <c r="CN19" s="5"/>
-      <c r="CO19" s="5"/>
-      <c r="CP19" s="5"/>
-      <c r="CQ19" s="5"/>
-      <c r="CR19" s="5"/>
-      <c r="CS19" s="5"/>
-      <c r="CT19" s="5"/>
-      <c r="CU19" s="5"/>
-      <c r="CV19" s="5"/>
-      <c r="CW19" s="5"/>
-      <c r="CX19" s="5"/>
-      <c r="CY19" s="5"/>
-      <c r="CZ19" s="5"/>
-      <c r="DA19" s="5"/>
-      <c r="DB19" s="5"/>
-      <c r="DC19" s="5"/>
-      <c r="DD19" s="5"/>
-      <c r="DE19" s="5"/>
-      <c r="DF19" s="5"/>
-      <c r="DG19" s="5"/>
-      <c r="DH19" s="5"/>
-      <c r="DI19" s="5"/>
-      <c r="DJ19" s="5"/>
-      <c r="DK19" s="5"/>
-      <c r="DL19" s="5"/>
-      <c r="DM19" s="5"/>
-      <c r="DN19" s="5"/>
-      <c r="DO19" s="5"/>
-      <c r="DP19" s="5"/>
-      <c r="DQ19" s="5"/>
-      <c r="DR19" s="5"/>
-      <c r="DS19" s="5"/>
-    </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="4"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="4"/>
+      <c r="BD19" s="4"/>
+      <c r="BE19" s="4"/>
+      <c r="BF19" s="4"/>
+      <c r="BG19" s="4"/>
+      <c r="BH19" s="4"/>
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="4"/>
+      <c r="BL19" s="4"/>
+      <c r="BM19" s="4"/>
+      <c r="BN19" s="4"/>
+      <c r="BO19" s="4"/>
+      <c r="BP19" s="4"/>
+      <c r="BQ19" s="4"/>
+      <c r="BR19" s="4"/>
+      <c r="BS19" s="4"/>
+      <c r="BT19" s="4"/>
+      <c r="BU19" s="4"/>
+      <c r="BV19" s="4"/>
+      <c r="BW19" s="4"/>
+      <c r="BX19" s="4"/>
+      <c r="BY19" s="4"/>
+      <c r="BZ19" s="4"/>
+      <c r="CA19" s="4"/>
+      <c r="CB19" s="4"/>
+      <c r="CC19" s="4"/>
+      <c r="CD19" s="4"/>
+      <c r="CE19" s="4"/>
+      <c r="CF19" s="4"/>
+      <c r="CG19" s="4"/>
+      <c r="CH19" s="4"/>
+      <c r="CI19" s="4"/>
+      <c r="CJ19" s="4"/>
+      <c r="CK19" s="4"/>
+      <c r="CL19" s="4"/>
+      <c r="CM19" s="4"/>
+      <c r="CN19" s="4"/>
+      <c r="CO19" s="4"/>
+      <c r="CP19" s="4"/>
+      <c r="CQ19" s="4"/>
+      <c r="CR19" s="4"/>
+      <c r="CS19" s="4"/>
+      <c r="CT19" s="4"/>
+      <c r="CU19" s="4"/>
+      <c r="CV19" s="4"/>
+      <c r="CW19" s="4"/>
+      <c r="CX19" s="4"/>
+      <c r="CY19" s="4"/>
+      <c r="CZ19" s="4"/>
+      <c r="DA19" s="4"/>
+      <c r="DB19" s="4"/>
+      <c r="DC19" s="4"/>
+      <c r="DD19" s="4"/>
+      <c r="DE19" s="4"/>
+      <c r="DF19" s="4"/>
+      <c r="DG19" s="4"/>
+      <c r="DH19" s="4"/>
+      <c r="DI19" s="4"/>
+      <c r="DJ19" s="4"/>
+      <c r="DK19" s="4"/>
+      <c r="DL19" s="4"/>
+      <c r="DM19" s="4"/>
+      <c r="DN19" s="4"/>
+      <c r="DO19" s="4"/>
+      <c r="DP19" s="4"/>
+      <c r="DQ19" s="4"/>
+      <c r="DR19" s="4"/>
+      <c r="DS19" s="4"/>
+    </row>
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5266,80 +5265,80 @@
         <v>34</v>
       </c>
       <c r="AW20" s="2"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="5"/>
-      <c r="BI20" s="5"/>
-      <c r="BJ20" s="5"/>
-      <c r="BK20" s="5"/>
-      <c r="BL20" s="5"/>
-      <c r="BM20" s="5"/>
-      <c r="BN20" s="5"/>
-      <c r="BO20" s="5"/>
-      <c r="BP20" s="5"/>
-      <c r="BQ20" s="5"/>
-      <c r="BR20" s="5"/>
-      <c r="BS20" s="5"/>
-      <c r="BT20" s="5"/>
-      <c r="BU20" s="5"/>
-      <c r="BV20" s="5"/>
-      <c r="BW20" s="5"/>
-      <c r="BX20" s="5"/>
-      <c r="BY20" s="5"/>
-      <c r="BZ20" s="5"/>
-      <c r="CA20" s="5"/>
-      <c r="CB20" s="5"/>
-      <c r="CC20" s="5"/>
-      <c r="CD20" s="5"/>
-      <c r="CE20" s="5"/>
-      <c r="CF20" s="5"/>
-      <c r="CG20" s="5"/>
-      <c r="CH20" s="5"/>
-      <c r="CI20" s="5"/>
-      <c r="CJ20" s="5"/>
-      <c r="CK20" s="5"/>
-      <c r="CL20" s="5"/>
-      <c r="CM20" s="5"/>
-      <c r="CN20" s="5"/>
-      <c r="CO20" s="5"/>
-      <c r="CP20" s="5"/>
-      <c r="CQ20" s="5"/>
-      <c r="CR20" s="5"/>
-      <c r="CS20" s="5"/>
-      <c r="CT20" s="5"/>
-      <c r="CU20" s="5"/>
-      <c r="CV20" s="5"/>
-      <c r="CW20" s="5"/>
-      <c r="CX20" s="5"/>
-      <c r="CY20" s="5"/>
-      <c r="CZ20" s="5"/>
-      <c r="DA20" s="5"/>
-      <c r="DB20" s="5"/>
-      <c r="DC20" s="5"/>
-      <c r="DD20" s="5"/>
-      <c r="DE20" s="5"/>
-      <c r="DF20" s="5"/>
-      <c r="DG20" s="5"/>
-      <c r="DH20" s="5"/>
-      <c r="DI20" s="5"/>
-      <c r="DJ20" s="5"/>
-      <c r="DK20" s="5"/>
-      <c r="DL20" s="5"/>
-      <c r="DM20" s="5"/>
-      <c r="DN20" s="5"/>
-      <c r="DO20" s="5"/>
-      <c r="DP20" s="5"/>
-      <c r="DQ20" s="5"/>
-      <c r="DR20" s="5"/>
-      <c r="DS20" s="5"/>
-    </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="4"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="4"/>
+      <c r="BG20" s="4"/>
+      <c r="BH20" s="4"/>
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+      <c r="BM20" s="4"/>
+      <c r="BN20" s="4"/>
+      <c r="BO20" s="4"/>
+      <c r="BP20" s="4"/>
+      <c r="BQ20" s="4"/>
+      <c r="BR20" s="4"/>
+      <c r="BS20" s="4"/>
+      <c r="BT20" s="4"/>
+      <c r="BU20" s="4"/>
+      <c r="BV20" s="4"/>
+      <c r="BW20" s="4"/>
+      <c r="BX20" s="4"/>
+      <c r="BY20" s="4"/>
+      <c r="BZ20" s="4"/>
+      <c r="CA20" s="4"/>
+      <c r="CB20" s="4"/>
+      <c r="CC20" s="4"/>
+      <c r="CD20" s="4"/>
+      <c r="CE20" s="4"/>
+      <c r="CF20" s="4"/>
+      <c r="CG20" s="4"/>
+      <c r="CH20" s="4"/>
+      <c r="CI20" s="4"/>
+      <c r="CJ20" s="4"/>
+      <c r="CK20" s="4"/>
+      <c r="CL20" s="4"/>
+      <c r="CM20" s="4"/>
+      <c r="CN20" s="4"/>
+      <c r="CO20" s="4"/>
+      <c r="CP20" s="4"/>
+      <c r="CQ20" s="4"/>
+      <c r="CR20" s="4"/>
+      <c r="CS20" s="4"/>
+      <c r="CT20" s="4"/>
+      <c r="CU20" s="4"/>
+      <c r="CV20" s="4"/>
+      <c r="CW20" s="4"/>
+      <c r="CX20" s="4"/>
+      <c r="CY20" s="4"/>
+      <c r="CZ20" s="4"/>
+      <c r="DA20" s="4"/>
+      <c r="DB20" s="4"/>
+      <c r="DC20" s="4"/>
+      <c r="DD20" s="4"/>
+      <c r="DE20" s="4"/>
+      <c r="DF20" s="4"/>
+      <c r="DG20" s="4"/>
+      <c r="DH20" s="4"/>
+      <c r="DI20" s="4"/>
+      <c r="DJ20" s="4"/>
+      <c r="DK20" s="4"/>
+      <c r="DL20" s="4"/>
+      <c r="DM20" s="4"/>
+      <c r="DN20" s="4"/>
+      <c r="DO20" s="4"/>
+      <c r="DP20" s="4"/>
+      <c r="DQ20" s="4"/>
+      <c r="DR20" s="4"/>
+      <c r="DS20" s="4"/>
+    </row>
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5484,80 +5483,80 @@
         <v>34</v>
       </c>
       <c r="AW21" s="2"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="5"/>
-      <c r="BB21" s="5"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="5"/>
-      <c r="BE21" s="5"/>
-      <c r="BF21" s="5"/>
-      <c r="BG21" s="5"/>
-      <c r="BH21" s="5"/>
-      <c r="BI21" s="5"/>
-      <c r="BJ21" s="5"/>
-      <c r="BK21" s="5"/>
-      <c r="BL21" s="5"/>
-      <c r="BM21" s="5"/>
-      <c r="BN21" s="5"/>
-      <c r="BO21" s="5"/>
-      <c r="BP21" s="5"/>
-      <c r="BQ21" s="5"/>
-      <c r="BR21" s="5"/>
-      <c r="BS21" s="5"/>
-      <c r="BT21" s="5"/>
-      <c r="BU21" s="5"/>
-      <c r="BV21" s="5"/>
-      <c r="BW21" s="5"/>
-      <c r="BX21" s="5"/>
-      <c r="BY21" s="5"/>
-      <c r="BZ21" s="5"/>
-      <c r="CA21" s="5"/>
-      <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="5"/>
-      <c r="CE21" s="5"/>
-      <c r="CF21" s="5"/>
-      <c r="CG21" s="5"/>
-      <c r="CH21" s="5"/>
-      <c r="CI21" s="5"/>
-      <c r="CJ21" s="5"/>
-      <c r="CK21" s="5"/>
-      <c r="CL21" s="5"/>
-      <c r="CM21" s="5"/>
-      <c r="CN21" s="5"/>
-      <c r="CO21" s="5"/>
-      <c r="CP21" s="5"/>
-      <c r="CQ21" s="5"/>
-      <c r="CR21" s="5"/>
-      <c r="CS21" s="5"/>
-      <c r="CT21" s="5"/>
-      <c r="CU21" s="5"/>
-      <c r="CV21" s="5"/>
-      <c r="CW21" s="5"/>
-      <c r="CX21" s="5"/>
-      <c r="CY21" s="5"/>
-      <c r="CZ21" s="5"/>
-      <c r="DA21" s="5"/>
-      <c r="DB21" s="5"/>
-      <c r="DC21" s="5"/>
-      <c r="DD21" s="5"/>
-      <c r="DE21" s="5"/>
-      <c r="DF21" s="5"/>
-      <c r="DG21" s="5"/>
-      <c r="DH21" s="5"/>
-      <c r="DI21" s="5"/>
-      <c r="DJ21" s="5"/>
-      <c r="DK21" s="5"/>
-      <c r="DL21" s="5"/>
-      <c r="DM21" s="5"/>
-      <c r="DN21" s="5"/>
-      <c r="DO21" s="5"/>
-      <c r="DP21" s="5"/>
-      <c r="DQ21" s="5"/>
-      <c r="DR21" s="5"/>
-      <c r="DS21" s="5"/>
-    </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="4"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="4"/>
+      <c r="BG21" s="4"/>
+      <c r="BH21" s="4"/>
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+      <c r="BM21" s="4"/>
+      <c r="BN21" s="4"/>
+      <c r="BO21" s="4"/>
+      <c r="BP21" s="4"/>
+      <c r="BQ21" s="4"/>
+      <c r="BR21" s="4"/>
+      <c r="BS21" s="4"/>
+      <c r="BT21" s="4"/>
+      <c r="BU21" s="4"/>
+      <c r="BV21" s="4"/>
+      <c r="BW21" s="4"/>
+      <c r="BX21" s="4"/>
+      <c r="BY21" s="4"/>
+      <c r="BZ21" s="4"/>
+      <c r="CA21" s="4"/>
+      <c r="CB21" s="4"/>
+      <c r="CC21" s="4"/>
+      <c r="CD21" s="4"/>
+      <c r="CE21" s="4"/>
+      <c r="CF21" s="4"/>
+      <c r="CG21" s="4"/>
+      <c r="CH21" s="4"/>
+      <c r="CI21" s="4"/>
+      <c r="CJ21" s="4"/>
+      <c r="CK21" s="4"/>
+      <c r="CL21" s="4"/>
+      <c r="CM21" s="4"/>
+      <c r="CN21" s="4"/>
+      <c r="CO21" s="4"/>
+      <c r="CP21" s="4"/>
+      <c r="CQ21" s="4"/>
+      <c r="CR21" s="4"/>
+      <c r="CS21" s="4"/>
+      <c r="CT21" s="4"/>
+      <c r="CU21" s="4"/>
+      <c r="CV21" s="4"/>
+      <c r="CW21" s="4"/>
+      <c r="CX21" s="4"/>
+      <c r="CY21" s="4"/>
+      <c r="CZ21" s="4"/>
+      <c r="DA21" s="4"/>
+      <c r="DB21" s="4"/>
+      <c r="DC21" s="4"/>
+      <c r="DD21" s="4"/>
+      <c r="DE21" s="4"/>
+      <c r="DF21" s="4"/>
+      <c r="DG21" s="4"/>
+      <c r="DH21" s="4"/>
+      <c r="DI21" s="4"/>
+      <c r="DJ21" s="4"/>
+      <c r="DK21" s="4"/>
+      <c r="DL21" s="4"/>
+      <c r="DM21" s="4"/>
+      <c r="DN21" s="4"/>
+      <c r="DO21" s="4"/>
+      <c r="DP21" s="4"/>
+      <c r="DQ21" s="4"/>
+      <c r="DR21" s="4"/>
+      <c r="DS21" s="4"/>
+    </row>
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5702,80 +5701,80 @@
         <v>34</v>
       </c>
       <c r="AW22" s="2"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
-      <c r="BN22" s="5"/>
-      <c r="BO22" s="5"/>
-      <c r="BP22" s="5"/>
-      <c r="BQ22" s="5"/>
-      <c r="BR22" s="5"/>
-      <c r="BS22" s="5"/>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CG22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CL22" s="5"/>
-      <c r="CM22" s="5"/>
-      <c r="CN22" s="5"/>
-      <c r="CO22" s="5"/>
-      <c r="CP22" s="5"/>
-      <c r="CQ22" s="5"/>
-      <c r="CR22" s="5"/>
-      <c r="CS22" s="5"/>
-      <c r="CT22" s="5"/>
-      <c r="CU22" s="5"/>
-      <c r="CV22" s="5"/>
-      <c r="CW22" s="5"/>
-      <c r="CX22" s="5"/>
-      <c r="CY22" s="5"/>
-      <c r="CZ22" s="5"/>
-      <c r="DA22" s="5"/>
-      <c r="DB22" s="5"/>
-      <c r="DC22" s="5"/>
-      <c r="DD22" s="5"/>
-      <c r="DE22" s="5"/>
-      <c r="DF22" s="5"/>
-      <c r="DG22" s="5"/>
-      <c r="DH22" s="5"/>
-      <c r="DI22" s="5"/>
-      <c r="DJ22" s="5"/>
-      <c r="DK22" s="5"/>
-      <c r="DL22" s="5"/>
-      <c r="DM22" s="5"/>
-      <c r="DN22" s="5"/>
-      <c r="DO22" s="5"/>
-      <c r="DP22" s="5"/>
-      <c r="DQ22" s="5"/>
-      <c r="DR22" s="5"/>
-      <c r="DS22" s="5"/>
-    </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="4"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="4"/>
+      <c r="BN22" s="4"/>
+      <c r="BO22" s="4"/>
+      <c r="BP22" s="4"/>
+      <c r="BQ22" s="4"/>
+      <c r="BR22" s="4"/>
+      <c r="BS22" s="4"/>
+      <c r="BT22" s="4"/>
+      <c r="BU22" s="4"/>
+      <c r="BV22" s="4"/>
+      <c r="BW22" s="4"/>
+      <c r="BX22" s="4"/>
+      <c r="BY22" s="4"/>
+      <c r="BZ22" s="4"/>
+      <c r="CA22" s="4"/>
+      <c r="CB22" s="4"/>
+      <c r="CC22" s="4"/>
+      <c r="CD22" s="4"/>
+      <c r="CE22" s="4"/>
+      <c r="CF22" s="4"/>
+      <c r="CG22" s="4"/>
+      <c r="CH22" s="4"/>
+      <c r="CI22" s="4"/>
+      <c r="CJ22" s="4"/>
+      <c r="CK22" s="4"/>
+      <c r="CL22" s="4"/>
+      <c r="CM22" s="4"/>
+      <c r="CN22" s="4"/>
+      <c r="CO22" s="4"/>
+      <c r="CP22" s="4"/>
+      <c r="CQ22" s="4"/>
+      <c r="CR22" s="4"/>
+      <c r="CS22" s="4"/>
+      <c r="CT22" s="4"/>
+      <c r="CU22" s="4"/>
+      <c r="CV22" s="4"/>
+      <c r="CW22" s="4"/>
+      <c r="CX22" s="4"/>
+      <c r="CY22" s="4"/>
+      <c r="CZ22" s="4"/>
+      <c r="DA22" s="4"/>
+      <c r="DB22" s="4"/>
+      <c r="DC22" s="4"/>
+      <c r="DD22" s="4"/>
+      <c r="DE22" s="4"/>
+      <c r="DF22" s="4"/>
+      <c r="DG22" s="4"/>
+      <c r="DH22" s="4"/>
+      <c r="DI22" s="4"/>
+      <c r="DJ22" s="4"/>
+      <c r="DK22" s="4"/>
+      <c r="DL22" s="4"/>
+      <c r="DM22" s="4"/>
+      <c r="DN22" s="4"/>
+      <c r="DO22" s="4"/>
+      <c r="DP22" s="4"/>
+      <c r="DQ22" s="4"/>
+      <c r="DR22" s="4"/>
+      <c r="DS22" s="4"/>
+    </row>
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5920,80 +5919,80 @@
         <v>34</v>
       </c>
       <c r="AW23" s="2"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="5"/>
-      <c r="BE23" s="5"/>
-      <c r="BF23" s="5"/>
-      <c r="BG23" s="5"/>
-      <c r="BH23" s="5"/>
-      <c r="BI23" s="5"/>
-      <c r="BJ23" s="5"/>
-      <c r="BK23" s="5"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="5"/>
-      <c r="BN23" s="5"/>
-      <c r="BO23" s="5"/>
-      <c r="BP23" s="5"/>
-      <c r="BQ23" s="5"/>
-      <c r="BR23" s="5"/>
-      <c r="BS23" s="5"/>
-      <c r="BT23" s="5"/>
-      <c r="BU23" s="5"/>
-      <c r="BV23" s="5"/>
-      <c r="BW23" s="5"/>
-      <c r="BX23" s="5"/>
-      <c r="BY23" s="5"/>
-      <c r="BZ23" s="5"/>
-      <c r="CA23" s="5"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CG23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
-      <c r="CK23" s="5"/>
-      <c r="CL23" s="5"/>
-      <c r="CM23" s="5"/>
-      <c r="CN23" s="5"/>
-      <c r="CO23" s="5"/>
-      <c r="CP23" s="5"/>
-      <c r="CQ23" s="5"/>
-      <c r="CR23" s="5"/>
-      <c r="CS23" s="5"/>
-      <c r="CT23" s="5"/>
-      <c r="CU23" s="5"/>
-      <c r="CV23" s="5"/>
-      <c r="CW23" s="5"/>
-      <c r="CX23" s="5"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="5"/>
-      <c r="DA23" s="5"/>
-      <c r="DB23" s="5"/>
-      <c r="DC23" s="5"/>
-      <c r="DD23" s="5"/>
-      <c r="DE23" s="5"/>
-      <c r="DF23" s="5"/>
-      <c r="DG23" s="5"/>
-      <c r="DH23" s="5"/>
-      <c r="DI23" s="5"/>
-      <c r="DJ23" s="5"/>
-      <c r="DK23" s="5"/>
-      <c r="DL23" s="5"/>
-      <c r="DM23" s="5"/>
-      <c r="DN23" s="5"/>
-      <c r="DO23" s="5"/>
-      <c r="DP23" s="5"/>
-      <c r="DQ23" s="5"/>
-      <c r="DR23" s="5"/>
-      <c r="DS23" s="5"/>
-    </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
+      <c r="BH23" s="4"/>
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+      <c r="BM23" s="4"/>
+      <c r="BN23" s="4"/>
+      <c r="BO23" s="4"/>
+      <c r="BP23" s="4"/>
+      <c r="BQ23" s="4"/>
+      <c r="BR23" s="4"/>
+      <c r="BS23" s="4"/>
+      <c r="BT23" s="4"/>
+      <c r="BU23" s="4"/>
+      <c r="BV23" s="4"/>
+      <c r="BW23" s="4"/>
+      <c r="BX23" s="4"/>
+      <c r="BY23" s="4"/>
+      <c r="BZ23" s="4"/>
+      <c r="CA23" s="4"/>
+      <c r="CB23" s="4"/>
+      <c r="CC23" s="4"/>
+      <c r="CD23" s="4"/>
+      <c r="CE23" s="4"/>
+      <c r="CF23" s="4"/>
+      <c r="CG23" s="4"/>
+      <c r="CH23" s="4"/>
+      <c r="CI23" s="4"/>
+      <c r="CJ23" s="4"/>
+      <c r="CK23" s="4"/>
+      <c r="CL23" s="4"/>
+      <c r="CM23" s="4"/>
+      <c r="CN23" s="4"/>
+      <c r="CO23" s="4"/>
+      <c r="CP23" s="4"/>
+      <c r="CQ23" s="4"/>
+      <c r="CR23" s="4"/>
+      <c r="CS23" s="4"/>
+      <c r="CT23" s="4"/>
+      <c r="CU23" s="4"/>
+      <c r="CV23" s="4"/>
+      <c r="CW23" s="4"/>
+      <c r="CX23" s="4"/>
+      <c r="CY23" s="4"/>
+      <c r="CZ23" s="4"/>
+      <c r="DA23" s="4"/>
+      <c r="DB23" s="4"/>
+      <c r="DC23" s="4"/>
+      <c r="DD23" s="4"/>
+      <c r="DE23" s="4"/>
+      <c r="DF23" s="4"/>
+      <c r="DG23" s="4"/>
+      <c r="DH23" s="4"/>
+      <c r="DI23" s="4"/>
+      <c r="DJ23" s="4"/>
+      <c r="DK23" s="4"/>
+      <c r="DL23" s="4"/>
+      <c r="DM23" s="4"/>
+      <c r="DN23" s="4"/>
+      <c r="DO23" s="4"/>
+      <c r="DP23" s="4"/>
+      <c r="DQ23" s="4"/>
+      <c r="DR23" s="4"/>
+      <c r="DS23" s="4"/>
+    </row>
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6138,80 +6137,80 @@
         <v>34</v>
       </c>
       <c r="AW24" s="2"/>
-      <c r="AZ24" s="5"/>
-      <c r="BA24" s="5"/>
-      <c r="BB24" s="5"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="5"/>
-      <c r="BE24" s="5"/>
-      <c r="BF24" s="5"/>
-      <c r="BG24" s="5"/>
-      <c r="BH24" s="5"/>
-      <c r="BI24" s="5"/>
-      <c r="BJ24" s="5"/>
-      <c r="BK24" s="5"/>
-      <c r="BL24" s="5"/>
-      <c r="BM24" s="5"/>
-      <c r="BN24" s="5"/>
-      <c r="BO24" s="5"/>
-      <c r="BP24" s="5"/>
-      <c r="BQ24" s="5"/>
-      <c r="BR24" s="5"/>
-      <c r="BS24" s="5"/>
-      <c r="BT24" s="5"/>
-      <c r="BU24" s="5"/>
-      <c r="BV24" s="5"/>
-      <c r="BW24" s="5"/>
-      <c r="BX24" s="5"/>
-      <c r="BY24" s="5"/>
-      <c r="BZ24" s="5"/>
-      <c r="CA24" s="5"/>
-      <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
-      <c r="CD24" s="5"/>
-      <c r="CE24" s="5"/>
-      <c r="CF24" s="5"/>
-      <c r="CG24" s="5"/>
-      <c r="CH24" s="5"/>
-      <c r="CI24" s="5"/>
-      <c r="CJ24" s="5"/>
-      <c r="CK24" s="5"/>
-      <c r="CL24" s="5"/>
-      <c r="CM24" s="5"/>
-      <c r="CN24" s="5"/>
-      <c r="CO24" s="5"/>
-      <c r="CP24" s="5"/>
-      <c r="CQ24" s="5"/>
-      <c r="CR24" s="5"/>
-      <c r="CS24" s="5"/>
-      <c r="CT24" s="5"/>
-      <c r="CU24" s="5"/>
-      <c r="CV24" s="5"/>
-      <c r="CW24" s="5"/>
-      <c r="CX24" s="5"/>
-      <c r="CY24" s="5"/>
-      <c r="CZ24" s="5"/>
-      <c r="DA24" s="5"/>
-      <c r="DB24" s="5"/>
-      <c r="DC24" s="5"/>
-      <c r="DD24" s="5"/>
-      <c r="DE24" s="5"/>
-      <c r="DF24" s="5"/>
-      <c r="DG24" s="5"/>
-      <c r="DH24" s="5"/>
-      <c r="DI24" s="5"/>
-      <c r="DJ24" s="5"/>
-      <c r="DK24" s="5"/>
-      <c r="DL24" s="5"/>
-      <c r="DM24" s="5"/>
-      <c r="DN24" s="5"/>
-      <c r="DO24" s="5"/>
-      <c r="DP24" s="5"/>
-      <c r="DQ24" s="5"/>
-      <c r="DR24" s="5"/>
-      <c r="DS24" s="5"/>
-    </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="4"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="4"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="4"/>
+      <c r="BG24" s="4"/>
+      <c r="BH24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+      <c r="BM24" s="4"/>
+      <c r="BN24" s="4"/>
+      <c r="BO24" s="4"/>
+      <c r="BP24" s="4"/>
+      <c r="BQ24" s="4"/>
+      <c r="BR24" s="4"/>
+      <c r="BS24" s="4"/>
+      <c r="BT24" s="4"/>
+      <c r="BU24" s="4"/>
+      <c r="BV24" s="4"/>
+      <c r="BW24" s="4"/>
+      <c r="BX24" s="4"/>
+      <c r="BY24" s="4"/>
+      <c r="BZ24" s="4"/>
+      <c r="CA24" s="4"/>
+      <c r="CB24" s="4"/>
+      <c r="CC24" s="4"/>
+      <c r="CD24" s="4"/>
+      <c r="CE24" s="4"/>
+      <c r="CF24" s="4"/>
+      <c r="CG24" s="4"/>
+      <c r="CH24" s="4"/>
+      <c r="CI24" s="4"/>
+      <c r="CJ24" s="4"/>
+      <c r="CK24" s="4"/>
+      <c r="CL24" s="4"/>
+      <c r="CM24" s="4"/>
+      <c r="CN24" s="4"/>
+      <c r="CO24" s="4"/>
+      <c r="CP24" s="4"/>
+      <c r="CQ24" s="4"/>
+      <c r="CR24" s="4"/>
+      <c r="CS24" s="4"/>
+      <c r="CT24" s="4"/>
+      <c r="CU24" s="4"/>
+      <c r="CV24" s="4"/>
+      <c r="CW24" s="4"/>
+      <c r="CX24" s="4"/>
+      <c r="CY24" s="4"/>
+      <c r="CZ24" s="4"/>
+      <c r="DA24" s="4"/>
+      <c r="DB24" s="4"/>
+      <c r="DC24" s="4"/>
+      <c r="DD24" s="4"/>
+      <c r="DE24" s="4"/>
+      <c r="DF24" s="4"/>
+      <c r="DG24" s="4"/>
+      <c r="DH24" s="4"/>
+      <c r="DI24" s="4"/>
+      <c r="DJ24" s="4"/>
+      <c r="DK24" s="4"/>
+      <c r="DL24" s="4"/>
+      <c r="DM24" s="4"/>
+      <c r="DN24" s="4"/>
+      <c r="DO24" s="4"/>
+      <c r="DP24" s="4"/>
+      <c r="DQ24" s="4"/>
+      <c r="DR24" s="4"/>
+      <c r="DS24" s="4"/>
+    </row>
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6356,80 +6355,80 @@
         <v>34</v>
       </c>
       <c r="AW25" s="2"/>
-      <c r="AZ25" s="5"/>
-      <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="5"/>
-      <c r="BE25" s="5"/>
-      <c r="BF25" s="5"/>
-      <c r="BG25" s="5"/>
-      <c r="BH25" s="5"/>
-      <c r="BI25" s="5"/>
-      <c r="BJ25" s="5"/>
-      <c r="BK25" s="5"/>
-      <c r="BL25" s="5"/>
-      <c r="BM25" s="5"/>
-      <c r="BN25" s="5"/>
-      <c r="BO25" s="5"/>
-      <c r="BP25" s="5"/>
-      <c r="BQ25" s="5"/>
-      <c r="BR25" s="5"/>
-      <c r="BS25" s="5"/>
-      <c r="BT25" s="5"/>
-      <c r="BU25" s="5"/>
-      <c r="BV25" s="5"/>
-      <c r="BW25" s="5"/>
-      <c r="BX25" s="5"/>
-      <c r="BY25" s="5"/>
-      <c r="BZ25" s="5"/>
-      <c r="CA25" s="5"/>
-      <c r="CB25" s="5"/>
-      <c r="CC25" s="5"/>
-      <c r="CD25" s="5"/>
-      <c r="CE25" s="5"/>
-      <c r="CF25" s="5"/>
-      <c r="CG25" s="5"/>
-      <c r="CH25" s="5"/>
-      <c r="CI25" s="5"/>
-      <c r="CJ25" s="5"/>
-      <c r="CK25" s="5"/>
-      <c r="CL25" s="5"/>
-      <c r="CM25" s="5"/>
-      <c r="CN25" s="5"/>
-      <c r="CO25" s="5"/>
-      <c r="CP25" s="5"/>
-      <c r="CQ25" s="5"/>
-      <c r="CR25" s="5"/>
-      <c r="CS25" s="5"/>
-      <c r="CT25" s="5"/>
-      <c r="CU25" s="5"/>
-      <c r="CV25" s="5"/>
-      <c r="CW25" s="5"/>
-      <c r="CX25" s="5"/>
-      <c r="CY25" s="5"/>
-      <c r="CZ25" s="5"/>
-      <c r="DA25" s="5"/>
-      <c r="DB25" s="5"/>
-      <c r="DC25" s="5"/>
-      <c r="DD25" s="5"/>
-      <c r="DE25" s="5"/>
-      <c r="DF25" s="5"/>
-      <c r="DG25" s="5"/>
-      <c r="DH25" s="5"/>
-      <c r="DI25" s="5"/>
-      <c r="DJ25" s="5"/>
-      <c r="DK25" s="5"/>
-      <c r="DL25" s="5"/>
-      <c r="DM25" s="5"/>
-      <c r="DN25" s="5"/>
-      <c r="DO25" s="5"/>
-      <c r="DP25" s="5"/>
-      <c r="DQ25" s="5"/>
-      <c r="DR25" s="5"/>
-      <c r="DS25" s="5"/>
-    </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="4"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="4"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="4"/>
+      <c r="BG25" s="4"/>
+      <c r="BH25" s="4"/>
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+      <c r="BM25" s="4"/>
+      <c r="BN25" s="4"/>
+      <c r="BO25" s="4"/>
+      <c r="BP25" s="4"/>
+      <c r="BQ25" s="4"/>
+      <c r="BR25" s="4"/>
+      <c r="BS25" s="4"/>
+      <c r="BT25" s="4"/>
+      <c r="BU25" s="4"/>
+      <c r="BV25" s="4"/>
+      <c r="BW25" s="4"/>
+      <c r="BX25" s="4"/>
+      <c r="BY25" s="4"/>
+      <c r="BZ25" s="4"/>
+      <c r="CA25" s="4"/>
+      <c r="CB25" s="4"/>
+      <c r="CC25" s="4"/>
+      <c r="CD25" s="4"/>
+      <c r="CE25" s="4"/>
+      <c r="CF25" s="4"/>
+      <c r="CG25" s="4"/>
+      <c r="CH25" s="4"/>
+      <c r="CI25" s="4"/>
+      <c r="CJ25" s="4"/>
+      <c r="CK25" s="4"/>
+      <c r="CL25" s="4"/>
+      <c r="CM25" s="4"/>
+      <c r="CN25" s="4"/>
+      <c r="CO25" s="4"/>
+      <c r="CP25" s="4"/>
+      <c r="CQ25" s="4"/>
+      <c r="CR25" s="4"/>
+      <c r="CS25" s="4"/>
+      <c r="CT25" s="4"/>
+      <c r="CU25" s="4"/>
+      <c r="CV25" s="4"/>
+      <c r="CW25" s="4"/>
+      <c r="CX25" s="4"/>
+      <c r="CY25" s="4"/>
+      <c r="CZ25" s="4"/>
+      <c r="DA25" s="4"/>
+      <c r="DB25" s="4"/>
+      <c r="DC25" s="4"/>
+      <c r="DD25" s="4"/>
+      <c r="DE25" s="4"/>
+      <c r="DF25" s="4"/>
+      <c r="DG25" s="4"/>
+      <c r="DH25" s="4"/>
+      <c r="DI25" s="4"/>
+      <c r="DJ25" s="4"/>
+      <c r="DK25" s="4"/>
+      <c r="DL25" s="4"/>
+      <c r="DM25" s="4"/>
+      <c r="DN25" s="4"/>
+      <c r="DO25" s="4"/>
+      <c r="DP25" s="4"/>
+      <c r="DQ25" s="4"/>
+      <c r="DR25" s="4"/>
+      <c r="DS25" s="4"/>
+    </row>
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6574,80 +6573,80 @@
         <v>34</v>
       </c>
       <c r="AW26" s="2"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="5"/>
-      <c r="BB26" s="5"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="5"/>
-      <c r="BE26" s="5"/>
-      <c r="BF26" s="5"/>
-      <c r="BG26" s="5"/>
-      <c r="BH26" s="5"/>
-      <c r="BI26" s="5"/>
-      <c r="BJ26" s="5"/>
-      <c r="BK26" s="5"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="5"/>
-      <c r="BN26" s="5"/>
-      <c r="BO26" s="5"/>
-      <c r="BP26" s="5"/>
-      <c r="BQ26" s="5"/>
-      <c r="BR26" s="5"/>
-      <c r="BS26" s="5"/>
-      <c r="BT26" s="5"/>
-      <c r="BU26" s="5"/>
-      <c r="BV26" s="5"/>
-      <c r="BW26" s="5"/>
-      <c r="BX26" s="5"/>
-      <c r="BY26" s="5"/>
-      <c r="BZ26" s="5"/>
-      <c r="CA26" s="5"/>
-      <c r="CB26" s="5"/>
-      <c r="CC26" s="5"/>
-      <c r="CD26" s="5"/>
-      <c r="CE26" s="5"/>
-      <c r="CF26" s="5"/>
-      <c r="CG26" s="5"/>
-      <c r="CH26" s="5"/>
-      <c r="CI26" s="5"/>
-      <c r="CJ26" s="5"/>
-      <c r="CK26" s="5"/>
-      <c r="CL26" s="5"/>
-      <c r="CM26" s="5"/>
-      <c r="CN26" s="5"/>
-      <c r="CO26" s="5"/>
-      <c r="CP26" s="5"/>
-      <c r="CQ26" s="5"/>
-      <c r="CR26" s="5"/>
-      <c r="CS26" s="5"/>
-      <c r="CT26" s="5"/>
-      <c r="CU26" s="5"/>
-      <c r="CV26" s="5"/>
-      <c r="CW26" s="5"/>
-      <c r="CX26" s="5"/>
-      <c r="CY26" s="5"/>
-      <c r="CZ26" s="5"/>
-      <c r="DA26" s="5"/>
-      <c r="DB26" s="5"/>
-      <c r="DC26" s="5"/>
-      <c r="DD26" s="5"/>
-      <c r="DE26" s="5"/>
-      <c r="DF26" s="5"/>
-      <c r="DG26" s="5"/>
-      <c r="DH26" s="5"/>
-      <c r="DI26" s="5"/>
-      <c r="DJ26" s="5"/>
-      <c r="DK26" s="5"/>
-      <c r="DL26" s="5"/>
-      <c r="DM26" s="5"/>
-      <c r="DN26" s="5"/>
-      <c r="DO26" s="5"/>
-      <c r="DP26" s="5"/>
-      <c r="DQ26" s="5"/>
-      <c r="DR26" s="5"/>
-      <c r="DS26" s="5"/>
-    </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="4"/>
+      <c r="BB26" s="4"/>
+      <c r="BC26" s="4"/>
+      <c r="BD26" s="4"/>
+      <c r="BE26" s="4"/>
+      <c r="BF26" s="4"/>
+      <c r="BG26" s="4"/>
+      <c r="BH26" s="4"/>
+      <c r="BI26" s="4"/>
+      <c r="BJ26" s="4"/>
+      <c r="BK26" s="4"/>
+      <c r="BL26" s="4"/>
+      <c r="BM26" s="4"/>
+      <c r="BN26" s="4"/>
+      <c r="BO26" s="4"/>
+      <c r="BP26" s="4"/>
+      <c r="BQ26" s="4"/>
+      <c r="BR26" s="4"/>
+      <c r="BS26" s="4"/>
+      <c r="BT26" s="4"/>
+      <c r="BU26" s="4"/>
+      <c r="BV26" s="4"/>
+      <c r="BW26" s="4"/>
+      <c r="BX26" s="4"/>
+      <c r="BY26" s="4"/>
+      <c r="BZ26" s="4"/>
+      <c r="CA26" s="4"/>
+      <c r="CB26" s="4"/>
+      <c r="CC26" s="4"/>
+      <c r="CD26" s="4"/>
+      <c r="CE26" s="4"/>
+      <c r="CF26" s="4"/>
+      <c r="CG26" s="4"/>
+      <c r="CH26" s="4"/>
+      <c r="CI26" s="4"/>
+      <c r="CJ26" s="4"/>
+      <c r="CK26" s="4"/>
+      <c r="CL26" s="4"/>
+      <c r="CM26" s="4"/>
+      <c r="CN26" s="4"/>
+      <c r="CO26" s="4"/>
+      <c r="CP26" s="4"/>
+      <c r="CQ26" s="4"/>
+      <c r="CR26" s="4"/>
+      <c r="CS26" s="4"/>
+      <c r="CT26" s="4"/>
+      <c r="CU26" s="4"/>
+      <c r="CV26" s="4"/>
+      <c r="CW26" s="4"/>
+      <c r="CX26" s="4"/>
+      <c r="CY26" s="4"/>
+      <c r="CZ26" s="4"/>
+      <c r="DA26" s="4"/>
+      <c r="DB26" s="4"/>
+      <c r="DC26" s="4"/>
+      <c r="DD26" s="4"/>
+      <c r="DE26" s="4"/>
+      <c r="DF26" s="4"/>
+      <c r="DG26" s="4"/>
+      <c r="DH26" s="4"/>
+      <c r="DI26" s="4"/>
+      <c r="DJ26" s="4"/>
+      <c r="DK26" s="4"/>
+      <c r="DL26" s="4"/>
+      <c r="DM26" s="4"/>
+      <c r="DN26" s="4"/>
+      <c r="DO26" s="4"/>
+      <c r="DP26" s="4"/>
+      <c r="DQ26" s="4"/>
+      <c r="DR26" s="4"/>
+      <c r="DS26" s="4"/>
+    </row>
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -6792,80 +6791,80 @@
         <v>34</v>
       </c>
       <c r="AW27" s="2"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="5"/>
-      <c r="BB27" s="5"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="5"/>
-      <c r="BE27" s="5"/>
-      <c r="BF27" s="5"/>
-      <c r="BG27" s="5"/>
-      <c r="BH27" s="5"/>
-      <c r="BI27" s="5"/>
-      <c r="BJ27" s="5"/>
-      <c r="BK27" s="5"/>
-      <c r="BL27" s="5"/>
-      <c r="BM27" s="5"/>
-      <c r="BN27" s="5"/>
-      <c r="BO27" s="5"/>
-      <c r="BP27" s="5"/>
-      <c r="BQ27" s="5"/>
-      <c r="BR27" s="5"/>
-      <c r="BS27" s="5"/>
-      <c r="BT27" s="5"/>
-      <c r="BU27" s="5"/>
-      <c r="BV27" s="5"/>
-      <c r="BW27" s="5"/>
-      <c r="BX27" s="5"/>
-      <c r="BY27" s="5"/>
-      <c r="BZ27" s="5"/>
-      <c r="CA27" s="5"/>
-      <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
-      <c r="CD27" s="5"/>
-      <c r="CE27" s="5"/>
-      <c r="CF27" s="5"/>
-      <c r="CG27" s="5"/>
-      <c r="CH27" s="5"/>
-      <c r="CI27" s="5"/>
-      <c r="CJ27" s="5"/>
-      <c r="CK27" s="5"/>
-      <c r="CL27" s="5"/>
-      <c r="CM27" s="5"/>
-      <c r="CN27" s="5"/>
-      <c r="CO27" s="5"/>
-      <c r="CP27" s="5"/>
-      <c r="CQ27" s="5"/>
-      <c r="CR27" s="5"/>
-      <c r="CS27" s="5"/>
-      <c r="CT27" s="5"/>
-      <c r="CU27" s="5"/>
-      <c r="CV27" s="5"/>
-      <c r="CW27" s="5"/>
-      <c r="CX27" s="5"/>
-      <c r="CY27" s="5"/>
-      <c r="CZ27" s="5"/>
-      <c r="DA27" s="5"/>
-      <c r="DB27" s="5"/>
-      <c r="DC27" s="5"/>
-      <c r="DD27" s="5"/>
-      <c r="DE27" s="5"/>
-      <c r="DF27" s="5"/>
-      <c r="DG27" s="5"/>
-      <c r="DH27" s="5"/>
-      <c r="DI27" s="5"/>
-      <c r="DJ27" s="5"/>
-      <c r="DK27" s="5"/>
-      <c r="DL27" s="5"/>
-      <c r="DM27" s="5"/>
-      <c r="DN27" s="5"/>
-      <c r="DO27" s="5"/>
-      <c r="DP27" s="5"/>
-      <c r="DQ27" s="5"/>
-      <c r="DR27" s="5"/>
-      <c r="DS27" s="5"/>
-    </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="4"/>
+      <c r="BB27" s="4"/>
+      <c r="BC27" s="4"/>
+      <c r="BD27" s="4"/>
+      <c r="BE27" s="4"/>
+      <c r="BF27" s="4"/>
+      <c r="BG27" s="4"/>
+      <c r="BH27" s="4"/>
+      <c r="BI27" s="4"/>
+      <c r="BJ27" s="4"/>
+      <c r="BK27" s="4"/>
+      <c r="BL27" s="4"/>
+      <c r="BM27" s="4"/>
+      <c r="BN27" s="4"/>
+      <c r="BO27" s="4"/>
+      <c r="BP27" s="4"/>
+      <c r="BQ27" s="4"/>
+      <c r="BR27" s="4"/>
+      <c r="BS27" s="4"/>
+      <c r="BT27" s="4"/>
+      <c r="BU27" s="4"/>
+      <c r="BV27" s="4"/>
+      <c r="BW27" s="4"/>
+      <c r="BX27" s="4"/>
+      <c r="BY27" s="4"/>
+      <c r="BZ27" s="4"/>
+      <c r="CA27" s="4"/>
+      <c r="CB27" s="4"/>
+      <c r="CC27" s="4"/>
+      <c r="CD27" s="4"/>
+      <c r="CE27" s="4"/>
+      <c r="CF27" s="4"/>
+      <c r="CG27" s="4"/>
+      <c r="CH27" s="4"/>
+      <c r="CI27" s="4"/>
+      <c r="CJ27" s="4"/>
+      <c r="CK27" s="4"/>
+      <c r="CL27" s="4"/>
+      <c r="CM27" s="4"/>
+      <c r="CN27" s="4"/>
+      <c r="CO27" s="4"/>
+      <c r="CP27" s="4"/>
+      <c r="CQ27" s="4"/>
+      <c r="CR27" s="4"/>
+      <c r="CS27" s="4"/>
+      <c r="CT27" s="4"/>
+      <c r="CU27" s="4"/>
+      <c r="CV27" s="4"/>
+      <c r="CW27" s="4"/>
+      <c r="CX27" s="4"/>
+      <c r="CY27" s="4"/>
+      <c r="CZ27" s="4"/>
+      <c r="DA27" s="4"/>
+      <c r="DB27" s="4"/>
+      <c r="DC27" s="4"/>
+      <c r="DD27" s="4"/>
+      <c r="DE27" s="4"/>
+      <c r="DF27" s="4"/>
+      <c r="DG27" s="4"/>
+      <c r="DH27" s="4"/>
+      <c r="DI27" s="4"/>
+      <c r="DJ27" s="4"/>
+      <c r="DK27" s="4"/>
+      <c r="DL27" s="4"/>
+      <c r="DM27" s="4"/>
+      <c r="DN27" s="4"/>
+      <c r="DO27" s="4"/>
+      <c r="DP27" s="4"/>
+      <c r="DQ27" s="4"/>
+      <c r="DR27" s="4"/>
+      <c r="DS27" s="4"/>
+    </row>
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7010,80 +7009,80 @@
         <v>34</v>
       </c>
       <c r="AW28" s="2"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="5"/>
-      <c r="BB28" s="5"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="5"/>
-      <c r="BE28" s="5"/>
-      <c r="BF28" s="5"/>
-      <c r="BG28" s="5"/>
-      <c r="BH28" s="5"/>
-      <c r="BI28" s="5"/>
-      <c r="BJ28" s="5"/>
-      <c r="BK28" s="5"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="5"/>
-      <c r="BN28" s="5"/>
-      <c r="BO28" s="5"/>
-      <c r="BP28" s="5"/>
-      <c r="BQ28" s="5"/>
-      <c r="BR28" s="5"/>
-      <c r="BS28" s="5"/>
-      <c r="BT28" s="5"/>
-      <c r="BU28" s="5"/>
-      <c r="BV28" s="5"/>
-      <c r="BW28" s="5"/>
-      <c r="BX28" s="5"/>
-      <c r="BY28" s="5"/>
-      <c r="BZ28" s="5"/>
-      <c r="CA28" s="5"/>
-      <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
-      <c r="CD28" s="5"/>
-      <c r="CE28" s="5"/>
-      <c r="CF28" s="5"/>
-      <c r="CG28" s="5"/>
-      <c r="CH28" s="5"/>
-      <c r="CI28" s="5"/>
-      <c r="CJ28" s="5"/>
-      <c r="CK28" s="5"/>
-      <c r="CL28" s="5"/>
-      <c r="CM28" s="5"/>
-      <c r="CN28" s="5"/>
-      <c r="CO28" s="5"/>
-      <c r="CP28" s="5"/>
-      <c r="CQ28" s="5"/>
-      <c r="CR28" s="5"/>
-      <c r="CS28" s="5"/>
-      <c r="CT28" s="5"/>
-      <c r="CU28" s="5"/>
-      <c r="CV28" s="5"/>
-      <c r="CW28" s="5"/>
-      <c r="CX28" s="5"/>
-      <c r="CY28" s="5"/>
-      <c r="CZ28" s="5"/>
-      <c r="DA28" s="5"/>
-      <c r="DB28" s="5"/>
-      <c r="DC28" s="5"/>
-      <c r="DD28" s="5"/>
-      <c r="DE28" s="5"/>
-      <c r="DF28" s="5"/>
-      <c r="DG28" s="5"/>
-      <c r="DH28" s="5"/>
-      <c r="DI28" s="5"/>
-      <c r="DJ28" s="5"/>
-      <c r="DK28" s="5"/>
-      <c r="DL28" s="5"/>
-      <c r="DM28" s="5"/>
-      <c r="DN28" s="5"/>
-      <c r="DO28" s="5"/>
-      <c r="DP28" s="5"/>
-      <c r="DQ28" s="5"/>
-      <c r="DR28" s="5"/>
-      <c r="DS28" s="5"/>
-    </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="4"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="4"/>
+      <c r="BD28" s="4"/>
+      <c r="BE28" s="4"/>
+      <c r="BF28" s="4"/>
+      <c r="BG28" s="4"/>
+      <c r="BH28" s="4"/>
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+      <c r="BM28" s="4"/>
+      <c r="BN28" s="4"/>
+      <c r="BO28" s="4"/>
+      <c r="BP28" s="4"/>
+      <c r="BQ28" s="4"/>
+      <c r="BR28" s="4"/>
+      <c r="BS28" s="4"/>
+      <c r="BT28" s="4"/>
+      <c r="BU28" s="4"/>
+      <c r="BV28" s="4"/>
+      <c r="BW28" s="4"/>
+      <c r="BX28" s="4"/>
+      <c r="BY28" s="4"/>
+      <c r="BZ28" s="4"/>
+      <c r="CA28" s="4"/>
+      <c r="CB28" s="4"/>
+      <c r="CC28" s="4"/>
+      <c r="CD28" s="4"/>
+      <c r="CE28" s="4"/>
+      <c r="CF28" s="4"/>
+      <c r="CG28" s="4"/>
+      <c r="CH28" s="4"/>
+      <c r="CI28" s="4"/>
+      <c r="CJ28" s="4"/>
+      <c r="CK28" s="4"/>
+      <c r="CL28" s="4"/>
+      <c r="CM28" s="4"/>
+      <c r="CN28" s="4"/>
+      <c r="CO28" s="4"/>
+      <c r="CP28" s="4"/>
+      <c r="CQ28" s="4"/>
+      <c r="CR28" s="4"/>
+      <c r="CS28" s="4"/>
+      <c r="CT28" s="4"/>
+      <c r="CU28" s="4"/>
+      <c r="CV28" s="4"/>
+      <c r="CW28" s="4"/>
+      <c r="CX28" s="4"/>
+      <c r="CY28" s="4"/>
+      <c r="CZ28" s="4"/>
+      <c r="DA28" s="4"/>
+      <c r="DB28" s="4"/>
+      <c r="DC28" s="4"/>
+      <c r="DD28" s="4"/>
+      <c r="DE28" s="4"/>
+      <c r="DF28" s="4"/>
+      <c r="DG28" s="4"/>
+      <c r="DH28" s="4"/>
+      <c r="DI28" s="4"/>
+      <c r="DJ28" s="4"/>
+      <c r="DK28" s="4"/>
+      <c r="DL28" s="4"/>
+      <c r="DM28" s="4"/>
+      <c r="DN28" s="4"/>
+      <c r="DO28" s="4"/>
+      <c r="DP28" s="4"/>
+      <c r="DQ28" s="4"/>
+      <c r="DR28" s="4"/>
+      <c r="DS28" s="4"/>
+    </row>
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7228,80 +7227,80 @@
         <v>34</v>
       </c>
       <c r="AW29" s="2"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="5"/>
-      <c r="BE29" s="5"/>
-      <c r="BF29" s="5"/>
-      <c r="BG29" s="5"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="5"/>
-      <c r="BJ29" s="5"/>
-      <c r="BK29" s="5"/>
-      <c r="BL29" s="5"/>
-      <c r="BM29" s="5"/>
-      <c r="BN29" s="5"/>
-      <c r="BO29" s="5"/>
-      <c r="BP29" s="5"/>
-      <c r="BQ29" s="5"/>
-      <c r="BR29" s="5"/>
-      <c r="BS29" s="5"/>
-      <c r="BT29" s="5"/>
-      <c r="BU29" s="5"/>
-      <c r="BV29" s="5"/>
-      <c r="BW29" s="5"/>
-      <c r="BX29" s="5"/>
-      <c r="BY29" s="5"/>
-      <c r="BZ29" s="5"/>
-      <c r="CA29" s="5"/>
-      <c r="CB29" s="5"/>
-      <c r="CC29" s="5"/>
-      <c r="CD29" s="5"/>
-      <c r="CE29" s="5"/>
-      <c r="CF29" s="5"/>
-      <c r="CG29" s="5"/>
-      <c r="CH29" s="5"/>
-      <c r="CI29" s="5"/>
-      <c r="CJ29" s="5"/>
-      <c r="CK29" s="5"/>
-      <c r="CL29" s="5"/>
-      <c r="CM29" s="5"/>
-      <c r="CN29" s="5"/>
-      <c r="CO29" s="5"/>
-      <c r="CP29" s="5"/>
-      <c r="CQ29" s="5"/>
-      <c r="CR29" s="5"/>
-      <c r="CS29" s="5"/>
-      <c r="CT29" s="5"/>
-      <c r="CU29" s="5"/>
-      <c r="CV29" s="5"/>
-      <c r="CW29" s="5"/>
-      <c r="CX29" s="5"/>
-      <c r="CY29" s="5"/>
-      <c r="CZ29" s="5"/>
-      <c r="DA29" s="5"/>
-      <c r="DB29" s="5"/>
-      <c r="DC29" s="5"/>
-      <c r="DD29" s="5"/>
-      <c r="DE29" s="5"/>
-      <c r="DF29" s="5"/>
-      <c r="DG29" s="5"/>
-      <c r="DH29" s="5"/>
-      <c r="DI29" s="5"/>
-      <c r="DJ29" s="5"/>
-      <c r="DK29" s="5"/>
-      <c r="DL29" s="5"/>
-      <c r="DM29" s="5"/>
-      <c r="DN29" s="5"/>
-      <c r="DO29" s="5"/>
-      <c r="DP29" s="5"/>
-      <c r="DQ29" s="5"/>
-      <c r="DR29" s="5"/>
-      <c r="DS29" s="5"/>
-    </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="4"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="4"/>
+      <c r="BD29" s="4"/>
+      <c r="BE29" s="4"/>
+      <c r="BF29" s="4"/>
+      <c r="BG29" s="4"/>
+      <c r="BH29" s="4"/>
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+      <c r="BM29" s="4"/>
+      <c r="BN29" s="4"/>
+      <c r="BO29" s="4"/>
+      <c r="BP29" s="4"/>
+      <c r="BQ29" s="4"/>
+      <c r="BR29" s="4"/>
+      <c r="BS29" s="4"/>
+      <c r="BT29" s="4"/>
+      <c r="BU29" s="4"/>
+      <c r="BV29" s="4"/>
+      <c r="BW29" s="4"/>
+      <c r="BX29" s="4"/>
+      <c r="BY29" s="4"/>
+      <c r="BZ29" s="4"/>
+      <c r="CA29" s="4"/>
+      <c r="CB29" s="4"/>
+      <c r="CC29" s="4"/>
+      <c r="CD29" s="4"/>
+      <c r="CE29" s="4"/>
+      <c r="CF29" s="4"/>
+      <c r="CG29" s="4"/>
+      <c r="CH29" s="4"/>
+      <c r="CI29" s="4"/>
+      <c r="CJ29" s="4"/>
+      <c r="CK29" s="4"/>
+      <c r="CL29" s="4"/>
+      <c r="CM29" s="4"/>
+      <c r="CN29" s="4"/>
+      <c r="CO29" s="4"/>
+      <c r="CP29" s="4"/>
+      <c r="CQ29" s="4"/>
+      <c r="CR29" s="4"/>
+      <c r="CS29" s="4"/>
+      <c r="CT29" s="4"/>
+      <c r="CU29" s="4"/>
+      <c r="CV29" s="4"/>
+      <c r="CW29" s="4"/>
+      <c r="CX29" s="4"/>
+      <c r="CY29" s="4"/>
+      <c r="CZ29" s="4"/>
+      <c r="DA29" s="4"/>
+      <c r="DB29" s="4"/>
+      <c r="DC29" s="4"/>
+      <c r="DD29" s="4"/>
+      <c r="DE29" s="4"/>
+      <c r="DF29" s="4"/>
+      <c r="DG29" s="4"/>
+      <c r="DH29" s="4"/>
+      <c r="DI29" s="4"/>
+      <c r="DJ29" s="4"/>
+      <c r="DK29" s="4"/>
+      <c r="DL29" s="4"/>
+      <c r="DM29" s="4"/>
+      <c r="DN29" s="4"/>
+      <c r="DO29" s="4"/>
+      <c r="DP29" s="4"/>
+      <c r="DQ29" s="4"/>
+      <c r="DR29" s="4"/>
+      <c r="DS29" s="4"/>
+    </row>
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7446,80 +7445,80 @@
         <v>34</v>
       </c>
       <c r="AW30" s="2"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="5"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="5"/>
-      <c r="BE30" s="5"/>
-      <c r="BF30" s="5"/>
-      <c r="BG30" s="5"/>
-      <c r="BH30" s="5"/>
-      <c r="BI30" s="5"/>
-      <c r="BJ30" s="5"/>
-      <c r="BK30" s="5"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="5"/>
-      <c r="BN30" s="5"/>
-      <c r="BO30" s="5"/>
-      <c r="BP30" s="5"/>
-      <c r="BQ30" s="5"/>
-      <c r="BR30" s="5"/>
-      <c r="BS30" s="5"/>
-      <c r="BT30" s="5"/>
-      <c r="BU30" s="5"/>
-      <c r="BV30" s="5"/>
-      <c r="BW30" s="5"/>
-      <c r="BX30" s="5"/>
-      <c r="BY30" s="5"/>
-      <c r="BZ30" s="5"/>
-      <c r="CA30" s="5"/>
-      <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
-      <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CG30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
-      <c r="CJ30" s="5"/>
-      <c r="CK30" s="5"/>
-      <c r="CL30" s="5"/>
-      <c r="CM30" s="5"/>
-      <c r="CN30" s="5"/>
-      <c r="CO30" s="5"/>
-      <c r="CP30" s="5"/>
-      <c r="CQ30" s="5"/>
-      <c r="CR30" s="5"/>
-      <c r="CS30" s="5"/>
-      <c r="CT30" s="5"/>
-      <c r="CU30" s="5"/>
-      <c r="CV30" s="5"/>
-      <c r="CW30" s="5"/>
-      <c r="CX30" s="5"/>
-      <c r="CY30" s="5"/>
-      <c r="CZ30" s="5"/>
-      <c r="DA30" s="5"/>
-      <c r="DB30" s="5"/>
-      <c r="DC30" s="5"/>
-      <c r="DD30" s="5"/>
-      <c r="DE30" s="5"/>
-      <c r="DF30" s="5"/>
-      <c r="DG30" s="5"/>
-      <c r="DH30" s="5"/>
-      <c r="DI30" s="5"/>
-      <c r="DJ30" s="5"/>
-      <c r="DK30" s="5"/>
-      <c r="DL30" s="5"/>
-      <c r="DM30" s="5"/>
-      <c r="DN30" s="5"/>
-      <c r="DO30" s="5"/>
-      <c r="DP30" s="5"/>
-      <c r="DQ30" s="5"/>
-      <c r="DR30" s="5"/>
-      <c r="DS30" s="5"/>
-    </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="4"/>
+      <c r="BB30" s="4"/>
+      <c r="BC30" s="4"/>
+      <c r="BD30" s="4"/>
+      <c r="BE30" s="4"/>
+      <c r="BF30" s="4"/>
+      <c r="BG30" s="4"/>
+      <c r="BH30" s="4"/>
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+      <c r="BM30" s="4"/>
+      <c r="BN30" s="4"/>
+      <c r="BO30" s="4"/>
+      <c r="BP30" s="4"/>
+      <c r="BQ30" s="4"/>
+      <c r="BR30" s="4"/>
+      <c r="BS30" s="4"/>
+      <c r="BT30" s="4"/>
+      <c r="BU30" s="4"/>
+      <c r="BV30" s="4"/>
+      <c r="BW30" s="4"/>
+      <c r="BX30" s="4"/>
+      <c r="BY30" s="4"/>
+      <c r="BZ30" s="4"/>
+      <c r="CA30" s="4"/>
+      <c r="CB30" s="4"/>
+      <c r="CC30" s="4"/>
+      <c r="CD30" s="4"/>
+      <c r="CE30" s="4"/>
+      <c r="CF30" s="4"/>
+      <c r="CG30" s="4"/>
+      <c r="CH30" s="4"/>
+      <c r="CI30" s="4"/>
+      <c r="CJ30" s="4"/>
+      <c r="CK30" s="4"/>
+      <c r="CL30" s="4"/>
+      <c r="CM30" s="4"/>
+      <c r="CN30" s="4"/>
+      <c r="CO30" s="4"/>
+      <c r="CP30" s="4"/>
+      <c r="CQ30" s="4"/>
+      <c r="CR30" s="4"/>
+      <c r="CS30" s="4"/>
+      <c r="CT30" s="4"/>
+      <c r="CU30" s="4"/>
+      <c r="CV30" s="4"/>
+      <c r="CW30" s="4"/>
+      <c r="CX30" s="4"/>
+      <c r="CY30" s="4"/>
+      <c r="CZ30" s="4"/>
+      <c r="DA30" s="4"/>
+      <c r="DB30" s="4"/>
+      <c r="DC30" s="4"/>
+      <c r="DD30" s="4"/>
+      <c r="DE30" s="4"/>
+      <c r="DF30" s="4"/>
+      <c r="DG30" s="4"/>
+      <c r="DH30" s="4"/>
+      <c r="DI30" s="4"/>
+      <c r="DJ30" s="4"/>
+      <c r="DK30" s="4"/>
+      <c r="DL30" s="4"/>
+      <c r="DM30" s="4"/>
+      <c r="DN30" s="4"/>
+      <c r="DO30" s="4"/>
+      <c r="DP30" s="4"/>
+      <c r="DQ30" s="4"/>
+      <c r="DR30" s="4"/>
+      <c r="DS30" s="4"/>
+    </row>
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -7664,85 +7663,85 @@
         <v>34</v>
       </c>
       <c r="AW31" s="2"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="5"/>
-      <c r="BB31" s="5"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="5"/>
-      <c r="BE31" s="5"/>
-      <c r="BF31" s="5"/>
-      <c r="BG31" s="5"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="5"/>
-      <c r="BJ31" s="5"/>
-      <c r="BK31" s="5"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="5"/>
-      <c r="BN31" s="5"/>
-      <c r="BO31" s="5"/>
-      <c r="BP31" s="5"/>
-      <c r="BQ31" s="5"/>
-      <c r="BR31" s="5"/>
-      <c r="BS31" s="5"/>
-      <c r="BT31" s="5"/>
-      <c r="BU31" s="5"/>
-      <c r="BV31" s="5"/>
-      <c r="BW31" s="5"/>
-      <c r="BX31" s="5"/>
-      <c r="BY31" s="5"/>
-      <c r="BZ31" s="5"/>
-      <c r="CA31" s="5"/>
-      <c r="CB31" s="5"/>
-      <c r="CC31" s="5"/>
-      <c r="CD31" s="5"/>
-      <c r="CE31" s="5"/>
-      <c r="CF31" s="5"/>
-      <c r="CG31" s="5"/>
-      <c r="CH31" s="5"/>
-      <c r="CI31" s="5"/>
-      <c r="CJ31" s="5"/>
-      <c r="CK31" s="5"/>
-      <c r="CL31" s="5"/>
-      <c r="CM31" s="5"/>
-      <c r="CN31" s="5"/>
-      <c r="CO31" s="5"/>
-      <c r="CP31" s="5"/>
-      <c r="CQ31" s="5"/>
-      <c r="CR31" s="5"/>
-      <c r="CS31" s="5"/>
-      <c r="CT31" s="5"/>
-      <c r="CU31" s="5"/>
-      <c r="CV31" s="5"/>
-      <c r="CW31" s="5"/>
-      <c r="CX31" s="5"/>
-      <c r="CY31" s="5"/>
-      <c r="CZ31" s="5"/>
-      <c r="DA31" s="5"/>
-      <c r="DB31" s="5"/>
-      <c r="DC31" s="5"/>
-      <c r="DD31" s="5"/>
-      <c r="DE31" s="5"/>
-      <c r="DF31" s="5"/>
-      <c r="DG31" s="5"/>
-      <c r="DH31" s="5"/>
-      <c r="DI31" s="5"/>
-      <c r="DJ31" s="5"/>
-      <c r="DK31" s="5"/>
-      <c r="DL31" s="5"/>
-      <c r="DM31" s="5"/>
-      <c r="DN31" s="5"/>
-      <c r="DO31" s="5"/>
-      <c r="DP31" s="5"/>
-      <c r="DQ31" s="5"/>
-      <c r="DR31" s="5"/>
-      <c r="DS31" s="5"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="4"/>
+      <c r="BB31" s="4"/>
+      <c r="BC31" s="4"/>
+      <c r="BD31" s="4"/>
+      <c r="BE31" s="4"/>
+      <c r="BF31" s="4"/>
+      <c r="BG31" s="4"/>
+      <c r="BH31" s="4"/>
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+      <c r="BM31" s="4"/>
+      <c r="BN31" s="4"/>
+      <c r="BO31" s="4"/>
+      <c r="BP31" s="4"/>
+      <c r="BQ31" s="4"/>
+      <c r="BR31" s="4"/>
+      <c r="BS31" s="4"/>
+      <c r="BT31" s="4"/>
+      <c r="BU31" s="4"/>
+      <c r="BV31" s="4"/>
+      <c r="BW31" s="4"/>
+      <c r="BX31" s="4"/>
+      <c r="BY31" s="4"/>
+      <c r="BZ31" s="4"/>
+      <c r="CA31" s="4"/>
+      <c r="CB31" s="4"/>
+      <c r="CC31" s="4"/>
+      <c r="CD31" s="4"/>
+      <c r="CE31" s="4"/>
+      <c r="CF31" s="4"/>
+      <c r="CG31" s="4"/>
+      <c r="CH31" s="4"/>
+      <c r="CI31" s="4"/>
+      <c r="CJ31" s="4"/>
+      <c r="CK31" s="4"/>
+      <c r="CL31" s="4"/>
+      <c r="CM31" s="4"/>
+      <c r="CN31" s="4"/>
+      <c r="CO31" s="4"/>
+      <c r="CP31" s="4"/>
+      <c r="CQ31" s="4"/>
+      <c r="CR31" s="4"/>
+      <c r="CS31" s="4"/>
+      <c r="CT31" s="4"/>
+      <c r="CU31" s="4"/>
+      <c r="CV31" s="4"/>
+      <c r="CW31" s="4"/>
+      <c r="CX31" s="4"/>
+      <c r="CY31" s="4"/>
+      <c r="CZ31" s="4"/>
+      <c r="DA31" s="4"/>
+      <c r="DB31" s="4"/>
+      <c r="DC31" s="4"/>
+      <c r="DD31" s="4"/>
+      <c r="DE31" s="4"/>
+      <c r="DF31" s="4"/>
+      <c r="DG31" s="4"/>
+      <c r="DH31" s="4"/>
+      <c r="DI31" s="4"/>
+      <c r="DJ31" s="4"/>
+      <c r="DK31" s="4"/>
+      <c r="DL31" s="4"/>
+      <c r="DM31" s="4"/>
+      <c r="DN31" s="4"/>
+      <c r="DO31" s="4"/>
+      <c r="DP31" s="4"/>
+      <c r="DQ31" s="4"/>
+      <c r="DR31" s="4"/>
+      <c r="DS31" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B31">
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AS3:AZ3 AW4:AZ10 AW23:BJ31 AW11:BA22 AS4:AV31">
+  <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AW4:AZ10 BE4:BJ10 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 AW11:BA22 BC11:BJ22 AW23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7755,14 +7754,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7770,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -7778,7 +7777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -7786,7 +7785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -7794,7 +7793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -7802,7 +7801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -7810,7 +7809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -7818,7 +7817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -7826,7 +7825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -7834,7 +7833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -7842,7 +7841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -7850,7 +7849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -7858,7 +7857,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -7866,7 +7865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -7874,7 +7873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -7882,7 +7881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -7890,7 +7889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -7906,7 +7905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -7914,7 +7913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -7922,7 +7921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -7930,7 +7929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -7938,7 +7937,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -7946,7 +7945,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -7954,7 +7953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -7962,7 +7961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -7970,7 +7969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -7978,7 +7977,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -7986,7 +7985,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -7994,7 +7993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8011,18 +8010,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8030,7 +8029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8039,7 +8038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8048,7 +8047,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8057,7 +8056,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8066,13 +8065,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8081,7 +8080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8090,7 +8089,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8106,13 +8105,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8121,7 +8120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8130,7 +8129,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8139,7 +8138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8148,7 +8147,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8157,7 +8156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8166,7 +8165,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8175,7 +8174,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8184,7 +8183,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8193,7 +8192,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8202,7 +8201,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8211,7 +8210,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8220,7 +8219,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8229,25 +8228,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8256,7 +8255,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8265,7 +8264,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8274,7 +8273,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A11B778-169E-4259-B926-02E637A6C0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D767BA8D-5733-40B7-A3BE-6F8AE5D788A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1028,21 +1028,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.6640625" customWidth="1"/>
+    <col min="20" max="25" width="7.7109375" customWidth="1"/>
     <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="4" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="28" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="4" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1178,7 +1178,9 @@
       <c r="AV1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AW1" s="7"/>
+      <c r="AW1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="AX1" s="7"/>
       <c r="AY1" s="7"/>
       <c r="AZ1" s="7"/>
@@ -1222,7 +1224,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1367,7 +1369,9 @@
       <c r="AV2" s="1">
         <v>46239</v>
       </c>
-      <c r="AW2" s="7"/>
+      <c r="AW2" s="7">
+        <v>46241</v>
+      </c>
       <c r="AX2" s="1"/>
       <c r="AY2" s="7"/>
       <c r="AZ2" s="1"/>
@@ -1411,7 +1415,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1555,7 +1559,9 @@
       <c r="AV3" t="s">
         <v>34</v>
       </c>
-      <c r="AW3" s="2"/>
+      <c r="AW3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ3" s="4"/>
       <c r="BA3" s="4"/>
       <c r="BB3" s="4"/>
@@ -1629,7 +1635,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1773,7 +1779,9 @@
       <c r="AV4" t="s">
         <v>34</v>
       </c>
-      <c r="AW4" s="2"/>
+      <c r="AW4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
@@ -1847,7 +1855,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -1991,7 +1999,9 @@
       <c r="AV5" t="s">
         <v>34</v>
       </c>
-      <c r="AW5" s="2"/>
+      <c r="AW5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4"/>
@@ -2065,7 +2075,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2209,7 +2219,9 @@
       <c r="AV6" t="s">
         <v>34</v>
       </c>
-      <c r="AW6" s="2"/>
+      <c r="AW6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
@@ -2283,7 +2295,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2427,7 +2439,9 @@
       <c r="AV7" t="s">
         <v>34</v>
       </c>
-      <c r="AW7" s="2"/>
+      <c r="AW7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="4"/>
@@ -2501,7 +2515,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2645,7 +2659,9 @@
       <c r="AV8" t="s">
         <v>34</v>
       </c>
-      <c r="AW8" s="2"/>
+      <c r="AW8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
@@ -2719,7 +2735,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2863,7 +2879,9 @@
       <c r="AV9" t="s">
         <v>34</v>
       </c>
-      <c r="AW9" s="2"/>
+      <c r="AW9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="4"/>
@@ -2937,7 +2955,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3081,7 +3099,9 @@
       <c r="AV10" t="s">
         <v>34</v>
       </c>
-      <c r="AW10" s="2"/>
+      <c r="AW10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="4"/>
@@ -3155,7 +3175,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3299,7 +3319,9 @@
       <c r="AV11" t="s">
         <v>34</v>
       </c>
-      <c r="AW11" s="2"/>
+      <c r="AW11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4"/>
@@ -3373,7 +3395,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3520,7 +3542,9 @@
       <c r="AV12" t="s">
         <v>34</v>
       </c>
-      <c r="AW12" s="2"/>
+      <c r="AW12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
@@ -3594,7 +3618,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3738,7 +3762,9 @@
       <c r="AV13" t="s">
         <v>34</v>
       </c>
-      <c r="AW13" s="2"/>
+      <c r="AW13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
@@ -3812,7 +3838,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -3956,7 +3982,9 @@
       <c r="AV14" t="s">
         <v>35</v>
       </c>
-      <c r="AW14" s="2"/>
+      <c r="AW14" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
@@ -4030,7 +4058,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4174,7 +4202,9 @@
       <c r="AV15" t="s">
         <v>34</v>
       </c>
-      <c r="AW15" s="2"/>
+      <c r="AW15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
@@ -4248,7 +4278,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4392,7 +4422,9 @@
       <c r="AV16" t="s">
         <v>34</v>
       </c>
-      <c r="AW16" s="2"/>
+      <c r="AW16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
       <c r="BB16" s="4"/>
@@ -4466,7 +4498,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4610,7 +4642,9 @@
       <c r="AV17" t="s">
         <v>34</v>
       </c>
-      <c r="AW17" s="2"/>
+      <c r="AW17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
@@ -4684,7 +4718,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4828,7 +4862,9 @@
       <c r="AV18" t="s">
         <v>34</v>
       </c>
-      <c r="AW18" s="2"/>
+      <c r="AW18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
@@ -4902,7 +4938,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5046,7 +5082,9 @@
       <c r="AV19" t="s">
         <v>34</v>
       </c>
-      <c r="AW19" s="2"/>
+      <c r="AW19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
       <c r="BB19" s="4"/>
@@ -5120,7 +5158,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5264,7 +5302,9 @@
       <c r="AV20" t="s">
         <v>34</v>
       </c>
-      <c r="AW20" s="2"/>
+      <c r="AW20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
@@ -5338,7 +5378,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5482,7 +5522,9 @@
       <c r="AV21" t="s">
         <v>34</v>
       </c>
-      <c r="AW21" s="2"/>
+      <c r="AW21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
@@ -5556,7 +5598,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5700,7 +5742,9 @@
       <c r="AV22" t="s">
         <v>34</v>
       </c>
-      <c r="AW22" s="2"/>
+      <c r="AW22" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
@@ -5774,7 +5818,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -5918,7 +5962,9 @@
       <c r="AV23" t="s">
         <v>34</v>
       </c>
-      <c r="AW23" s="2"/>
+      <c r="AW23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
@@ -5992,7 +6038,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6136,7 +6182,9 @@
       <c r="AV24" t="s">
         <v>34</v>
       </c>
-      <c r="AW24" s="2"/>
+      <c r="AW24" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
@@ -6210,7 +6258,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6354,7 +6402,9 @@
       <c r="AV25" t="s">
         <v>34</v>
       </c>
-      <c r="AW25" s="2"/>
+      <c r="AW25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
@@ -6428,7 +6478,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6572,7 +6622,9 @@
       <c r="AV26" t="s">
         <v>34</v>
       </c>
-      <c r="AW26" s="2"/>
+      <c r="AW26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ26" s="4"/>
       <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
@@ -6646,7 +6698,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -6790,7 +6842,9 @@
       <c r="AV27" t="s">
         <v>34</v>
       </c>
-      <c r="AW27" s="2"/>
+      <c r="AW27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ27" s="4"/>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
@@ -6864,7 +6918,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7008,7 +7062,9 @@
       <c r="AV28" t="s">
         <v>34</v>
       </c>
-      <c r="AW28" s="2"/>
+      <c r="AW28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ28" s="4"/>
       <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
@@ -7082,7 +7138,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7226,7 +7282,9 @@
       <c r="AV29" t="s">
         <v>34</v>
       </c>
-      <c r="AW29" s="2"/>
+      <c r="AW29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ29" s="4"/>
       <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
@@ -7300,7 +7358,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7444,7 +7502,9 @@
       <c r="AV30" t="s">
         <v>34</v>
       </c>
-      <c r="AW30" s="2"/>
+      <c r="AW30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ30" s="4"/>
       <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
@@ -7518,7 +7578,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -7662,7 +7722,9 @@
       <c r="AV31" t="s">
         <v>34</v>
       </c>
-      <c r="AW31" s="2"/>
+      <c r="AW31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ31" s="4"/>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
@@ -7741,7 +7803,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AW4:AZ10 BE4:BJ10 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 AW11:BA22 BC11:BJ22 AW23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AX4:AZ10 BE4:BJ10 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AX11:BA13 AW4:AW13 AW14:BA22 AW23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7754,14 +7816,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7769,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -7777,7 +7839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -7785,7 +7847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -7793,7 +7855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -7801,7 +7863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -7809,7 +7871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -7817,7 +7879,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -7825,7 +7887,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -7833,7 +7895,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -7841,7 +7903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -7849,7 +7911,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -7857,7 +7919,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -7865,7 +7927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -7873,7 +7935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -7881,7 +7943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -7889,7 +7951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -7897,7 +7959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -7905,7 +7967,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -7913,7 +7975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -7921,7 +7983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -7929,7 +7991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -7937,7 +7999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -7945,7 +8007,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -7953,7 +8015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -7961,7 +8023,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -7969,7 +8031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -7977,7 +8039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -7985,7 +8047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -7993,7 +8055,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8010,18 +8072,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8029,7 +8091,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8038,7 +8100,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8047,7 +8109,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8056,7 +8118,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8065,13 +8127,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8080,7 +8142,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8089,7 +8151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8105,13 +8167,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8120,7 +8182,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8129,7 +8191,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8138,7 +8200,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8147,7 +8209,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8156,7 +8218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8165,7 +8227,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8174,7 +8236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8183,7 +8245,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8192,7 +8254,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8201,7 +8263,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8210,7 +8272,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8219,7 +8281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8228,25 +8290,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8255,7 +8317,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8264,7 +8326,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8273,7 +8335,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D767BA8D-5733-40B7-A3BE-6F8AE5D788A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B917467-C59E-4232-905B-967FB38E6D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1181,7 +1181,9 @@
       <c r="AW1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AX1" s="7"/>
+      <c r="AX1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="AY1" s="7"/>
       <c r="AZ1" s="7"/>
       <c r="BA1" s="7"/>
@@ -1372,7 +1374,9 @@
       <c r="AW2" s="7">
         <v>46241</v>
       </c>
-      <c r="AX2" s="1"/>
+      <c r="AX2" s="1">
+        <v>46246</v>
+      </c>
       <c r="AY2" s="7"/>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="7"/>
@@ -1560,6 +1564,9 @@
         <v>34</v>
       </c>
       <c r="AW3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AX3" t="s">
         <v>34</v>
       </c>
       <c r="AZ3" s="4"/>
@@ -1782,6 +1789,9 @@
       <c r="AW4" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX4" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ4" s="4"/>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
@@ -2002,6 +2012,9 @@
       <c r="AW5" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX5" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ5" s="4"/>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4"/>
@@ -2222,6 +2235,9 @@
       <c r="AW6" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX6" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ6" s="4"/>
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
@@ -2442,6 +2458,9 @@
       <c r="AW7" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX7" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ7" s="4"/>
       <c r="BA7" s="4"/>
       <c r="BB7" s="4"/>
@@ -2662,6 +2681,9 @@
       <c r="AW8" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX8" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
@@ -2882,6 +2904,9 @@
       <c r="AW9" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX9" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ9" s="4"/>
       <c r="BA9" s="4"/>
       <c r="BB9" s="4"/>
@@ -3102,6 +3127,9 @@
       <c r="AW10" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX10" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ10" s="4"/>
       <c r="BA10" s="4"/>
       <c r="BB10" s="4"/>
@@ -3322,6 +3350,9 @@
       <c r="AW11" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX11" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ11" s="4"/>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4"/>
@@ -3545,6 +3576,9 @@
       <c r="AW12" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX12" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
@@ -3765,6 +3799,9 @@
       <c r="AW13" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX13" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ13" s="4"/>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
@@ -3985,6 +4022,9 @@
       <c r="AW14" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="AX14" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ14" s="4"/>
       <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
@@ -4205,6 +4245,9 @@
       <c r="AW15" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX15" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
@@ -4425,6 +4468,9 @@
       <c r="AW16" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX16" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ16" s="4"/>
       <c r="BA16" s="4"/>
       <c r="BB16" s="4"/>
@@ -4645,6 +4691,9 @@
       <c r="AW17" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX17" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ17" s="4"/>
       <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
@@ -4865,6 +4914,9 @@
       <c r="AW18" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX18" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ18" s="4"/>
       <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
@@ -5085,6 +5137,9 @@
       <c r="AW19" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX19" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ19" s="4"/>
       <c r="BA19" s="4"/>
       <c r="BB19" s="4"/>
@@ -5305,6 +5360,9 @@
       <c r="AW20" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX20" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ20" s="4"/>
       <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
@@ -5525,6 +5583,9 @@
       <c r="AW21" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX21" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ21" s="4"/>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
@@ -5745,6 +5806,9 @@
       <c r="AW22" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="AX22" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ22" s="4"/>
       <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
@@ -5965,6 +6029,9 @@
       <c r="AW23" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX23" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ23" s="4"/>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
@@ -6185,6 +6252,9 @@
       <c r="AW24" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="AX24" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ24" s="4"/>
       <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
@@ -6405,6 +6475,9 @@
       <c r="AW25" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX25" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
@@ -6625,6 +6698,9 @@
       <c r="AW26" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX26" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ26" s="4"/>
       <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
@@ -6845,6 +6921,9 @@
       <c r="AW27" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX27" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ27" s="4"/>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
@@ -7065,6 +7144,9 @@
       <c r="AW28" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX28" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ28" s="4"/>
       <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
@@ -7285,6 +7367,9 @@
       <c r="AW29" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX29" t="s">
+        <v>35</v>
+      </c>
       <c r="AZ29" s="4"/>
       <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
@@ -7505,6 +7590,9 @@
       <c r="AW30" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX30" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ30" s="4"/>
       <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
@@ -7725,6 +7813,9 @@
       <c r="AW31" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AX31" t="s">
+        <v>34</v>
+      </c>
       <c r="AZ31" s="4"/>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
@@ -7803,7 +7894,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AX4:AZ10 BE4:BJ10 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 BC11:BJ22 AX11:BA13 AW4:AW13 AW14:BA22 AW23:BJ31">
+  <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AX4:AZ10 BE4:BJ10 AW4:AW13 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 AX11:BA13 BC11:BJ22 AW14:BA22 AW23:BJ31">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B917467-C59E-4232-905B-967FB38E6D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504501D8-5173-4AA9-ACBF-DC6B3EA5C38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1028,21 +1028,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="4" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="4" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1184,7 +1193,9 @@
       <c r="AX1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AY1" s="7"/>
+      <c r="AY1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="AZ1" s="7"/>
       <c r="BA1" s="7"/>
       <c r="BB1" s="7"/>
@@ -1226,7 +1237,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1377,7 +1388,9 @@
       <c r="AX2" s="1">
         <v>46246</v>
       </c>
-      <c r="AY2" s="7"/>
+      <c r="AY2" s="7">
+        <v>46248</v>
+      </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="7"/>
       <c r="BB2" s="1"/>
@@ -1419,7 +1432,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1567,6 +1580,9 @@
         <v>34</v>
       </c>
       <c r="AX3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ3" s="4"/>
@@ -1642,7 +1658,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1790,6 +1806,9 @@
         <v>34</v>
       </c>
       <c r="AX4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ4" s="4"/>
@@ -1865,7 +1884,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2013,6 +2032,9 @@
         <v>34</v>
       </c>
       <c r="AX5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ5" s="4"/>
@@ -2088,7 +2110,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2236,6 +2258,9 @@
         <v>34</v>
       </c>
       <c r="AX6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ6" s="4"/>
@@ -2311,7 +2336,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2459,6 +2484,9 @@
         <v>34</v>
       </c>
       <c r="AX7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ7" s="4"/>
@@ -2534,7 +2562,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2682,6 +2710,9 @@
         <v>34</v>
       </c>
       <c r="AX8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ8" s="4"/>
@@ -2757,7 +2788,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2905,6 +2936,9 @@
         <v>34</v>
       </c>
       <c r="AX9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ9" s="4"/>
@@ -2980,7 +3014,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3128,6 +3162,9 @@
         <v>34</v>
       </c>
       <c r="AX10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ10" s="4"/>
@@ -3203,7 +3240,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3351,6 +3388,9 @@
         <v>34</v>
       </c>
       <c r="AX11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ11" s="4"/>
@@ -3426,7 +3466,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3577,6 +3617,9 @@
         <v>34</v>
       </c>
       <c r="AX12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ12" s="4"/>
@@ -3652,7 +3695,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3800,6 +3843,9 @@
         <v>34</v>
       </c>
       <c r="AX13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ13" s="4"/>
@@ -3875,7 +3921,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4023,6 +4069,9 @@
         <v>35</v>
       </c>
       <c r="AX14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ14" s="4"/>
@@ -4098,7 +4147,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4246,6 +4295,9 @@
         <v>34</v>
       </c>
       <c r="AX15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ15" s="4"/>
@@ -4321,7 +4373,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4469,6 +4521,9 @@
         <v>34</v>
       </c>
       <c r="AX16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ16" s="4"/>
@@ -4544,7 +4599,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4692,6 +4747,9 @@
         <v>34</v>
       </c>
       <c r="AX17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ17" s="4"/>
@@ -4767,7 +4825,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4915,6 +4973,9 @@
         <v>34</v>
       </c>
       <c r="AX18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ18" s="4"/>
@@ -4990,7 +5051,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5138,6 +5199,9 @@
         <v>34</v>
       </c>
       <c r="AX19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY19" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ19" s="4"/>
@@ -5213,7 +5277,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5361,6 +5425,9 @@
         <v>34</v>
       </c>
       <c r="AX20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY20" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ20" s="4"/>
@@ -5436,7 +5503,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5584,6 +5651,9 @@
         <v>34</v>
       </c>
       <c r="AX21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY21" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ21" s="4"/>
@@ -5659,7 +5729,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5807,6 +5877,9 @@
         <v>35</v>
       </c>
       <c r="AX22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ22" s="4"/>
@@ -5882,7 +5955,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6030,6 +6103,9 @@
         <v>34</v>
       </c>
       <c r="AX23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ23" s="4"/>
@@ -6105,7 +6181,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6253,6 +6329,9 @@
         <v>35</v>
       </c>
       <c r="AX24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY24" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ24" s="4"/>
@@ -6328,7 +6407,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6477,6 +6556,9 @@
       </c>
       <c r="AX25" t="s">
         <v>34</v>
+      </c>
+      <c r="AY25" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="AZ25" s="4"/>
       <c r="BA25" s="4"/>
@@ -6551,7 +6633,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6699,6 +6781,9 @@
         <v>34</v>
       </c>
       <c r="AX26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ26" s="4"/>
@@ -6774,7 +6859,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -6922,6 +7007,9 @@
         <v>34</v>
       </c>
       <c r="AX27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY27" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ27" s="4"/>
@@ -6997,7 +7085,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7145,6 +7233,9 @@
         <v>34</v>
       </c>
       <c r="AX28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY28" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ28" s="4"/>
@@ -7220,7 +7311,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7369,6 +7460,9 @@
       </c>
       <c r="AX29" t="s">
         <v>35</v>
+      </c>
+      <c r="AY29" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="AZ29" s="4"/>
       <c r="BA29" s="4"/>
@@ -7443,7 +7537,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7592,6 +7686,9 @@
       </c>
       <c r="AX30" t="s">
         <v>34</v>
+      </c>
+      <c r="AY30" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="AZ30" s="4"/>
       <c r="BA30" s="4"/>
@@ -7666,7 +7763,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -7814,6 +7911,9 @@
         <v>34</v>
       </c>
       <c r="AX31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY31" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AZ31" s="4"/>
@@ -7907,14 +8007,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7922,7 +8022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -7930,7 +8030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -7938,7 +8038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -7946,7 +8046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -7954,7 +8054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -7962,7 +8062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -7970,7 +8070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -7978,7 +8078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -7986,7 +8086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -7994,7 +8094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8002,7 +8102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8010,7 +8110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8018,7 +8118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8026,7 +8126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8034,7 +8134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8042,7 +8142,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8050,7 +8150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8058,7 +8158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8066,7 +8166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8074,7 +8174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8082,7 +8182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8090,7 +8190,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8098,7 +8198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8106,7 +8206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8114,7 +8214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8122,7 +8222,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8130,7 +8230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8138,7 +8238,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8146,7 +8246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8163,18 +8263,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8182,7 +8282,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8191,7 +8291,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8200,7 +8300,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8209,7 +8309,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8218,13 +8318,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8233,7 +8333,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8242,7 +8342,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8258,13 +8358,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8273,7 +8373,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8282,7 +8382,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8291,7 +8391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8300,7 +8400,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8309,7 +8409,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8318,7 +8418,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8327,7 +8427,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8336,7 +8436,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8345,7 +8445,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8354,7 +8454,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8363,7 +8463,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8372,7 +8472,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8381,25 +8481,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8408,7 +8508,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8417,7 +8517,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8426,7 +8526,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504501D8-5173-4AA9-ACBF-DC6B3EA5C38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECBF5B1-841C-4766-AB0D-9AD76AE65F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1028,30 +1028,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="4" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="4" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1196,7 +1195,9 @@
       <c r="AY1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AZ1" s="7"/>
+      <c r="AZ1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="BA1" s="7"/>
       <c r="BB1" s="7"/>
       <c r="BC1" s="7"/>
@@ -1237,7 +1238,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1391,7 +1392,9 @@
       <c r="AY2" s="7">
         <v>46248</v>
       </c>
-      <c r="AZ2" s="1"/>
+      <c r="AZ2" s="1">
+        <v>46253</v>
+      </c>
       <c r="BA2" s="7"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="7"/>
@@ -1432,7 +1435,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1585,7 +1588,9 @@
       <c r="AY3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ3" s="4"/>
+      <c r="AZ3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA3" s="4"/>
       <c r="BB3" s="4"/>
       <c r="BC3" s="4"/>
@@ -1658,7 +1663,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1811,7 +1816,9 @@
       <c r="AY4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ4" s="4"/>
+      <c r="AZ4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4"/>
@@ -1884,7 +1891,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2037,7 +2044,9 @@
       <c r="AY5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ5" s="4"/>
+      <c r="AZ5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4"/>
       <c r="BC5" s="4"/>
@@ -2110,7 +2119,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2263,7 +2272,9 @@
       <c r="AY6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ6" s="4"/>
+      <c r="AZ6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
       <c r="BC6" s="4"/>
@@ -2336,7 +2347,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2489,7 +2500,9 @@
       <c r="AY7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ7" s="4"/>
+      <c r="AZ7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA7" s="4"/>
       <c r="BB7" s="4"/>
       <c r="BC7" s="4"/>
@@ -2562,7 +2575,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2715,7 +2728,9 @@
       <c r="AY8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ8" s="4"/>
+      <c r="AZ8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
       <c r="BC8" s="4"/>
@@ -2788,7 +2803,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2941,7 +2956,9 @@
       <c r="AY9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ9" s="4"/>
+      <c r="AZ9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA9" s="4"/>
       <c r="BB9" s="4"/>
       <c r="BC9" s="4"/>
@@ -3014,7 +3031,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3167,7 +3184,9 @@
       <c r="AY10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ10" s="4"/>
+      <c r="AZ10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA10" s="4"/>
       <c r="BB10" s="4"/>
       <c r="BC10" s="4"/>
@@ -3240,7 +3259,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3393,7 +3412,9 @@
       <c r="AY11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ11" s="4"/>
+      <c r="AZ11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
@@ -3466,7 +3487,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3622,7 +3643,9 @@
       <c r="AY12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ12" s="4"/>
+      <c r="AZ12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
       <c r="BC12" s="4"/>
@@ -3695,7 +3718,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3848,7 +3871,9 @@
       <c r="AY13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ13" s="4"/>
+      <c r="AZ13" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
@@ -3921,7 +3946,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4074,7 +4099,9 @@
       <c r="AY14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ14" s="4"/>
+      <c r="AZ14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
       <c r="BC14" s="4"/>
@@ -4147,7 +4174,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4300,7 +4327,9 @@
       <c r="AY15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ15" s="4"/>
+      <c r="AZ15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
       <c r="BC15" s="4"/>
@@ -4373,7 +4402,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4526,7 +4555,9 @@
       <c r="AY16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ16" s="4"/>
+      <c r="AZ16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA16" s="4"/>
       <c r="BB16" s="4"/>
       <c r="BC16" s="4"/>
@@ -4599,7 +4630,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4752,7 +4783,9 @@
       <c r="AY17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ17" s="4"/>
+      <c r="AZ17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
@@ -4825,7 +4858,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -4978,7 +5011,9 @@
       <c r="AY18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ18" s="4"/>
+      <c r="AZ18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
@@ -5051,7 +5086,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5204,7 +5239,9 @@
       <c r="AY19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ19" s="4"/>
+      <c r="AZ19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA19" s="4"/>
       <c r="BB19" s="4"/>
       <c r="BC19" s="4"/>
@@ -5277,7 +5314,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5430,7 +5467,9 @@
       <c r="AY20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ20" s="4"/>
+      <c r="AZ20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
@@ -5503,7 +5542,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5656,7 +5695,9 @@
       <c r="AY21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ21" s="4"/>
+      <c r="AZ21" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
@@ -5729,7 +5770,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5882,7 +5923,9 @@
       <c r="AY22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ22" s="4"/>
+      <c r="AZ22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
@@ -5955,7 +5998,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6108,7 +6151,9 @@
       <c r="AY23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ23" s="4"/>
+      <c r="AZ23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
@@ -6181,7 +6226,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6334,7 +6379,9 @@
       <c r="AY24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ24" s="4"/>
+      <c r="AZ24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
@@ -6407,7 +6454,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6560,7 +6607,9 @@
       <c r="AY25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AZ25" s="4"/>
+      <c r="AZ25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
@@ -6633,7 +6682,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6786,7 +6835,9 @@
       <c r="AY26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ26" s="4"/>
+      <c r="AZ26" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
@@ -6859,7 +6910,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7012,7 +7063,9 @@
       <c r="AY27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ27" s="4"/>
+      <c r="AZ27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
@@ -7085,7 +7138,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7238,7 +7291,9 @@
       <c r="AY28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ28" s="4"/>
+      <c r="AZ28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
@@ -7311,7 +7366,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7464,7 +7519,9 @@
       <c r="AY29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ29" s="4"/>
+      <c r="AZ29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
@@ -7537,7 +7594,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7690,7 +7747,9 @@
       <c r="AY30" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AZ30" s="4"/>
+      <c r="AZ30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
       <c r="BC30" s="4"/>
@@ -7763,7 +7822,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -7916,7 +7975,9 @@
       <c r="AY31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AZ31" s="4"/>
+      <c r="AZ31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
       <c r="BC31" s="4"/>
@@ -8007,14 +8068,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8022,7 +8083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8030,7 +8091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8038,7 +8099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8046,7 +8107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8054,7 +8115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8062,7 +8123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8070,7 +8131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8078,7 +8139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8086,7 +8147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8094,7 +8155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8102,7 +8163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8110,7 +8171,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8118,7 +8179,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8126,7 +8187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8134,7 +8195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8142,7 +8203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8150,7 +8211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8158,7 +8219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8166,7 +8227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8174,7 +8235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8182,7 +8243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8190,7 +8251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8198,7 +8259,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8206,7 +8267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8214,7 +8275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8222,7 +8283,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8230,7 +8291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8238,7 +8299,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8246,7 +8307,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8263,18 +8324,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8282,7 +8343,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8291,7 +8352,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8300,7 +8361,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8309,7 +8370,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8318,13 +8379,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8333,7 +8394,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8342,7 +8403,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8358,13 +8419,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8373,7 +8434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8382,7 +8443,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8391,7 +8452,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8400,7 +8461,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8409,7 +8470,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8418,7 +8479,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8427,7 +8488,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8436,7 +8497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8445,7 +8506,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8454,7 +8515,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8463,7 +8524,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8472,7 +8533,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8481,25 +8542,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8508,7 +8569,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8517,7 +8578,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8526,7 +8587,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECBF5B1-841C-4766-AB0D-9AD76AE65F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA7B195-E75C-4EDF-ACC7-2EEE100574F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5696,7 +5696,7 @@
         <v>34</v>
       </c>
       <c r="AZ21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA7B195-E75C-4EDF-ACC7-2EEE100574F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177D1F59-ECDE-4712-A422-1ACBFDE4A2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>FÉRIAS</t>
+  </si>
+  <si>
+    <t>3F | P</t>
   </si>
 </sst>
 </file>
@@ -740,7 +743,27 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3872,7 +3895,7 @@
         <v>34</v>
       </c>
       <c r="AZ13" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
@@ -8056,8 +8079,13 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AX4:AZ10 BE4:BJ10 AW4:AW13 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 AX11:BA13 BC11:BJ22 AW14:BA22 AW23:BJ31">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AZ3:AZ31">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177D1F59-ECDE-4712-A422-1ACBFDE4A2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173211B0-D42F-4CE9-9183-8085F34BF44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -743,17 +743,7 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1051,29 +1041,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="4" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1221,7 +1213,9 @@
       <c r="AZ1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BA1" s="7"/>
+      <c r="BA1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BB1" s="7"/>
       <c r="BC1" s="7"/>
       <c r="BD1" s="7"/>
@@ -1261,7 +1255,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1418,7 +1412,9 @@
       <c r="AZ2" s="1">
         <v>46253</v>
       </c>
-      <c r="BA2" s="7"/>
+      <c r="BA2" s="7">
+        <v>46255</v>
+      </c>
       <c r="BB2" s="1"/>
       <c r="BC2" s="7"/>
       <c r="BD2" s="1"/>
@@ -1458,7 +1454,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1614,7 +1610,9 @@
       <c r="AZ3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA3" s="4"/>
+      <c r="BA3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB3" s="4"/>
       <c r="BC3" s="4"/>
       <c r="BD3" s="4"/>
@@ -1686,7 +1684,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1842,7 +1840,9 @@
       <c r="AZ4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA4" s="4"/>
+      <c r="BA4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4"/>
       <c r="BD4" s="4"/>
@@ -1914,7 +1914,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2070,7 +2070,9 @@
       <c r="AZ5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA5" s="4"/>
+      <c r="BA5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB5" s="4"/>
       <c r="BC5" s="4"/>
       <c r="BD5" s="4"/>
@@ -2142,7 +2144,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2298,7 +2300,9 @@
       <c r="AZ6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA6" s="4"/>
+      <c r="BA6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB6" s="4"/>
       <c r="BC6" s="4"/>
       <c r="BD6" s="4"/>
@@ -2370,7 +2374,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2526,7 +2530,9 @@
       <c r="AZ7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA7" s="4"/>
+      <c r="BA7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB7" s="4"/>
       <c r="BC7" s="4"/>
       <c r="BD7" s="4"/>
@@ -2598,7 +2604,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2754,7 +2760,9 @@
       <c r="AZ8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA8" s="4"/>
+      <c r="BA8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB8" s="4"/>
       <c r="BC8" s="4"/>
       <c r="BD8" s="4"/>
@@ -2826,7 +2834,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2982,7 +2990,9 @@
       <c r="AZ9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA9" s="4"/>
+      <c r="BA9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB9" s="4"/>
       <c r="BC9" s="4"/>
       <c r="BD9" s="4"/>
@@ -3054,7 +3064,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3210,7 +3220,9 @@
       <c r="AZ10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA10" s="4"/>
+      <c r="BA10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB10" s="4"/>
       <c r="BC10" s="4"/>
       <c r="BD10" s="4"/>
@@ -3282,7 +3294,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3438,7 +3450,9 @@
       <c r="AZ11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA11" s="4"/>
+      <c r="BA11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
       <c r="BD11" s="4"/>
@@ -3510,7 +3524,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3669,7 +3683,9 @@
       <c r="AZ12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA12" s="4"/>
+      <c r="BA12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BB12" s="4"/>
       <c r="BC12" s="4"/>
       <c r="BD12" s="4"/>
@@ -3741,7 +3757,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3897,7 +3913,9 @@
       <c r="AZ13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="BA13" s="4"/>
+      <c r="BA13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
       <c r="BD13" s="4"/>
@@ -3969,7 +3987,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4125,7 +4143,9 @@
       <c r="AZ14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA14" s="4"/>
+      <c r="BA14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB14" s="4"/>
       <c r="BC14" s="4"/>
       <c r="BD14" s="4"/>
@@ -4197,7 +4217,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4353,7 +4373,9 @@
       <c r="AZ15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA15" s="4"/>
+      <c r="BA15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB15" s="4"/>
       <c r="BC15" s="4"/>
       <c r="BD15" s="4"/>
@@ -4425,7 +4447,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4581,7 +4603,9 @@
       <c r="AZ16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA16" s="4"/>
+      <c r="BA16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB16" s="4"/>
       <c r="BC16" s="4"/>
       <c r="BD16" s="4"/>
@@ -4653,7 +4677,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4809,7 +4833,9 @@
       <c r="AZ17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA17" s="4"/>
+      <c r="BA17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
       <c r="BD17" s="4"/>
@@ -4881,7 +4907,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5037,7 +5063,9 @@
       <c r="AZ18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA18" s="4"/>
+      <c r="BA18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
       <c r="BD18" s="4"/>
@@ -5109,7 +5137,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5265,7 +5293,9 @@
       <c r="AZ19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA19" s="4"/>
+      <c r="BA19" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BB19" s="4"/>
       <c r="BC19" s="4"/>
       <c r="BD19" s="4"/>
@@ -5337,7 +5367,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5493,7 +5523,9 @@
       <c r="AZ20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA20" s="4"/>
+      <c r="BA20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
       <c r="BD20" s="4"/>
@@ -5565,7 +5597,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5721,7 +5753,9 @@
       <c r="AZ21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA21" s="4"/>
+      <c r="BA21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
       <c r="BD21" s="4"/>
@@ -5793,7 +5827,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5949,7 +5983,9 @@
       <c r="AZ22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA22" s="4"/>
+      <c r="BA22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
       <c r="BD22" s="4"/>
@@ -6021,7 +6057,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6177,7 +6213,9 @@
       <c r="AZ23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA23" s="4"/>
+      <c r="BA23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
       <c r="BD23" s="4"/>
@@ -6249,7 +6287,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6405,7 +6443,9 @@
       <c r="AZ24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA24" s="4"/>
+      <c r="BA24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
       <c r="BD24" s="4"/>
@@ -6477,7 +6517,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6633,7 +6673,9 @@
       <c r="AZ25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA25" s="4"/>
+      <c r="BA25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
@@ -6705,7 +6747,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6861,7 +6903,9 @@
       <c r="AZ26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BA26" s="4"/>
+      <c r="BA26" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
       <c r="BD26" s="4"/>
@@ -6933,7 +6977,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7089,7 +7133,9 @@
       <c r="AZ27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA27" s="4"/>
+      <c r="BA27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4"/>
@@ -7161,7 +7207,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7317,7 +7363,9 @@
       <c r="AZ28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA28" s="4"/>
+      <c r="BA28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
       <c r="BD28" s="4"/>
@@ -7389,7 +7437,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7545,7 +7593,9 @@
       <c r="AZ29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA29" s="4"/>
+      <c r="BA29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
       <c r="BD29" s="4"/>
@@ -7617,7 +7667,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7773,7 +7823,9 @@
       <c r="AZ30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA30" s="4"/>
+      <c r="BA30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB30" s="4"/>
       <c r="BC30" s="4"/>
       <c r="BD30" s="4"/>
@@ -7845,7 +7897,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8001,7 +8053,9 @@
       <c r="AZ31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BA31" s="4"/>
+      <c r="BA31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BB31" s="4"/>
       <c r="BC31" s="4"/>
       <c r="BD31" s="4"/>
@@ -8078,8 +8132,8 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 AS3:AZ3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 AX4:AZ10 BE4:BJ10 AW4:AW13 O4:AB31 AS4:AV31 BK4:DG31 D6:J31 M6:N31 AX11:BA13 BC11:BJ22 AW14:BA22 AW23:BJ31">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AS3:AZ31 BC11:BJ22 BB23:BJ31 BA5:BA31">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8096,14 +8150,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8111,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8119,7 +8173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8127,7 +8181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8135,7 +8189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8143,7 +8197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8151,7 +8205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8159,7 +8213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8167,7 +8221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8175,7 +8229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8183,7 +8237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8191,7 +8245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8199,7 +8253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8207,7 +8261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8215,7 +8269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8223,7 +8277,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8231,7 +8285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8239,7 +8293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8247,7 +8301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8255,7 +8309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8263,7 +8317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8271,7 +8325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8279,7 +8333,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8287,7 +8341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8295,7 +8349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8303,7 +8357,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8311,7 +8365,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8319,7 +8373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8327,7 +8381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8335,7 +8389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8352,18 +8406,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8371,7 +8425,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8380,7 +8434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8389,7 +8443,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8398,7 +8452,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8407,13 +8461,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8422,7 +8476,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8431,7 +8485,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8447,13 +8501,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8462,7 +8516,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8471,7 +8525,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8480,7 +8534,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8489,7 +8543,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8498,7 +8552,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8507,7 +8561,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8516,7 +8570,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8525,7 +8579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8534,7 +8588,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8543,7 +8597,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8552,7 +8606,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8561,7 +8615,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8570,25 +8624,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8597,7 +8651,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8606,7 +8660,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8615,7 +8669,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173211B0-D42F-4CE9-9183-8085F34BF44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1E9E63-1F33-45C9-A914-058BC283F059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -743,7 +743,57 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1041,31 +1091,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS31"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1216,7 +1265,9 @@
       <c r="BA1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BB1" s="7"/>
+      <c r="BB1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="BC1" s="7"/>
       <c r="BD1" s="7"/>
       <c r="BE1" s="7"/>
@@ -1255,7 +1306,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1415,7 +1466,9 @@
       <c r="BA2" s="7">
         <v>46255</v>
       </c>
-      <c r="BB2" s="1"/>
+      <c r="BB2" s="1">
+        <v>46260</v>
+      </c>
       <c r="BC2" s="7"/>
       <c r="BD2" s="1"/>
       <c r="BE2" s="7"/>
@@ -1454,7 +1507,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1613,7 +1666,9 @@
       <c r="BA3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB3" s="4"/>
+      <c r="BB3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC3" s="4"/>
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
@@ -1684,7 +1739,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1843,7 +1898,9 @@
       <c r="BA4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB4" s="4"/>
+      <c r="BB4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC4" s="4"/>
       <c r="BD4" s="4"/>
       <c r="BE4" s="4"/>
@@ -1914,7 +1971,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2073,7 +2130,9 @@
       <c r="BA5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB5" s="4"/>
+      <c r="BB5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC5" s="4"/>
       <c r="BD5" s="4"/>
       <c r="BE5" s="4"/>
@@ -2144,7 +2203,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2303,7 +2362,9 @@
       <c r="BA6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB6" s="4"/>
+      <c r="BB6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC6" s="4"/>
       <c r="BD6" s="4"/>
       <c r="BE6" s="4"/>
@@ -2374,7 +2435,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2533,7 +2594,9 @@
       <c r="BA7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB7" s="4"/>
+      <c r="BB7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC7" s="4"/>
       <c r="BD7" s="4"/>
       <c r="BE7" s="4"/>
@@ -2604,7 +2667,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2763,7 +2826,9 @@
       <c r="BA8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB8" s="4"/>
+      <c r="BB8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC8" s="4"/>
       <c r="BD8" s="4"/>
       <c r="BE8" s="4"/>
@@ -2834,7 +2899,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -2993,7 +3058,9 @@
       <c r="BA9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB9" s="4"/>
+      <c r="BB9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC9" s="4"/>
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
@@ -3064,7 +3131,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3223,7 +3290,9 @@
       <c r="BA10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB10" s="4"/>
+      <c r="BB10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC10" s="4"/>
       <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
@@ -3294,7 +3363,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3453,7 +3522,9 @@
       <c r="BA11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB11" s="4"/>
+      <c r="BB11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC11" s="4"/>
       <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
@@ -3524,7 +3595,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3686,7 +3757,9 @@
       <c r="BA12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BB12" s="4"/>
+      <c r="BB12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BC12" s="4"/>
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
@@ -3757,7 +3830,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -3916,7 +3989,9 @@
       <c r="BA13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB13" s="4"/>
+      <c r="BB13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC13" s="4"/>
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
@@ -3987,7 +4062,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4146,7 +4221,9 @@
       <c r="BA14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB14" s="4"/>
+      <c r="BB14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC14" s="4"/>
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
@@ -4217,7 +4294,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4376,7 +4453,9 @@
       <c r="BA15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB15" s="4"/>
+      <c r="BB15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC15" s="4"/>
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
@@ -4447,7 +4526,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4606,7 +4685,9 @@
       <c r="BA16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB16" s="4"/>
+      <c r="BB16" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BC16" s="4"/>
       <c r="BD16" s="4"/>
       <c r="BE16" s="4"/>
@@ -4677,7 +4758,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4836,7 +4917,9 @@
       <c r="BA17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB17" s="4"/>
+      <c r="BB17" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BC17" s="4"/>
       <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
@@ -4907,7 +4990,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5066,7 +5149,9 @@
       <c r="BA18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB18" s="4"/>
+      <c r="BB18" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BC18" s="4"/>
       <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
@@ -5137,7 +5222,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5296,7 +5381,9 @@
       <c r="BA19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BB19" s="4"/>
+      <c r="BB19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC19" s="4"/>
       <c r="BD19" s="4"/>
       <c r="BE19" s="4"/>
@@ -5367,7 +5454,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5526,7 +5613,9 @@
       <c r="BA20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB20" s="4"/>
+      <c r="BB20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC20" s="4"/>
       <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
@@ -5597,7 +5686,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5756,7 +5845,9 @@
       <c r="BA21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB21" s="4"/>
+      <c r="BB21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC21" s="4"/>
       <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
@@ -5827,7 +5918,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -5986,7 +6077,9 @@
       <c r="BA22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB22" s="4"/>
+      <c r="BB22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC22" s="4"/>
       <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
@@ -6057,7 +6150,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6216,7 +6309,9 @@
       <c r="BA23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB23" s="4"/>
+      <c r="BB23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC23" s="4"/>
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
@@ -6287,7 +6382,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6446,7 +6541,9 @@
       <c r="BA24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB24" s="4"/>
+      <c r="BB24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC24" s="4"/>
       <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
@@ -6517,7 +6614,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6676,7 +6773,9 @@
       <c r="BA25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB25" s="4"/>
+      <c r="BB25" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
@@ -6747,7 +6846,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -6906,7 +7005,9 @@
       <c r="BA26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BB26" s="4"/>
+      <c r="BB26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC26" s="4"/>
       <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
@@ -6977,7 +7078,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7136,7 +7237,9 @@
       <c r="BA27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB27" s="4"/>
+      <c r="BB27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
@@ -7207,7 +7310,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7366,7 +7469,9 @@
       <c r="BA28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB28" s="4"/>
+      <c r="BB28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC28" s="4"/>
       <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
@@ -7437,7 +7542,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7596,7 +7701,9 @@
       <c r="BA29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB29" s="4"/>
+      <c r="BB29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC29" s="4"/>
       <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
@@ -7667,7 +7774,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -7826,7 +7933,9 @@
       <c r="BA30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB30" s="4"/>
+      <c r="BB30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC30" s="4"/>
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
@@ -7897,7 +8006,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8056,7 +8165,9 @@
       <c r="BA31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BB31" s="4"/>
+      <c r="BB31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BC31" s="4"/>
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
@@ -8132,14 +8243,39 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 BB3:BB22 K3:L31 AC3:AQ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 D6:J31 M6:N31 AS3:AZ31 BC11:BJ22 BB23:BJ31 BA5:BA31">
+  <conditionalFormatting sqref="D3:AB3 BE3:DG3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 BA5:BA31 D6:J31 M6:N31 BC11:BJ31">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AZ3:AZ31">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB12">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB16">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB17">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB18">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
+  <conditionalFormatting sqref="BB25">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8150,14 +8286,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8165,7 +8301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8173,7 +8309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8181,7 +8317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8189,7 +8325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8197,7 +8333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8205,7 +8341,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8213,7 +8349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8221,7 +8357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8229,7 +8365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8237,7 +8373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8245,7 +8381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8253,7 +8389,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8261,7 +8397,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8269,7 +8405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8277,7 +8413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8285,7 +8421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8293,7 +8429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8301,7 +8437,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8309,7 +8445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8317,7 +8453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8325,7 +8461,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8333,7 +8469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8341,7 +8477,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8349,7 +8485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8357,7 +8493,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8365,7 +8501,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8373,7 +8509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8381,7 +8517,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8389,7 +8525,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8406,18 +8542,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8425,7 +8561,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8434,7 +8570,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8443,7 +8579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8452,7 +8588,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8461,13 +8597,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8476,7 +8612,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8485,7 +8621,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8501,13 +8637,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8516,7 +8652,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8525,7 +8661,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8534,7 +8670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8543,7 +8679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8552,7 +8688,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8561,7 +8697,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8570,7 +8706,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8579,7 +8715,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8588,7 +8724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8597,7 +8733,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8606,7 +8742,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8615,7 +8751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8624,25 +8760,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8651,7 +8787,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8660,7 +8796,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8669,7 +8805,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1E9E63-1F33-45C9-A914-058BC283F059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A73785-17E7-42BD-B36A-63F98D465E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -743,27 +743,7 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4686,7 +4666,7 @@
         <v>34</v>
       </c>
       <c r="BB16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BC16" s="4"/>
       <c r="BD16" s="4"/>
@@ -6774,7 +6754,7 @@
         <v>34</v>
       </c>
       <c r="BB25" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
@@ -8244,31 +8224,21 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:AB3 BE3:DG3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 BA5:BA31 D6:J31 M6:N31 BC11:BJ31">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB16">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB17">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB18">
+  <conditionalFormatting sqref="BB16:BB18">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A73785-17E7-42BD-B36A-63F98D465E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8424EBD-A7D5-4C47-AB38-5A6319805FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5130,7 +5130,7 @@
         <v>34</v>
       </c>
       <c r="BB18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BC18" s="4"/>
       <c r="BD18" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8424EBD-A7D5-4C47-AB38-5A6319805FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6B0F05-000F-4250-B79F-FACD7E67CB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -1248,7 +1248,9 @@
       <c r="BB1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BC1" s="7"/>
+      <c r="BC1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BD1" s="7"/>
       <c r="BE1" s="7"/>
       <c r="BF1" s="7"/>
@@ -1449,7 +1451,9 @@
       <c r="BB2" s="1">
         <v>46260</v>
       </c>
-      <c r="BC2" s="7"/>
+      <c r="BC2" s="7">
+        <v>46262</v>
+      </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="7"/>
       <c r="BF2" s="1"/>
@@ -1649,7 +1653,9 @@
       <c r="BB3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC3" s="4"/>
+      <c r="BC3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
@@ -1881,7 +1887,9 @@
       <c r="BB4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC4" s="4"/>
+      <c r="BC4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD4" s="4"/>
       <c r="BE4" s="4"/>
       <c r="BF4" s="4"/>
@@ -2113,7 +2121,9 @@
       <c r="BB5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC5" s="4"/>
+      <c r="BC5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD5" s="4"/>
       <c r="BE5" s="4"/>
       <c r="BF5" s="4"/>
@@ -2345,7 +2355,9 @@
       <c r="BB6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC6" s="4"/>
+      <c r="BC6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD6" s="4"/>
       <c r="BE6" s="4"/>
       <c r="BF6" s="4"/>
@@ -2577,7 +2589,9 @@
       <c r="BB7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC7" s="4"/>
+      <c r="BC7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD7" s="4"/>
       <c r="BE7" s="4"/>
       <c r="BF7" s="4"/>
@@ -2809,7 +2823,9 @@
       <c r="BB8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC8" s="4"/>
+      <c r="BC8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD8" s="4"/>
       <c r="BE8" s="4"/>
       <c r="BF8" s="4"/>
@@ -3041,7 +3057,9 @@
       <c r="BB9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC9" s="4"/>
+      <c r="BC9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
       <c r="BF9" s="4"/>
@@ -3273,7 +3291,9 @@
       <c r="BB10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC10" s="4"/>
+      <c r="BC10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
       <c r="BF10" s="4"/>
@@ -3505,7 +3525,9 @@
       <c r="BB11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC11" s="4"/>
+      <c r="BC11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
       <c r="BF11" s="4"/>
@@ -3740,7 +3762,9 @@
       <c r="BB12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BC12" s="4"/>
+      <c r="BC12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
       <c r="BF12" s="4"/>
@@ -3972,7 +3996,9 @@
       <c r="BB13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC13" s="4"/>
+      <c r="BC13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
@@ -4204,7 +4230,9 @@
       <c r="BB14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC14" s="4"/>
+      <c r="BC14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
       <c r="BF14" s="4"/>
@@ -4436,7 +4464,9 @@
       <c r="BB15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC15" s="4"/>
+      <c r="BC15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
       <c r="BF15" s="4"/>
@@ -4668,7 +4698,9 @@
       <c r="BB16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC16" s="4"/>
+      <c r="BC16" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BD16" s="4"/>
       <c r="BE16" s="4"/>
       <c r="BF16" s="4"/>
@@ -4900,7 +4932,9 @@
       <c r="BB17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BC17" s="4"/>
+      <c r="BC17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
       <c r="BF17" s="4"/>
@@ -5132,7 +5166,9 @@
       <c r="BB18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC18" s="4"/>
+      <c r="BC18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
       <c r="BF18" s="4"/>
@@ -5364,7 +5400,9 @@
       <c r="BB19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC19" s="4"/>
+      <c r="BC19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD19" s="4"/>
       <c r="BE19" s="4"/>
       <c r="BF19" s="4"/>
@@ -5596,7 +5634,9 @@
       <c r="BB20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC20" s="4"/>
+      <c r="BC20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
       <c r="BF20" s="4"/>
@@ -5828,7 +5868,9 @@
       <c r="BB21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC21" s="4"/>
+      <c r="BC21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
       <c r="BF21" s="4"/>
@@ -6060,7 +6102,9 @@
       <c r="BB22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC22" s="4"/>
+      <c r="BC22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
       <c r="BF22" s="4"/>
@@ -6292,7 +6336,9 @@
       <c r="BB23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC23" s="4"/>
+      <c r="BC23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
@@ -6524,7 +6570,9 @@
       <c r="BB24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC24" s="4"/>
+      <c r="BC24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
       <c r="BF24" s="4"/>
@@ -6756,7 +6804,9 @@
       <c r="BB25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC25" s="4"/>
+      <c r="BC25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
       <c r="BF25" s="4"/>
@@ -6988,7 +7038,9 @@
       <c r="BB26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC26" s="4"/>
+      <c r="BC26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
@@ -7220,7 +7272,9 @@
       <c r="BB27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC27" s="4"/>
+      <c r="BC27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
       <c r="BF27" s="4"/>
@@ -7452,7 +7506,9 @@
       <c r="BB28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC28" s="4"/>
+      <c r="BC28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
       <c r="BF28" s="4"/>
@@ -7684,7 +7740,9 @@
       <c r="BB29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC29" s="4"/>
+      <c r="BC29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
@@ -7916,7 +7974,9 @@
       <c r="BB30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC30" s="4"/>
+      <c r="BC30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
       <c r="BF30" s="4"/>
@@ -8148,7 +8208,9 @@
       <c r="BB31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BC31" s="4"/>
+      <c r="BC31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
       <c r="BF31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6B0F05-000F-4250-B79F-FACD7E67CB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFD6C20-C3F8-4D4D-9433-4B9967D77039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -189,7 +189,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +339,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -686,7 +694,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -697,6 +705,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1070,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DS31"/>
+  <dimension ref="A1:DS32"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1251,7 +1260,9 @@
       <c r="BC1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BD1" s="7"/>
+      <c r="BD1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="BE1" s="7"/>
       <c r="BF1" s="7"/>
       <c r="BG1" s="7"/>
@@ -1454,7 +1465,9 @@
       <c r="BC2" s="7">
         <v>46262</v>
       </c>
-      <c r="BD2" s="1"/>
+      <c r="BD2" s="1">
+        <v>46267</v>
+      </c>
       <c r="BE2" s="7"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="7"/>
@@ -1656,7 +1669,9 @@
       <c r="BC3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD3" s="4"/>
+      <c r="BD3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
@@ -1890,7 +1905,9 @@
       <c r="BC4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD4" s="4"/>
+      <c r="BD4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE4" s="4"/>
       <c r="BF4" s="4"/>
       <c r="BG4" s="4"/>
@@ -2124,7 +2141,9 @@
       <c r="BC5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD5" s="4"/>
+      <c r="BD5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE5" s="4"/>
       <c r="BF5" s="4"/>
       <c r="BG5" s="4"/>
@@ -2358,7 +2377,9 @@
       <c r="BC6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD6" s="4"/>
+      <c r="BD6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE6" s="4"/>
       <c r="BF6" s="4"/>
       <c r="BG6" s="4"/>
@@ -2592,7 +2613,9 @@
       <c r="BC7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD7" s="4"/>
+      <c r="BD7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE7" s="4"/>
       <c r="BF7" s="4"/>
       <c r="BG7" s="4"/>
@@ -2826,7 +2849,9 @@
       <c r="BC8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD8" s="4"/>
+      <c r="BD8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE8" s="4"/>
       <c r="BF8" s="4"/>
       <c r="BG8" s="4"/>
@@ -3060,7 +3085,9 @@
       <c r="BC9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD9" s="4"/>
+      <c r="BD9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE9" s="4"/>
       <c r="BF9" s="4"/>
       <c r="BG9" s="4"/>
@@ -3294,7 +3321,9 @@
       <c r="BC10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD10" s="4"/>
+      <c r="BD10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE10" s="4"/>
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
@@ -3528,7 +3557,9 @@
       <c r="BC11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD11" s="4"/>
+      <c r="BD11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE11" s="4"/>
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
@@ -3765,7 +3796,9 @@
       <c r="BC12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BD12" s="4"/>
+      <c r="BD12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BE12" s="4"/>
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
@@ -3999,7 +4032,9 @@
       <c r="BC13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD13" s="4"/>
+      <c r="BD13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
@@ -4233,7 +4268,9 @@
       <c r="BC14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD14" s="4"/>
+      <c r="BD14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE14" s="4"/>
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
@@ -4467,7 +4504,9 @@
       <c r="BC15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD15" s="4"/>
+      <c r="BD15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE15" s="4"/>
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
@@ -4701,7 +4740,9 @@
       <c r="BC16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BD16" s="4"/>
+      <c r="BD16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE16" s="4"/>
       <c r="BF16" s="4"/>
       <c r="BG16" s="4"/>
@@ -4935,7 +4976,9 @@
       <c r="BC17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD17" s="4"/>
+      <c r="BD17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE17" s="4"/>
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
@@ -5169,7 +5212,9 @@
       <c r="BC18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD18" s="4"/>
+      <c r="BD18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE18" s="4"/>
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
@@ -5403,7 +5448,9 @@
       <c r="BC19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD19" s="4"/>
+      <c r="BD19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE19" s="4"/>
       <c r="BF19" s="4"/>
       <c r="BG19" s="4"/>
@@ -5637,7 +5684,9 @@
       <c r="BC20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD20" s="4"/>
+      <c r="BD20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE20" s="4"/>
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
@@ -5871,7 +5920,9 @@
       <c r="BC21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD21" s="4"/>
+      <c r="BD21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE21" s="4"/>
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
@@ -6105,7 +6156,9 @@
       <c r="BC22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD22" s="4"/>
+      <c r="BD22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE22" s="4"/>
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
@@ -6339,7 +6392,9 @@
       <c r="BC23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD23" s="4"/>
+      <c r="BD23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
@@ -6573,7 +6628,9 @@
       <c r="BC24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD24" s="4"/>
+      <c r="BD24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE24" s="4"/>
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
@@ -6807,7 +6864,9 @@
       <c r="BC25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD25" s="4"/>
+      <c r="BD25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE25" s="4"/>
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
@@ -7041,7 +7100,9 @@
       <c r="BC26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD26" s="4"/>
+      <c r="BD26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
@@ -7275,7 +7336,9 @@
       <c r="BC27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD27" s="4"/>
+      <c r="BD27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE27" s="4"/>
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
@@ -7509,7 +7572,9 @@
       <c r="BC28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD28" s="4"/>
+      <c r="BD28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE28" s="4"/>
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
@@ -7743,7 +7808,9 @@
       <c r="BC29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD29" s="4"/>
+      <c r="BD29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
@@ -7977,7 +8044,9 @@
       <c r="BC30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD30" s="4"/>
+      <c r="BD30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BE30" s="4"/>
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
@@ -8211,7 +8280,9 @@
       <c r="BC31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD31" s="4"/>
+      <c r="BD31" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BE31" s="4"/>
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
@@ -8280,12 +8351,15 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="BD32" s="8"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B31">
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 BE3:DG3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 BE4:BJ10 O4:AB31 BK4:DG31 BA5:BA31 D6:J31 M6:N31 BC11:BJ31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BE3:DG31 BC11:BD31">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFD6C20-C3F8-4D4D-9433-4B9967D77039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB9C300-20A6-4BC6-A119-B71391FEBDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -1080,30 +1080,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.7109375" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1263,7 +1263,9 @@
       <c r="BD1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BE1" s="7"/>
+      <c r="BE1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BF1" s="7"/>
       <c r="BG1" s="7"/>
       <c r="BH1" s="7"/>
@@ -1299,7 +1301,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1468,7 +1470,9 @@
       <c r="BD2" s="1">
         <v>46267</v>
       </c>
-      <c r="BE2" s="7"/>
+      <c r="BE2" s="7">
+        <v>46269</v>
+      </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="7"/>
       <c r="BH2" s="1"/>
@@ -1504,7 +1508,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1740,7 +1744,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1976,7 +1980,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2212,7 +2216,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2448,7 +2452,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2684,7 +2688,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2920,7 +2924,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3156,7 +3160,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3392,7 +3396,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3628,7 +3632,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3867,7 +3871,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4103,7 +4107,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4339,7 +4343,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4575,7 +4579,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4811,7 +4815,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5047,7 +5051,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5283,7 +5287,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5519,7 +5523,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5755,7 +5759,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5991,7 +5995,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6227,7 +6231,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6393,7 +6397,7 @@
         <v>34</v>
       </c>
       <c r="BD23" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
@@ -6463,7 +6467,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6699,7 +6703,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6935,7 +6939,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7101,7 +7105,7 @@
         <v>34</v>
       </c>
       <c r="BD26" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
@@ -7171,7 +7175,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7407,7 +7411,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7643,7 +7647,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7809,7 +7813,7 @@
         <v>34</v>
       </c>
       <c r="BD29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
@@ -7879,7 +7883,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8115,7 +8119,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8351,7 +8355,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8359,7 +8363,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BE3:DG31 BC11:BD31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -8392,14 +8396,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8407,7 +8411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8415,7 +8419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8423,7 +8427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8431,7 +8435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8439,7 +8443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8447,7 +8451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8455,7 +8459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8463,7 +8467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8471,7 +8475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8479,7 +8483,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8487,7 +8491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8495,7 +8499,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8503,7 +8507,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8511,7 +8515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8519,7 +8523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8527,7 +8531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8543,7 +8547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8551,7 +8555,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8559,7 +8563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8567,7 +8571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8575,7 +8579,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8583,7 +8587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8591,7 +8595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8599,7 +8603,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8607,7 +8611,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8615,7 +8619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8631,7 +8635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8648,18 +8652,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8667,7 +8671,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8676,7 +8680,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8685,7 +8689,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8694,7 +8698,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8703,13 +8707,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8718,7 +8722,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8727,7 +8731,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8743,13 +8747,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8758,7 +8762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8767,7 +8771,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8776,7 +8780,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8785,7 +8789,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8794,7 +8798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8803,7 +8807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8812,7 +8816,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8821,7 +8825,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8830,7 +8834,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8839,7 +8843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8848,7 +8852,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8857,7 +8861,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8866,25 +8870,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8893,7 +8897,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8902,7 +8906,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8911,7 +8915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB9C300-20A6-4BC6-A119-B71391FEBDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1E0C6E-2667-45B3-947F-43653A60CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>3F | P</t>
+  </si>
+  <si>
+    <t>5F | P</t>
   </si>
 </sst>
 </file>
@@ -752,7 +755,67 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1080,30 +1143,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1301,7 +1364,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1508,7 +1571,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1676,7 +1739,9 @@
       <c r="BD3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE3" s="4"/>
+      <c r="BE3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
       <c r="BH3" s="4"/>
@@ -1744,7 +1809,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1912,7 +1977,9 @@
       <c r="BD4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE4" s="4"/>
+      <c r="BE4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF4" s="4"/>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4"/>
@@ -1980,7 +2047,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2148,7 +2215,9 @@
       <c r="BD5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE5" s="4"/>
+      <c r="BE5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF5" s="4"/>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4"/>
@@ -2216,7 +2285,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2384,7 +2453,9 @@
       <c r="BD6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE6" s="4"/>
+      <c r="BE6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF6" s="4"/>
       <c r="BG6" s="4"/>
       <c r="BH6" s="4"/>
@@ -2452,7 +2523,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2620,7 +2691,9 @@
       <c r="BD7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE7" s="4"/>
+      <c r="BE7" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="BF7" s="4"/>
       <c r="BG7" s="4"/>
       <c r="BH7" s="4"/>
@@ -2688,7 +2761,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2856,7 +2929,9 @@
       <c r="BD8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE8" s="4"/>
+      <c r="BE8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF8" s="4"/>
       <c r="BG8" s="4"/>
       <c r="BH8" s="4"/>
@@ -2924,7 +2999,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3092,7 +3167,9 @@
       <c r="BD9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE9" s="4"/>
+      <c r="BE9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF9" s="4"/>
       <c r="BG9" s="4"/>
       <c r="BH9" s="4"/>
@@ -3160,7 +3237,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3328,7 +3405,9 @@
       <c r="BD10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE10" s="4"/>
+      <c r="BE10" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
@@ -3396,7 +3475,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3564,7 +3643,9 @@
       <c r="BD11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE11" s="4"/>
+      <c r="BE11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
@@ -3632,7 +3713,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3803,7 +3884,9 @@
       <c r="BD12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BE12" s="4"/>
+      <c r="BE12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
@@ -3871,7 +3954,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4039,7 +4122,9 @@
       <c r="BD13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE13" s="4"/>
+      <c r="BE13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
@@ -4107,7 +4192,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4275,7 +4360,9 @@
       <c r="BD14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE14" s="4"/>
+      <c r="BE14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
@@ -4343,7 +4430,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4511,7 +4598,9 @@
       <c r="BD15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE15" s="4"/>
+      <c r="BE15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
@@ -4579,7 +4668,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4747,7 +4836,9 @@
       <c r="BD16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE16" s="4"/>
+      <c r="BE16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF16" s="4"/>
       <c r="BG16" s="4"/>
       <c r="BH16" s="4"/>
@@ -4815,7 +4906,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -4983,7 +5074,9 @@
       <c r="BD17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE17" s="4"/>
+      <c r="BE17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
@@ -5051,7 +5144,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5219,7 +5312,9 @@
       <c r="BD18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE18" s="4"/>
+      <c r="BE18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
@@ -5287,7 +5382,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5455,7 +5550,9 @@
       <c r="BD19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE19" s="4"/>
+      <c r="BE19" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BF19" s="4"/>
       <c r="BG19" s="4"/>
       <c r="BH19" s="4"/>
@@ -5523,7 +5620,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5691,7 +5788,9 @@
       <c r="BD20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE20" s="4"/>
+      <c r="BE20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
@@ -5759,7 +5858,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -5927,7 +6026,9 @@
       <c r="BD21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE21" s="4"/>
+      <c r="BE21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
@@ -5995,7 +6096,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6163,7 +6264,9 @@
       <c r="BD22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE22" s="4"/>
+      <c r="BE22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
@@ -6231,7 +6334,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6399,7 +6502,9 @@
       <c r="BD23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="BE23" s="4"/>
+      <c r="BE23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
@@ -6467,7 +6572,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6635,7 +6740,9 @@
       <c r="BD24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE24" s="4"/>
+      <c r="BE24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
@@ -6703,7 +6810,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6871,7 +6978,9 @@
       <c r="BD25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE25" s="4"/>
+      <c r="BE25" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
@@ -6939,7 +7048,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7107,7 +7216,9 @@
       <c r="BD26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="BE26" s="4"/>
+      <c r="BE26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
@@ -7175,7 +7286,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7343,7 +7454,9 @@
       <c r="BD27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE27" s="4"/>
+      <c r="BE27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
@@ -7411,7 +7524,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7579,7 +7692,9 @@
       <c r="BD28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE28" s="4"/>
+      <c r="BE28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
@@ -7647,7 +7762,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7815,7 +7930,9 @@
       <c r="BD29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BE29" s="4"/>
+      <c r="BE29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
@@ -7883,7 +8000,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8051,7 +8168,9 @@
       <c r="BD30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BE30" s="4"/>
+      <c r="BE30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
@@ -8119,7 +8238,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8287,7 +8406,9 @@
       <c r="BD31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BE31" s="4"/>
+      <c r="BE31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
@@ -8355,7 +8476,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8363,29 +8484,34 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE3:BE31">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8396,14 +8522,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8411,7 +8537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8419,7 +8545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8427,7 +8553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8435,7 +8561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8443,7 +8569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8451,7 +8577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8459,7 +8585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8467,7 +8593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8475,7 +8601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8483,7 +8609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8491,7 +8617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8499,7 +8625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8507,7 +8633,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8515,7 +8641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8523,7 +8649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8531,7 +8657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8539,7 +8665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8547,7 +8673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8555,7 +8681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8563,7 +8689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8571,7 +8697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8579,7 +8705,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8587,7 +8713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8595,7 +8721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8603,7 +8729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8611,7 +8737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8619,7 +8745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8627,7 +8753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8635,7 +8761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8652,18 +8778,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8671,7 +8797,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8680,7 +8806,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8689,7 +8815,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8698,7 +8824,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8707,13 +8833,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8722,7 +8848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8731,7 +8857,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8747,13 +8873,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8762,7 +8888,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8771,7 +8897,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8780,7 +8906,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8789,7 +8915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8798,7 +8924,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8807,7 +8933,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8816,7 +8942,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8825,7 +8951,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8834,7 +8960,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8843,7 +8969,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8852,7 +8978,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8861,7 +8987,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8870,25 +8996,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -8897,7 +9023,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -8906,7 +9032,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -8915,7 +9041,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1E0C6E-2667-45B3-947F-43653A60CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11F918D-04CB-4B49-BF96-C1FA4F8C4C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="51">
   <si>
     <t>Aluno</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>5F | P</t>
+  </si>
+  <si>
+    <t>5/P</t>
   </si>
 </sst>
 </file>
@@ -755,57 +758,7 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1143,30 +1096,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.7109375" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1329,8 +1282,12 @@
       <c r="BE1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BF1" s="7"/>
-      <c r="BG1" s="7"/>
+      <c r="BF1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BH1" s="7"/>
       <c r="BI1" s="7"/>
       <c r="BJ1" s="7"/>
@@ -1364,7 +1321,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1536,8 +1493,12 @@
       <c r="BE2" s="7">
         <v>46269</v>
       </c>
-      <c r="BF2" s="1"/>
-      <c r="BG2" s="7"/>
+      <c r="BF2" s="1">
+        <v>46274</v>
+      </c>
+      <c r="BG2" s="7">
+        <v>46276</v>
+      </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="7"/>
       <c r="BJ2" s="1"/>
@@ -1571,7 +1532,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1742,7 +1703,9 @@
       <c r="BE3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF3" s="4"/>
+      <c r="BF3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG3" s="4"/>
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
@@ -1809,7 +1772,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1980,7 +1943,9 @@
       <c r="BE4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF4" s="4"/>
+      <c r="BF4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4"/>
       <c r="BI4" s="4"/>
@@ -2047,7 +2012,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2218,7 +2183,9 @@
       <c r="BE5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF5" s="4"/>
+      <c r="BF5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4"/>
       <c r="BI5" s="4"/>
@@ -2285,7 +2252,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2456,7 +2423,9 @@
       <c r="BE6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF6" s="4"/>
+      <c r="BF6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG6" s="4"/>
       <c r="BH6" s="4"/>
       <c r="BI6" s="4"/>
@@ -2523,7 +2492,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2694,7 +2663,9 @@
       <c r="BE7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="BF7" s="4"/>
+      <c r="BF7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG7" s="4"/>
       <c r="BH7" s="4"/>
       <c r="BI7" s="4"/>
@@ -2761,7 +2732,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2932,7 +2903,9 @@
       <c r="BE8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF8" s="4"/>
+      <c r="BF8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG8" s="4"/>
       <c r="BH8" s="4"/>
       <c r="BI8" s="4"/>
@@ -2999,7 +2972,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3170,7 +3143,9 @@
       <c r="BE9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF9" s="4"/>
+      <c r="BF9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG9" s="4"/>
       <c r="BH9" s="4"/>
       <c r="BI9" s="4"/>
@@ -3237,7 +3212,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3408,7 +3383,9 @@
       <c r="BE10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="BF10" s="4"/>
+      <c r="BF10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
       <c r="BI10" s="4"/>
@@ -3475,7 +3452,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3646,7 +3623,9 @@
       <c r="BE11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF11" s="4"/>
+      <c r="BF11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
       <c r="BI11" s="4"/>
@@ -3713,7 +3692,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3887,7 +3866,9 @@
       <c r="BE12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BF12" s="4"/>
+      <c r="BF12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
       <c r="BI12" s="4"/>
@@ -3954,7 +3935,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4125,7 +4106,9 @@
       <c r="BE13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF13" s="4"/>
+      <c r="BF13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
       <c r="BI13" s="4"/>
@@ -4192,7 +4175,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4363,7 +4346,9 @@
       <c r="BE14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF14" s="4"/>
+      <c r="BF14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
       <c r="BI14" s="4"/>
@@ -4430,7 +4415,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4601,7 +4586,9 @@
       <c r="BE15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF15" s="4"/>
+      <c r="BF15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
       <c r="BI15" s="4"/>
@@ -4668,7 +4655,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4839,7 +4826,9 @@
       <c r="BE16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF16" s="4"/>
+      <c r="BF16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG16" s="4"/>
       <c r="BH16" s="4"/>
       <c r="BI16" s="4"/>
@@ -4906,7 +4895,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5077,7 +5066,9 @@
       <c r="BE17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF17" s="4"/>
+      <c r="BF17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
       <c r="BI17" s="4"/>
@@ -5144,7 +5135,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5315,7 +5306,9 @@
       <c r="BE18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF18" s="4"/>
+      <c r="BF18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>
@@ -5382,7 +5375,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5553,7 +5546,9 @@
       <c r="BE19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BF19" s="4"/>
+      <c r="BF19" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="BG19" s="4"/>
       <c r="BH19" s="4"/>
       <c r="BI19" s="4"/>
@@ -5620,7 +5615,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5791,7 +5786,9 @@
       <c r="BE20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF20" s="4"/>
+      <c r="BF20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
@@ -5858,7 +5855,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6029,7 +6026,9 @@
       <c r="BE21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF21" s="4"/>
+      <c r="BF21" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
@@ -6096,7 +6095,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6267,7 +6266,9 @@
       <c r="BE22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF22" s="4"/>
+      <c r="BF22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
@@ -6334,7 +6335,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6505,7 +6506,9 @@
       <c r="BE23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF23" s="4"/>
+      <c r="BF23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
@@ -6572,7 +6575,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6743,7 +6746,9 @@
       <c r="BE24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF24" s="4"/>
+      <c r="BF24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
@@ -6810,7 +6815,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -6981,7 +6986,9 @@
       <c r="BE25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BF25" s="4"/>
+      <c r="BF25" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
@@ -7048,7 +7055,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7219,7 +7226,9 @@
       <c r="BE26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF26" s="4"/>
+      <c r="BF26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
@@ -7286,7 +7295,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7457,7 +7466,9 @@
       <c r="BE27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF27" s="4"/>
+      <c r="BF27" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
@@ -7524,7 +7535,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7695,7 +7706,9 @@
       <c r="BE28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF28" s="4"/>
+      <c r="BF28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
@@ -7762,7 +7775,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -7933,7 +7946,9 @@
       <c r="BE29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF29" s="4"/>
+      <c r="BF29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
@@ -8000,7 +8015,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8171,7 +8186,9 @@
       <c r="BE30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF30" s="4"/>
+      <c r="BF30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
@@ -8238,7 +8255,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8409,7 +8426,9 @@
       <c r="BE31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF31" s="4"/>
+      <c r="BF31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
@@ -8476,7 +8495,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8484,28 +8503,28 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8522,14 +8541,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8537,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8545,7 +8564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8553,7 +8572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8561,7 +8580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8569,7 +8588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8577,7 +8596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8585,7 +8604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8593,7 +8612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8601,7 +8620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8609,7 +8628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8617,7 +8636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8625,7 +8644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8633,7 +8652,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8641,7 +8660,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8649,7 +8668,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8657,7 +8676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8665,7 +8684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8673,7 +8692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8681,7 +8700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8689,7 +8708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8697,7 +8716,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8705,7 +8724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8713,7 +8732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8721,7 +8740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8729,7 +8748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8737,7 +8756,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8745,7 +8764,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8753,7 +8772,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8761,7 +8780,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8778,18 +8797,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8797,7 +8816,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8806,7 +8825,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8815,7 +8834,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8824,7 +8843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8833,13 +8852,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8848,7 +8867,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8857,7 +8876,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8873,13 +8892,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8888,7 +8907,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8897,7 +8916,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8906,7 +8925,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8915,7 +8934,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -8924,7 +8943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -8933,7 +8952,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -8942,7 +8961,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -8951,7 +8970,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -8960,7 +8979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -8969,7 +8988,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -8978,7 +8997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -8987,7 +9006,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -8996,25 +9015,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9023,7 +9042,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9032,7 +9051,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9041,7 +9060,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11F918D-04CB-4B49-BF96-C1FA4F8C4C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EB0650-7054-476C-80AE-C5A150963BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="51">
   <si>
     <t>Aluno</t>
   </si>
@@ -1706,7 +1706,9 @@
       <c r="BF3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG3" s="4"/>
+      <c r="BG3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
@@ -1946,7 +1948,9 @@
       <c r="BF4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG4" s="4"/>
+      <c r="BG4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH4" s="4"/>
       <c r="BI4" s="4"/>
       <c r="BJ4" s="4"/>
@@ -2186,7 +2190,9 @@
       <c r="BF5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG5" s="4"/>
+      <c r="BG5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH5" s="4"/>
       <c r="BI5" s="4"/>
       <c r="BJ5" s="4"/>
@@ -2426,7 +2432,9 @@
       <c r="BF6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG6" s="4"/>
+      <c r="BG6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH6" s="4"/>
       <c r="BI6" s="4"/>
       <c r="BJ6" s="4"/>
@@ -2666,7 +2674,9 @@
       <c r="BF7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG7" s="4"/>
+      <c r="BG7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH7" s="4"/>
       <c r="BI7" s="4"/>
       <c r="BJ7" s="4"/>
@@ -2906,7 +2916,9 @@
       <c r="BF8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG8" s="4"/>
+      <c r="BG8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH8" s="4"/>
       <c r="BI8" s="4"/>
       <c r="BJ8" s="4"/>
@@ -3146,7 +3158,9 @@
       <c r="BF9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG9" s="4"/>
+      <c r="BG9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH9" s="4"/>
       <c r="BI9" s="4"/>
       <c r="BJ9" s="4"/>
@@ -3386,7 +3400,9 @@
       <c r="BF10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG10" s="4"/>
+      <c r="BG10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH10" s="4"/>
       <c r="BI10" s="4"/>
       <c r="BJ10" s="4"/>
@@ -3626,7 +3642,9 @@
       <c r="BF11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG11" s="4"/>
+      <c r="BG11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH11" s="4"/>
       <c r="BI11" s="4"/>
       <c r="BJ11" s="4"/>
@@ -3869,7 +3887,9 @@
       <c r="BF12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG12" s="4"/>
+      <c r="BG12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH12" s="4"/>
       <c r="BI12" s="4"/>
       <c r="BJ12" s="4"/>
@@ -4109,7 +4129,9 @@
       <c r="BF13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG13" s="4"/>
+      <c r="BG13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH13" s="4"/>
       <c r="BI13" s="4"/>
       <c r="BJ13" s="4"/>
@@ -4349,7 +4371,9 @@
       <c r="BF14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG14" s="4"/>
+      <c r="BG14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH14" s="4"/>
       <c r="BI14" s="4"/>
       <c r="BJ14" s="4"/>
@@ -4589,7 +4613,9 @@
       <c r="BF15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG15" s="4"/>
+      <c r="BG15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH15" s="4"/>
       <c r="BI15" s="4"/>
       <c r="BJ15" s="4"/>
@@ -4829,7 +4855,9 @@
       <c r="BF16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG16" s="4"/>
+      <c r="BG16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH16" s="4"/>
       <c r="BI16" s="4"/>
       <c r="BJ16" s="4"/>
@@ -5069,7 +5097,9 @@
       <c r="BF17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG17" s="4"/>
+      <c r="BG17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH17" s="4"/>
       <c r="BI17" s="4"/>
       <c r="BJ17" s="4"/>
@@ -5309,7 +5339,9 @@
       <c r="BF18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG18" s="4"/>
+      <c r="BG18" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>
       <c r="BJ18" s="4"/>
@@ -5549,7 +5581,9 @@
       <c r="BF19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="BG19" s="4"/>
+      <c r="BG19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH19" s="4"/>
       <c r="BI19" s="4"/>
       <c r="BJ19" s="4"/>
@@ -5789,7 +5823,9 @@
       <c r="BF20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG20" s="4"/>
+      <c r="BG20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
       <c r="BJ20" s="4"/>
@@ -6029,7 +6065,9 @@
       <c r="BF21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="BG21" s="4"/>
+      <c r="BG21" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
       <c r="BJ21" s="4"/>
@@ -6269,7 +6307,9 @@
       <c r="BF22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG22" s="4"/>
+      <c r="BG22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
       <c r="BJ22" s="4"/>
@@ -6509,7 +6549,9 @@
       <c r="BF23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG23" s="4"/>
+      <c r="BG23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
       <c r="BJ23" s="4"/>
@@ -6749,7 +6791,9 @@
       <c r="BF24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG24" s="4"/>
+      <c r="BG24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
@@ -6989,7 +7033,9 @@
       <c r="BF25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BG25" s="4"/>
+      <c r="BG25" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
@@ -7229,7 +7275,9 @@
       <c r="BF26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG26" s="4"/>
+      <c r="BG26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
       <c r="BJ26" s="4"/>
@@ -7469,7 +7517,9 @@
       <c r="BF27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BG27" s="4"/>
+      <c r="BG27" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
       <c r="BJ27" s="4"/>
@@ -7709,7 +7759,9 @@
       <c r="BF28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG28" s="4"/>
+      <c r="BG28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
       <c r="BJ28" s="4"/>
@@ -7949,7 +8001,9 @@
       <c r="BF29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG29" s="4"/>
+      <c r="BG29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="4"/>
@@ -8189,7 +8243,9 @@
       <c r="BF30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG30" s="4"/>
+      <c r="BG30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="4"/>
@@ -8429,7 +8485,9 @@
       <c r="BF31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BG31" s="4"/>
+      <c r="BG31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EB0650-7054-476C-80AE-C5A150963BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438241DC-F5A1-4E5B-86B0-4EA4EAD92291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5340,7 +5340,7 @@
         <v>34</v>
       </c>
       <c r="BG18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438241DC-F5A1-4E5B-86B0-4EA4EAD92291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C7A4DC-2C51-4979-93BB-54C7CEC700CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -1096,30 +1096,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1774,7 +1774,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -2016,7 +2016,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2258,7 +2258,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2500,7 +2500,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2742,7 +2742,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2984,7 +2984,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3226,7 +3226,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3468,7 +3468,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3710,7 +3710,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3955,7 +3955,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4197,7 +4197,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4439,7 +4439,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4681,7 +4681,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4923,7 +4923,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5165,7 +5165,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5407,7 +5407,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5649,7 +5649,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5891,7 +5891,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6066,7 +6066,7 @@
         <v>50</v>
       </c>
       <c r="BG21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
@@ -6133,7 +6133,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6375,7 +6375,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6617,7 +6617,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6859,7 +6859,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -7101,7 +7101,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7343,7 +7343,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7518,7 +7518,7 @@
         <v>35</v>
       </c>
       <c r="BG27" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
@@ -7585,7 +7585,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7827,7 +7827,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -8069,7 +8069,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8311,7 +8311,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8553,7 +8553,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8599,14 +8599,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8855,18 +8855,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8883,7 +8883,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8892,7 +8892,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8901,7 +8901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8910,13 +8910,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8925,7 +8925,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8934,7 +8934,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8950,13 +8950,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8965,7 +8965,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8974,7 +8974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8983,7 +8983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8992,7 +8992,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -9001,7 +9001,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -9010,7 +9010,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -9019,7 +9019,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -9028,7 +9028,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -9037,7 +9037,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -9046,7 +9046,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -9055,7 +9055,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -9064,7 +9064,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -9073,25 +9073,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9100,7 +9100,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9109,7 +9109,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9118,7 +9118,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>
